--- a/data_processing/Dataset_data_filtered_final.xlsx
+++ b/data_processing/Dataset_data_filtered_final.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="594">
-  <si>
-    <t xml:space="preserve">Study Identifier</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="742">
+  <si>
+    <t xml:space="preserve">Study.Identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Year</t>
@@ -25,10 +25,10 @@
     <t xml:space="preserve">Intervention</t>
   </si>
   <si>
-    <t xml:space="preserve">Intervention types</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intervention subgroups</t>
+    <t xml:space="preserve">Intervention.types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervention.subgroups</t>
   </si>
   <si>
     <t xml:space="preserve">Country</t>
@@ -37,475 +37,475 @@
     <t xml:space="preserve">Setting</t>
   </si>
   <si>
-    <t xml:space="preserve">Types of disease_clean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type of disease in two categories (dementia and MCI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated Dementia Severity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is this a study focusing on carers of people living with dementia or mild cognitive impairment?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain 5</t>
+    <t xml:space="preserve">Types.of.disease_clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type.of.disease.in.two.categories.(dementia.and.MCI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updated.Dementia.Severity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is.this.a.study.focusing.on.carers.of.people.living.with.dementia.or.mild.cognitive.impairment?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain.5</t>
   </si>
   <si>
     <t xml:space="preserve">Overall</t>
   </si>
   <si>
-    <t xml:space="preserve">Baseline Educational level (indicate how this was measured)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline Female (percent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline For studies in carers only: Caregiver age in years (mean)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline For studies in carers only: Caregiver female (percent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline For studies in carers only: Full-time working (percent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline MMSE score (mean)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline Rural setting (percent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline Urban setting (percent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intervention Brief description of intervention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intervention Intervention details...97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intervention Intervention details (duration and intensity of the intervention, dosage of drugs, existence of a protocol or manual for psychosocial, training or education interventions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intervention Interv. type [SELECT: Pharmaceutical; Traditional Chinese Medicine; Other trad. medicines; Non-pharmacol.; Multicomponent (record each component); Interv. for carers; End of life care; Treatment/prevention of co-morbidities; Technology; Diagn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burden of caregiver Follow up mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burden of caregiver Follow up N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burden of caregiver Follow up SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burden of caregiver Post-test mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burden of caregiver Post-test N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burden of caregiver Post-test SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burden of caregiver Pre-test mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burden of caregiver Pre-test N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burden of caregiver Pre-test SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver Burden 3 months SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver Burden 3 months Mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver Burden Baseline SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver Burden Baseline Mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 1 month post-treatment (Zarit Caregiver Burden Scale)  1 month post-treatment mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 1 month post-treatment (Zarit Caregiver Burden Scale)  1 month post-treatment N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 1 month post-treatment (Zarit Caregiver Burden Scale)  1 month post-treatment SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 1 month post-treatment (Zarit Caregiver Burden Scale)  Baseline mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 1 month post-treatment (Zarit Caregiver Burden Scale)  Baseline N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 1 month post-treatment (Zarit Caregiver Burden Scale)  Baseline SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 1 month post-treatment (Zarit Caregiver Burden Scale)  End of intervention mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 1 month post-treatment (Zarit Caregiver Burden Scale)  End of intervention N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 1 month post-treatment (Zarit Caregiver Burden Scale)  End of intervention SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 4 months (Zarit Burden Interview) Baseline mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 4 months (Zarit Burden Interview) Baseline N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 4 months (Zarit Burden Interview) Baseline SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 4 months (Zarit Burden Interview) Posttest mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 4 months (Zarit Burden Interview) Posttest N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 4 months (Zarit Burden Interview) Posttest SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 6 months (Caregiver Burden Inventory) Posttest 2 (3 months post-intervention) mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 6 months (Caregiver Burden Inventory) Posttest 2 (3 months post-intervention) N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 6 months (Caregiver Burden Inventory) Posttest 2 (3 months post-intervention) SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 6 months (Caregiver Burden Inventory) Pretest mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 6 months (Caregiver Burden Inventory) Pretest N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 6 months (Caregiver Burden Inventory) Pretest SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 8 weeks (Zarit Burden Interview) 8 weeks mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 8 weeks (Zarit Burden Interview) 8 weeks N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 8 weeks (Zarit Burden Interview) 8 weeks SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 8 weeks (Zarit Burden Interview) Baseline mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 8 weeks (Zarit Burden Interview) Baseline N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden at 8 weeks (Zarit Burden Interview) Baseline SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden (Zarit Burden Scale) 7 weeks mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden (Zarit Burden Scale) 7 weeks N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden (Zarit Burden Scale) 7 weeks SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden (Zarit Burden Scale) Baseline mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden (Zarit Burden Scale) Baseline N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver burden (Zarit Burden Scale) Baseline SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver distress from BPSD (NPI-Q) 6 months Adjusted standardised mean difference between intervention and control groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver distress from BPSD (NPI-Q) 6 months N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver distress from BPSD (NPI-Q) 6 months Upper bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver distress from BPSD (NPI-Q) 6 months Lower bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver environmental quality of life (WHO-QoL-Bref) 6 months Adjusted standardised mean difference between intervention and control groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver environmental quality of life (WHO-QoL-Bref) 6 months N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver environmental quality of life (WHO-QoL-Bref) 6 months Upper bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver environmental quality of life (WHO-QoL-Bref) 6 months Lower bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver physical quality of life (WHO-QoL-Bref)  6 months Adjusted standardised mean difference between intervention and control groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver physical quality of life (WHO-QoL-Bref)  6 months N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver physical quality of life (WHO-QoL-Bref)  6 months Upper bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver physical quality of life (WHO-QoL-Bref)  6 months Lower bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver psychological morbidity (SRQ-20) 6 months Adjusted standardised mean difference between intervention and control groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver psychological morbidity (SRQ-20) 6 months N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver psychological morbidity (SRQ-20) 6 months Upper bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver psychological morbidity (SRQ-20) 6 months Lower bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver psychological quality of life (WHO-QoL-Bref) 6 months Adjusted standardised mean difference between intervention and control groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver psychological quality of life (WHO-QoL-Bref) 6 months N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver psychological quality of life (WHO-QoL-Bref) 6 months Upper bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver psychological quality of life (WHO-QoL-Bref) 6 months Lower bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 4 months (QOL-AD caregivers) Baseline mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 4 months (QOL-AD caregivers) Baseline N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 4 months (QOL-AD caregivers) Baseline SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 4 months (QOL-AD caregivers) Posttest mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 4 months (QOL-AD caregivers) Posttest N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 4 months (QOL-AD caregivers) Posttest SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 6 months (WHOQOL-BREF) Posttest 2 (3 months post-intervention) mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 6 months (WHOQOL-BREF) Posttest 2 (3 months post-intervention) N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 6 months (WHOQOL-BREF) Posttest 2 (3 months post-intervention) SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 6 months (WHOQOL-BREF) Pretest mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 6 months (WHOQOL-BREF) Pretest N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life at 6 months (WHOQOL-BREF) Pretest SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver role strain (Zarit burden interview) 6 months Adjusted standardised mean difference between intervention and control groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver role strain (Zarit burden interview) 6 months N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver role strain (Zarit burden interview) 6 months Upper bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver role strain (Zarit burden interview) 6 months Lower bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver social quality of life (WHO-QoL-Bref) 6 months Adjusted standardised mean difference between intervention and control groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver social quality of life (WHO-QoL-Bref) 6 months N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver social quality of life (WHO-QoL-Bref) 6 months Upper bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver social quality of life (WHO-QoL-Bref) 6 months Lower bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Care recipient BPSD severity (NPI-Q) 6 months Adjusted standardised mean difference between intervention and control groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Care recipient BPSD severity (NPI-Q) 6 months N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Care recipient BPSD severity (NPI-Q) 6 months Upper bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Care recipient BPSD severity (NPI-Q) 6 months Lower bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Care recipient quality of life (DEMQOL) 6 months Adjusted standardised mean difference between intervention and control groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Care recipient quality of life (DEMQOL) 6 months N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Care recipient quality of life (DEMQOL) 6 months Upper bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Care recipient quality of life (DEMQOL) 6 months Lower bound 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depression Follow up mean_211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depression Follow up N.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depression Follow up SD_212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depression Post-test mean_215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depression Post-test N.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depression Post-test SD_216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depression Pre-test mean_217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depression Pre-test N.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depression Pre-test SD_218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perceived caregiver burden at 6 months (Zarit Burden score) 6 months N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perceived caregiver burden at 6 months (Zarit Burden score) 6 months upper 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perceived caregiver burden at 6 months (Zarit Burden score) 6 months Treatment effect in intervention group at 6 months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perceived caregiver burden at 6 months (Zarit Burden score) 6 months lower 95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life 3 months SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life 3 months Mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life Baseline SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life Baseline Mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life Follow up mean.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life Follow up N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life Follow up SD_410</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life Post-test mean.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life Post-test N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life Post-test SD_411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life Pre-test mean.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life Pre-test N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality of life Pre-test SD_412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Interview (ZBI) Baseline mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Interview (ZBI) Baseline N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Interview (ZBI) Baseline SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Interview (ZBI) Change at 3 month follow up mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Interview (ZBI) Change at 3 month follow up N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Interview (ZBI) Change at 3 month follow up SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Interview (ZBI) Post Intervention Change mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Interview (ZBI) Post Intervention Change N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Interview (ZBI) Post Intervention Change SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Scale (ZBS) After intervention mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Scale (ZBS) After intervention N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Scale (ZBS) After intervention SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Scale (ZBS) Baseline mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Scale (ZBS) Baseline N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarit Burden Scale (ZBS) Baseline SD</t>
+    <t xml:space="preserve">Baseline.Educational.level.(indicate.how.this.was.measured)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline.Female.(percent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline.For.studies.in.carers.only:.Caregiver.age.in.years.(mean)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline.For.studies.in.carers.only:.Caregiver.female.(percent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline.For.studies.in.carers.only:.Full-time.working.(percent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline.MMSE.score.(mean)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline.Rural.setting.(percent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline.Urban.setting.(percent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervention.Brief.description.of.intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervention.Intervention.details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervention.Intervention.details.(duration.and.intensity.of.the.intervention,.dosage.of.drugs,.existence.of.a.protocol.or.manual.for.psychosocial,.training.or.education.interventions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervention.Interv..type.[SELECT:.Pharmaceutical;.Traditional.Chinese.Medicine;.Other.trad..medicines;.Non-pharmacol.;.Multicomponent.(record.each.component);.Interv..for.carers;.End.of.life.care;.Treatment/prevention.of.co-morbidities;.Technology;.Diagn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burden.of.caregiver.Follow.up.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burden.of.caregiver.Follow.up.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burden.of.caregiver.Follow.up.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burden.of.caregiver.Post-test.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burden.of.caregiver.Post-test.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burden.of.caregiver.Post-test.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burden.of.caregiver.Pre-test.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burden.of.caregiver.Pre-test.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burden.of.caregiver.Pre-test.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.Burden.3.months.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.Burden.3.months.Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.Burden.Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.Burden.Baseline.Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.1.month.post-treatment.(Zarit.Caregiver.Burden.Scale).1.month.post-treatment.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.1.month.post-treatment.(Zarit.Caregiver.Burden.Scale).1.month.post-treatment.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.1.month.post-treatment.(Zarit.Caregiver.Burden.Scale).1.month.post-treatment.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.1.month.post-treatment.(Zarit.Caregiver.Burden.Scale).Baseline.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.1.month.post-treatment.(Zarit.Caregiver.Burden.Scale).Baseline.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.1.month.post-treatment.(Zarit.Caregiver.Burden.Scale).Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.1.month.post-treatment.(Zarit.Caregiver.Burden.Scale).End.of.intervention.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.1.month.post-treatment.(Zarit.Caregiver.Burden.Scale).End.of.intervention.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.1.month.post-treatment.(Zarit.Caregiver.Burden.Scale).End.of.intervention.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.4.months.(Zarit.Burden.Interview).Baseline.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.4.months.(Zarit.Burden.Interview).Baseline.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.4.months.(Zarit.Burden.Interview).Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.4.months.(Zarit.Burden.Interview).Posttest.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.4.months.(Zarit.Burden.Interview).Posttest.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.4.months.(Zarit.Burden.Interview).Posttest.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.6.months.(Caregiver.Burden.Inventory).Posttest.2.(3.months.post-intervention).mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.6.months.(Caregiver.Burden.Inventory).Posttest.2.(3.months.post-intervention).N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.6.months.(Caregiver.Burden.Inventory).Posttest.2.(3.months.post-intervention).SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.6.months.(Caregiver.Burden.Inventory).Pretest.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.6.months.(Caregiver.Burden.Inventory).Pretest.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.6.months.(Caregiver.Burden.Inventory).Pretest.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.8.weeks.(Zarit.Burden.Interview).8.weeks.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.8.weeks.(Zarit.Burden.Interview).8.weeks.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.8.weeks.(Zarit.Burden.Interview).8.weeks.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.8.weeks.(Zarit.Burden.Interview).Baseline.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.8.weeks.(Zarit.Burden.Interview).Baseline.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.at.8.weeks.(Zarit.Burden.Interview).Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.(Zarit.Burden.Scale).7.weeks.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.(Zarit.Burden.Scale).7.weeks.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.(Zarit.Burden.Scale).7.weeks.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.(Zarit.Burden.Scale).Baseline.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.(Zarit.Burden.Scale).Baseline.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.burden.(Zarit.Burden.Scale).Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.distress.from.BPSD.(NPI-Q).6.months.Adjusted.standardised.mean.difference.between.intervention.and.control.groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.distress.from.BPSD.(NPI-Q).6.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.distress.from.BPSD.(NPI-Q).6.months.Upper.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.distress.from.BPSD.(NPI-Q).6.months.Lower.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.environmental.quality.of.life.(WHO-QoL-Bref).6.months.Adjusted.standardised.mean.difference.between.intervention.and.control.groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.environmental.quality.of.life.(WHO-QoL-Bref).6.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.environmental.quality.of.life.(WHO-QoL-Bref).6.months.Upper.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.environmental.quality.of.life.(WHO-QoL-Bref).6.months.Lower.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.physical.quality.of.life.(WHO-QoL-Bref).6.months.Adjusted.standardised.mean.difference.between.intervention.and.control.groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.physical.quality.of.life.(WHO-QoL-Bref).6.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.physical.quality.of.life.(WHO-QoL-Bref).6.months.Upper.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.physical.quality.of.life.(WHO-QoL-Bref).6.months.Lower.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.psychological.morbidity.(SRQ-20).6.months.Adjusted.standardised.mean.difference.between.intervention.and.control.groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.psychological.morbidity.(SRQ-20).6.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.psychological.morbidity.(SRQ-20).6.months.Upper.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.psychological.morbidity.(SRQ-20).6.months.Lower.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.psychological.quality.of.life.(WHO-QoL-Bref).6.months.Adjusted.standardised.mean.difference.between.intervention.and.control.groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.psychological.quality.of.life.(WHO-QoL-Bref).6.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.psychological.quality.of.life.(WHO-QoL-Bref).6.months.Upper.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.psychological.quality.of.life.(WHO-QoL-Bref).6.months.Lower.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.4.months.(QOL-AD.caregivers).Baseline.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.4.months.(QOL-AD.caregivers).Baseline.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.4.months.(QOL-AD.caregivers).Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.4.months.(QOL-AD.caregivers).Posttest.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.4.months.(QOL-AD.caregivers).Posttest.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.4.months.(QOL-AD.caregivers).Posttest.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.6.months.(WHOQOL-BREF).Posttest.2.(3.months.post-intervention).mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.6.months.(WHOQOL-BREF).Posttest.2.(3.months.post-intervention).N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.6.months.(WHOQOL-BREF).Posttest.2.(3.months.post-intervention).SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.6.months.(WHOQOL-BREF).Pretest.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.6.months.(WHOQOL-BREF).Pretest.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.at.6.months.(WHOQOL-BREF).Pretest.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.role.strain.(Zarit.burden.interview).6.months.Adjusted.standardised.mean.difference.between.intervention.and.control.groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.role.strain.(Zarit.burden.interview).6.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.role.strain.(Zarit.burden.interview).6.months.Upper.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.role.strain.(Zarit.burden.interview).6.months.Lower.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.social.quality.of.life.(WHO-QoL-Bref).6.months.Adjusted.standardised.mean.difference.between.intervention.and.control.groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.social.quality.of.life.(WHO-QoL-Bref).6.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.social.quality.of.life.(WHO-QoL-Bref).6.months.Upper.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.social.quality.of.life.(WHO-QoL-Bref).6.months.Lower.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Care.recipient.BPSD.severity.(NPI-Q).6.months.Adjusted.standardised.mean.difference.between.intervention.and.control.groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Care.recipient.BPSD.severity.(NPI-Q).6.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Care.recipient.BPSD.severity.(NPI-Q).6.months.Upper.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Care.recipient.BPSD.severity.(NPI-Q).6.months.Lower.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Care.recipient.quality.of.life.(DEMQOL).6.months.Adjusted.standardised.mean.difference.between.intervention.and.control.groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Care.recipient.quality.of.life.(DEMQOL).6.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Care.recipient.quality.of.life.(DEMQOL).6.months.Upper.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Care.recipient.quality.of.life.(DEMQOL).6.months.Lower.bound.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depression.Follow.up.mean_211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depression.Follow.up.N.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depression.Follow.up.SD_212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depression.Post-test.mean_215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depression.Post-test.N.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depression.Post-test.SD_216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depression.Pre-test.mean_217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depression.Pre-test.N.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depression.Pre-test.SD_218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perceived.caregiver.burden.at.6.months.(Zarit.Burden.score).6.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perceived.caregiver.burden.at.6.months.(Zarit.Burden.score).6.months.upper.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perceived.caregiver.burden.at.6.months.(Zarit.Burden.score).6.months.Treatment.effect.in.intervention.group.at.6.months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perceived.caregiver.burden.at.6.months.(Zarit.Burden.score).6.months.lower.95%.CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.3.months.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.3.months.Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.Baseline.Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.Follow.up.mean.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.Follow.up.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.Follow.up.SD_410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.Post-test.mean.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.Post-test.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.Post-test.SD_411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.Pre-test.mean.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.Pre-test.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality.of.life.Pre-test.SD_412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Interview.(ZBI).Baseline.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Interview.(ZBI).Baseline.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Interview.(ZBI).Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Interview.(ZBI).Change.at.3.month.follow.up.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Interview.(ZBI).Change.at.3.month.follow.up.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Interview.(ZBI).Change.at.3.month.follow.up.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Interview.(ZBI).Post.Intervention.Change.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Interview.(ZBI).Post.Intervention.Change.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Interview.(ZBI).Post.Intervention.Change.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Scale.(ZBS).After.intervention.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Scale.(ZBS).After.intervention.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Scale.(ZBS).After.intervention.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Scale.(ZBS).Baseline.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Scale.(ZBS).Baseline.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarit.Burden.Scale.(ZBS).Baseline.SD</t>
   </si>
   <si>
     <t xml:space="preserve">Amit 2008</t>
@@ -715,7 +715,7 @@
     <t xml:space="preserve">Peru</t>
   </si>
   <si>
-    <t xml:space="preserve">Intervention was carried out at the participant's home.</t>
+    <t xml:space="preserve">Intervention was carried out at the participant's home. </t>
   </si>
   <si>
     <t xml:space="preserve">Any severity stage</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">Turkey</t>
   </si>
   <si>
-    <t xml:space="preserve">Western Turkey, home based. Patient lists were obtained from dementia outpatient clinics at one university hospital and the office of the Alzheimer’s Association in Izmir.</t>
+    <t xml:space="preserve">Western Turkey, home based. Patient lists were obtained from dementia outpatient clinics at one university hospital and the office of the Alzheimer’s Association in Izmir. </t>
   </si>
   <si>
     <t xml:space="preserve">Mild</t>
@@ -1107,7 +1107,7 @@
   </si>
   <si>
     <t xml:space="preserve">"The PLST model (Hall &amp; Buckwalter, 1987) provides the foundation for a psychoeduca-tional intervention that assists formal and informal caregivers in understanding behaviors and plan-ning care for individuals with de-mentia. It has been tested widely since 1988. The model can be eas-ily understood by professional and non-professional caregivers and allows for flexible modification of the care plan based on individuals’ changing needs. The PLST model is a conceptual framework that organizes symp-toms, suggests causes of challenging behaviors, and teaches caregivers methods of modifying the envi-ronment to eliminate or minimize behavioral symptoms. The rea-sons for, or triggers of, symptoms can usually be modified in any setting, resulting in a decrease in behaviors distressing to caregiv-ers and individuals with dementia. The PLST model should empower caregivers by helping them pre-vent and manage the most difficult behaviors in Alzheimer’s disease. 
- [...] Interventions were conduct-ed at patients’ homes in their usual environment. Individuals with de-mentia and their caregivers in the experimental group were seen four times in a 6-month period. Each session lasted at least 1 hour. The intervention phase lasted 3 months. [...] The first home visit focused on understanding the behaviors of the individuals with dementia, how caregivers coped with these behav-iors, and difficulties experienced by caregivers. After 2 weeks, during the second home visit for caregivers in the experimental group, the PLST-based intervention was pro-vided and demonstrated. At the third home visit 2 months later, the care plan was reviewed, more techniques were taught, and writ-ten materials summarizing the care plan were provided. After the third home visit, follow-up telephone calls were made every 2 weeks. Ex-perimental group members also re-ceived a caregiver booklet prepared by the authors that contained a variety of educational and support materials, such as general informa-tion about the disease, common problems (e.g., sleep disturbances), how to administer medications, bathing, toileting, physical activi-ties, nutrition, and communication, as well as recommended reading for family members caring for individ-uals with dementia."</t>
+ [...] Interventions were conduct-ed at patients’ homes in their usual environment. Individuals with de-mentia and their caregivers in the experimental group were seen four times in a 6-month period. Each session lasted at least 1 hour. The intervention phase lasted 3 months. [...] The first home visit focused on understanding the behaviors of the individuals with dementia, how caregivers coped with these behav-iors, and difficulties experienced by caregivers. After 2 weeks, during the second home visit for caregivers in the experimental group, the PLST-based intervention was pro-vided and demonstrated. At the third home visit 2 months later, the care plan was reviewed, more techniques were taught, and writ-ten materials summarizing the care plan were provided. After the third home visit, follow-up telephone calls were made every 2 weeks. Ex-perimental group members also re-ceived a caregiver booklet prepared by the authors that contained a variety of educational and support materials, such as general informa-tion about the disease, common problems (e.g., sleep disturbances), how to administer medications, bathing, toileting, physical activi-ties, nutrition, and communication, as well as recommended reading for family members caring for individ-uals with dementia." </t>
   </si>
   <si>
     <t xml:space="preserve">34.71</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">Lin 2017</t>
   </si>
   <si>
-    <t xml:space="preserve">Nursing intervention</t>
+    <t xml:space="preserve"> Nursing intervention </t>
   </si>
   <si>
     <t xml:space="preserve">China</t>
   </si>
   <si>
-    <t xml:space="preserve">urban, community</t>
+    <t xml:space="preserve">urban, community </t>
   </si>
   <si>
     <t xml:space="preserve">66.54</t>
@@ -1471,7 +1471,7 @@
     <t xml:space="preserve">4.08</t>
   </si>
   <si>
-    <t xml:space="preserve">Tailored Activity Program - Brazilian Version (TAP-BR)</t>
+    <t xml:space="preserve">Tailored Activity Program - Brazilian Version (TAP-BR) </t>
   </si>
   <si>
     <t xml:space="preserve">Structured therapeutic psychosocial interventions</t>
@@ -1526,124 +1526,184 @@
     <t xml:space="preserve">4.07</t>
   </si>
   <si>
-    <t xml:space="preserve">Primary Cognition Measure standardized z-score change</t>
+    <t xml:space="preserve">Primary.Cognition.Measure.standardized.z-score.change</t>
   </si>
   <si>
     <t xml:space="preserve">Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Baseline Score - Primary Cognition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Participants at Baseline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post Treatment Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post Treatment N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post Treatment SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post Treatment Time (Months from Start)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline For studies in carers only: Part-time working (percent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL after 12 months treatment mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL after 12 months treatment N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL after 12 months treatment SD_22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL after 6 months treatment mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL after 6 months treatment N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL after 6 months treatment SD_23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL after treatment mean...353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL after treatment N...354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL after treatment SD_25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL Baseline mean...363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL Baseline N...364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADL Baseline SD_27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life (WHOQOL-BREF) Post-test (1 month after 24 week intervention) mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life (WHOQOL-BREF) Post-test (1 month after 24 week intervention) N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life (WHOQOL-BREF) Post-test (1 month after 24 week intervention) SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life (WHOQOL-BREF) Pre-test mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life (WHOQOL-BREF) Pre-test N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caregiver quality of life (WHOQOL-BREF) Pre-test SD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE after 12 months treatment mean.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE after 12 months treatment N_309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE after 12 months treatment SD_310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE after 6 months treatment mean.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE after 6 months treatment N_318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE after 6 months treatment SD_319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE after treatment mean.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE after treatment N_324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE after treatment SD_325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE Baseline mean.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE Baseline N_348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE Baseline SD_349</t>
+    <t xml:space="preserve">Baseline.Score.-.Primary.Cognition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number.of.Participants.at.Baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post.Treatment.Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post.Treatment.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post.Treatment.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post.Treatment.Time.(Weeks.from.Start)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post.Treatment.Time.(Months.from.Start)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervention.Brief.introduction.to.the.intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervention.Intervention.details.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.after.12.months.treatment.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.after.12.months.treatment.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.after.12.months.treatment.SD_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.after.6.months.treatment.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.after.6.months.treatment.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.after.6.months.treatment.SD_23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.after.treatment.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.after.treatment.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.after.treatment.SD_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.Baseline.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.Baseline.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADL.Baseline.SD_27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.after.treatment.(MMSE).6.months.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.after.treatment.(MMSE).6.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.after.treatment.(MMSE).6.months.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.after.treatment.(MMSE).Baseline.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.after.treatment.(MMSE).Baseline.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.after.treatment.(MMSE).Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.at.8.weeks.(MMSE).8.weeks.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.at.8.weeks.(MMSE).8.weeks.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.at.8.weeks.(MMSE).8.weeks.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.at.8.weeks.(MMSE).Baseline.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.at.8.weeks.(MMSE).Baseline.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognition.at.8.weeks.(MMSE).Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.after.12.months.treatment.mean.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.after.12.months.treatment.N_309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.after.12.months.treatment.SD_310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.after.6.months.treatment.mean.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.after.6.months.treatment.N_318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.after.6.months.treatment.SD_319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.After.intervention.(12.months.after.the.start.of.intervention).SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.After.intervention.(12.months.after.the.start.of.intervention).Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.after.treatment.mean.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.after.treatment.N_324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.after.treatment.SD_325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.Baseline.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.Baseline.Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.Baseline.mean.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.Baseline.N_348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.Baseline.SD_349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.one.year.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.one.year.Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.After.six.months.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.After.six.months.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.After.six.months.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.Baseline.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.Baseline.N.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE.Baseline.SD.1</t>
   </si>
   <si>
     <t xml:space="preserve">Wang 2010b</t>
@@ -1682,7 +1742,7 @@
     <t xml:space="preserve">12</t>
   </si>
   <si>
-    <t xml:space="preserve">Home care as usual for a year</t>
+    <t xml:space="preserve">Home care as usual for a year </t>
   </si>
   <si>
     <t xml:space="preserve">Home care guidance</t>
@@ -1709,7 +1769,7 @@
     <t xml:space="preserve">3.88</t>
   </si>
   <si>
-    <t xml:space="preserve">Community comprehensive intervention for a year</t>
+    <t xml:space="preserve">Community comprehensive intervention for a year </t>
   </si>
   <si>
     <t xml:space="preserve">Phone contact weekly, Home visit monthly, for 1 year, covering the following 4 components: 1) Health Education, 2) Basic personal care, 3) Psycho-emotional support, 4) Rehabilitation training guide. "干预组开展全面、 综合的社区护理。健康知识宣教 社区护理人员根据 AD 患者及家属健康知识需求， 定期开展知识讲座， 发放 AD 患者及照顾者健康教育和康复指导手册， 并详细讲解， 使其理解掌握， 能够简单复述宣教内容； 每周电话访问 1 次， 倾听患者及家属的问题， 建立良好的护患关系， 取得患者信任； 每个月家庭访视 1 次， 现场进行健康教育宣传及护理技术指导， 为期 1 年。基础生活护理 ① 基础护理： 实施 “无缝医疗保健”［3］，社区护理人员与家属共同讨论确定患者在家中适合的照料方式。 给予患者细心的呵护， 安排合理的作息时间， 保证良好的睡眠质量； 保持皮肤清洁， 衣物洁净， 注意保暖， 预防皮肤及肺部等各系统的感染； 按时服药， 促进疾病恢复； 根据身体状况， 做适当的户外运动， 锻炼身体， 增强体质。 ② 安全护理：家里地面不宜过于光滑， 必要时在盥洗室等处安扶手， 防止患者 跌 倒； 行动困难患者如厕、 洗浴要有人陪伴， 以 防 意 外 发生； 家中锐器物品、 药品妥善放置， 避免患者自伤或误服； 易走失的患者， 随身携带与家人联系的卡片， 避免单独外出， 防止 丢 失 迷 路。 ③ 饮 食 护 理： 一日三餐定时定量， 饥 饱 适 宜，膳 食 搭 配 合 理， 以清淡营养丰富为主， 多 食 豆 类、 奶 类、 瘦肉、 蔬菜、 海鲜、 粗纤维等食物， 保证优质蛋白质、 多不饱和脂肪酸及维生素等营养素的摄取。心理情感支持 全面评估患者， 根据其性格特征， 采取个性化护理， 充分体现 “以人为本”。 定期为患者做心理情感咨询， 了解患者的心理情绪状态， 减少患者因情绪异常引起行为问题的发生。 鼓励患者参加力所能及的家庭社会活动， 如看书、 读报、 听广播、 种花、 下棋、 打球、 参加社区老人联谊会等， 以 分 散 注 意 力， 排 遣 不 良 情 绪， 增 加 交 流， 提 高 沟 通 能力， 使其感受到生活的乐趣及自身价值， 促进心理健康。 指导照顾者掌握与老年痴呆患者交流的方法， 用理解、 宽容， 诚恳的态度对待病人， 耐心听取病人的诉说， 细心观察患者的情绪变化， 尽量满足其合理要求； 成立社区老年痴呆患者照顾者病友会， 提供照顾者之间分享照顾技巧的途径， 同时有助于减轻照顾者的照顾感受压力。康 复 训 练 指 导 ① 益 智 训 练： 减 缓 记 忆、 智 能 衰 退，指导家属要经常提醒患者日期、 时间、 地址、 家中电话号码等信息， 鼓励患者对往事的回忆， 要不厌其烦， 帮助其强化近期记忆和激发远期记忆。 让患者做一些简单的数字排列和运算，识图， 折纸等活动， 每日不少于 30 min。 组织患者参加适宜的集体活动， 增强其自信心， 促进计算， 判断， 思维， 理解等认知能力及语言能力的恢复。 ② 日常生活能力训练： 根据患者自理能力， 选择力所能及的生活内容进行训练。 自理能力较好的患者， 尽量让其自己完成做饭、 吃饭、 穿衣、 洗漱、 洗澡、打扫房间等日常生活， 四肢关节经常活动能够保持手脚灵活，促进血液循环； 自理能力较差的患者， 家属协助其完成复杂的生活活动， 并做好肢体功能康复训练。"</t>
@@ -1718,91 +1778,292 @@
     <t xml:space="preserve">Multicomponent: i) non-pharmcol, ii) Interv for carers</t>
   </si>
   <si>
-    <t xml:space="preserve">Wang 2012e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mutual support group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"The caregivers were recruited from a list of people with dementia attending one of two dementia resources and respite care centers in Guangzhou, Guangdong Province of mainland China. The resource center provided daytime physical care, self-care and skills training for clients, respite care, social and recreational activi-ties, and care-giving resources to about 3,000 clients with dementia, and their family members. The cli-ents with dementia were received to this center from mainly three sources, including: a regional psychiat-ric center, two psychiatric outpatient departments, and Social Security and Welfare Department of The Government."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9% (18-30yr);   41% (31-50yr);      23.1% (51-70yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peer-led mutual support group sessions, 1.5 hours every two weeks over a 24-week period, in addition to usual care</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"The peer-led mutual support group met bi-weekly, for a total of 12 1.5-hour sessions. All group sessions mainly consisted of information giving, sharing and discussion, psychological support, and problem solving; and a group protocol was spe-cifi cally designed for this study, based on evidence from other mutual support group intervention studies (Almberg et al., 1997; Fung &amp; Chien 2002; Toseland et al., 1989). Seven major themes of fam-ily support groups formed the basis for group members’ interactions and purposive activities in each session, including: (1) information about cli-ent’s condition; (2) development of group as a sup-port system; (3) emotional impact of care-giving; (4) learning about self-care; (5) improvement of interpersonal relationships; (6) establishing sup-port outside the group; and (7) improvement of home care skills. The protocol of the mutual sup-port group is presented in Table 1.To foster the use of problem-solving strategy within the group, at least one group members shared personal care-giving problems with other members in each session and these problems were worked on using a six-step model suggested by Zarit, Orr, and Zarit (1985). These six steps consisted of defi ning the problem, generation of alternatives, examining and evaluating each alternative, cognitive rehearsal of action plan, execution of the plan as homework, and evaluation of agreed outcomes.An advanced practice psychiatric nurse, who had more than 5 years of experience in dementia care and community mental health services and had experienced group facilitation, was chosen as facilitator for the supportive group. This nurse attended a 2-day training workshop organized by the research team on facilitation of a mutual sup-port group before the study was started. During the 24-week group intervention, the audio-taped group sessions were reviewed by the facilitator, together with the research team, to monitor treat-ment integrity, adherence to the protocol and any questions from group members.One to two peer leaders, elected by the group members, agreed to coordinate and plan the group sessions with the facilitator’s consultation, as suggested by Chien et al. (2006) and Toseland et al. (1989). The elected leaders were experienced in family and dementia care and received three 4-hour training sessions on planning and leading a mutual support group, using the protocol."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Routine care group (control)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3% (18-30yr);    43.6% (31-50yr);    23.1% (51.70yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conventional family services provided by dementia centers, including medical consultation, financial and social services advice, educational talks on dementia care, and referals and advice on medical and social services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"The control group received the conventional family services provided by the dementia centers. Similar to the other big cities in Guangdong and other Provinces of mainland China, the services included: (1) medical consultation of client and advice to family on client’s illness condition,  treatment plan and effects of med-ications provided on monthly basis by two visiting doctors; (2) advice and referrals of fi nancial aids and social welfare services provided by a social worker; (3) educational talk or seminars in dementia care conducted by registered general nurses; and (4) refer-rals and advices on medical and social services by the center staff. In other developing cities and sub-urban or remote areas, there is not any dementia care cen-ter and the only health care service that those fami-lies can obtain is the medical consultation by visiting doctors and their referrals to hospital care whenever necessary.Participants in the control group were informed about community supporting ser-vices for dementia care and referral to appropri-ate agencies for respite could be obtained from staff in the dementia center. After post-test, the research assistant asked them whether they would like to participate in a mutual support group spe-cifi cally organized for them."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28</t>
+    <t xml:space="preserve">TAN 2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">control group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Third Peoplel's Hospital of Foshan City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes （Intervention was implemented among carer, but outcomes were measured among patients）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no any intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervention group (Carer training)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"文盲1l例，小学22例，初中18例，高中以上9例"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The caregivers of observation groups were taught of AD disease nowledge，daily care，
+safe care knowledge，training and rehabilitation training guidance to improve their nursing skills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1．2．1对观察组照顾者的干预
+1．2．1．1 对照顾者进行AD相关护理知识和技巧的训练，内容
+包括：①AD患者的分期和常见的表现，让照顾者了解AD患者
+病情的发展。②日常生活护理。③AD患者安全护理，针对患者常
+见的走失、跌倒、自我伤害、意外受伤等安全问题对照顾者进行相
+关知识指导。④训练AD患者的康复技巧，根据AD患者的分期进
+行认图、物品分类、计算力、理解力和记忆力等方面的训练。⑤照
+顾者心理指导。尊重AD患者的人格、隐私，接纳痴呆老人的怪异
+言行，鼓励照顾者寻求邻居、朋友、同事的帮助和心理支持，主动
+利用社会支持，缓解照顾压力。
+1．2．1．2 课题组护士电话随访1次／周，家访2次／月。我们给
+照顾者留下咨询电话，随时帮助照顾者解决AD患者出现的问
+题。每季度去社区举办健康教育讲座1次，并现场指导照顾者对
+AD患者的康复训练，了解照顾者反馈的信息、有针对性调整讲
+课内容，提高培训效果。
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He 2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3R therapy treatment (Reminiscence, Reality Orientation, Remotivation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combination of structured psychosocial interventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean years of schooling = 10.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">individual intervention 30 min twice weekly + group intervention 60 min once weekly + family intervention 5~15min 3 times weekly for 6 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"3R 治疗具体方法如下。
+1．2．1方式采用个别干预、小组干预和家庭干预
+相结合的方式。a．个别干预：对门诊患者可采取约
+见方式；对住院患者，在病房内完成。每周2次，每
+次30 rain。b．小组干预：每周固定时问、地点进行。
+每周1次，每次60 rain。c．家庭干预：对照料者或密
+切接触者进行培训，印发训练小册子，在家中至少提
+供每周3次、每次5～15 min训练；电话追踪干预进
+行情况。
+1．2．2内容a．往事回忆：每个月1个主题来激发
+患者过去的回忆。包括：童年回忆；年轻时的经历；
+重大历史事件；名人；怀旧歌曲；老电影；悲伤的回
+忆；重要口子；喜爱的地方；喜爱的食物；我的家庭；
+我的成就。借助图片、旧照片、歌曲、电影、报纸等激
+发患者对往事的回忆，鼓励他们谈论与这些往事有
+关的经历和体验。b．现实定向：告知患者对自身疾
+病的正确认识；环境记忆的训练，如让患者说出家庭
+住址、周围特别的建筑物和路口、具体的回家路线
+等。小组干预时，通过他人介绍或自我介绍或现实
+定向板的方式让患者认清每一位参与者的姓名和身
+份、小组活动的地点、FI期和时间；随身小本记录生
+活计划，内容是何时、何地、干何事。c．再激发：训练
+者根据患者情况提出患者感兴趣的题目，鼓励患者
+进行讨论和参与，可让患者自述近年来亲身经历的
+大事，尤其是最高兴和最重要的事情，鼓励患者完整
+地表述，并结合目前热点民生、时事问题，加以讨论；
+小组干预时采用成语接龙等游戏方式、讲故事或手
+指、颈部运动操等形式。
+"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-pharmacological</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conventional therapy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean years of schooling =9.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"对照组给予常规治疗"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conventional therapy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SU 2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprehensive nursing intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No info. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 primary school ,9 middle school and 2 bachelor degree </t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psychological care, emotional care cognitive care, daily care, home safety  and care after the discharge from hospital for 14 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"1.2.1 心理护理 鼓励家属多陪伴患者,加强与患者的交流, 可一起参加社会或家庭活动D 尊重患者,以诚恳的态度对待患 者,鼓励患者战胜疾病,以增强患者信心D 针对患者不同病情, 有计划地与患者交谈,消除患者的顾虑,培养乐观情绪,使患者 以较好的心理状态配合治疗D 1.2.2 情感护理 针对患者焦虑情绪,在护理时应保持病房环 境的舒适性,在适当的时间放一些轻松愉悦的音乐:针对患者抑 郁倾述,应耐心倾听患者的倾述,不强迫患者做不愿意的事,以 鼓励为主,引导患者进行适当的运动,如散步等:针对易激动情 绪,应积极分析原因,安慰患者,避免语言刺激,鼓励患者做锻 炼,以放松心情:针对淡漠情绪,可增加病房内物品摆放,比如患 者感兴趣的物品,鼓励患者加强与他人的交流D 1.2.3 认知护理 对记忆的训练:念一串数字,让患者复述,逐 渐增加难度,增强患者的瞬时记忆:让患者看数件物品后数分 钟,让患者回忆刚刚所看到的物品,以增强短时记忆D 对定向力 的训练:开始让患者记忆一些特别的日期~时间等,如生日~节 日,让患者尝试记忆亲人~护士~医生的姓名:对回忆的训练:让 患者看对其意义较大的物品,使患者回忆往事:对分析能力的训 练:让患者对物品进行分类:对口语的训练:给患者讲述一段故 事,让患者回答一些简单的问题,或者简单概括故事的情节D 1.2.4 生活护理 给予患者自我照顾的机会,对患者进行生活 能力训练,如洗漱~穿脱衣~进餐等,鼓励患者尽量自理,如完全 不能自理,设专人护理,注意翻身拍背,按摩等,防止褥疮~感染等并发症D 对药物的发放,应按时按顿,指导患者将药物全部服 下,对有幻觉的患者,应耐心劝说,详细解释D 患者认知障碍严 重时,常出现白天休息,夜间吵闹,应保持夜间病房安静,入睡前 可予温水泡脚,对伴有严重睡眠障碍者,应给予药物帮助入睡D 1.2.5 安全护理 增强病房的安全性和舒适性,对有空间~时 间定向力障碍的患者,要求有专人陪护,防止走失D 对有行动不 便的患者,增加相应的设施,如座便器~扶手等D 1.2.6 出院健康指导 老年痴呆尚无有效的治疗,以预防为 主,关键是早发现~早治疗,延缓大脑细胞更加广泛和不可逆转 的退变,以控制病情的进展,防止并发症的发生,延长生命,提高 生活质量D 护理人员对患者和家属进行相关知识培训,提高主 动性,调动积极性,共同完成护理计划D 鼓励患者家属出院后多 陪伴患者,如散步~聊天,或参加一些学习和力所能及的社会家 庭活动D 给予多方面的帮助,使其消除孤独寂寞感,感受家庭的 温馨和生活的快乐D 嘱家属保持联系,指导家属参与家庭护理, 定时电话或者上门指导患者家属护理的技巧和质疑事项"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multicomponent (心理护理, 情感护理, 认知护理,  生活护理, 安全护理, 出院健康指导)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 primary school ,10 middle school and 3 bachelor degree </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Routine caring for 14 days (Control)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">常规护理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Routine caring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JIANG 2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对照组</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conventional therapy with Piracetam and Donepezil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"按医嘱进行脑复康，多奈哌齐 等药物治疗，康复护理干预期间药物剂量不变。 "</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multicomponent (Conventional therapy + Pharmaceutical)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">研究组 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.309999999999999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conventional therapy with Piracetam and Donepezil + whole course rehabilitafion nursing intervention including cognitive intervention，memory intervention，behaviour intervention，psychological intervention，safety intervention，community family nursing intervention，etc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"按医嘱进行脑复康，多奈哌齐 等药物治疗，康复护理干预期间药物剂量不变。 "研究组于入院第2天开始，根据本院编制的《老年痴呆全程康复护理规程》进行全程康复护理干预。 内容包括：①组织与管理：成立由专家、责任医生、责任护士、 护工组成的AD全程康复护理指导小组，小组成员负责制订 AD患者个性化全程康复护理计划，并负责组织实施。②健 康教育：针对AD患者的健康问题和照顾者对健康教育知识 的需求，每周进行相关老年性痴呆健康教育。③认知干预：干 预患者分析、综合、推理、判断和计算的能力，主要方法为3R 护理即Reminiscence(回忆往事)、Reality(现实定向)和 Remotivation(记忆再激发)。主要包括计算能力训练(如计算 家庭每月食品费、水电费、电话费、医疗费等开支，再算半年和 全年费用等)、数字排列训练(如扑克牌打乱后再让患者按顺 序排列等)、分类法训练(如给患者一张写有40种物品名称 的清单，让患者进行归类)等，每天训练三次。④记忆干预： 每天帮助患者记忆住所的环境、周围的人和物，最近进行的一 些活动等。⑤语言训练：要求患者叙述每天周围发生的事件、 家庭情况、新闻故事，让患者多交流，每天至少三次，防止出现 语言障碍。⑥行为干预：根据患者功能障碍情况，从13常生活 的穿衣、饮食、住房、用厕、出行等开始，并从患者的日常生活、 文体活动或一些轻的劳动过程中选出一些能使患者感兴趣并 有助于恢复功能和技能的活动，并按要求进行训练，帮助维持 或恢复功能。根据患者状况确定训练时间。⑦心理干预：每 天根据患者出现焦虑和抑郁等负性情绪的特点，采用安慰、鼓励、暗示以及听音乐、看幽默剧等方法对患者及照顾者进行心 理干预。同时鼓励患者与家人、亲友交往，从思想上、情感上 尽可能沟通，以减少患者的内心痛苦、孤独感、失望感、自罪自 责感。⑧用药指导：指导和督促患者按医嘱科学用药。⑨安 全干预：营造一个舒适、安全的住院环境及家居环境，防止出 现并发症和各种意外事故(如摔倒、骨折、走失、火灾、自杀自 残等)发生。⑩社区一家庭护理干预：患者在出院后，进行家庭 跟踪随访护理干预，每月为患者及照顾者进行讲课，每2周上 门随访1次，每周电话随访1次，了解患者的康复治疗情况， 提出相关指导意见。 "</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multicomponent intervention (Conventional therapy +  non-pharmacological)</t>
   </si>
   <si>
     <t xml:space="preserve">Wang 2014a</t>
   </si>
   <si>
-    <t xml:space="preserve">control group</t>
-  </si>
-  <si>
     <t xml:space="preserve">retried cadre's sanitarium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSE</t>
   </si>
   <si>
     <t xml:space="preserve">14.12</t>
@@ -1833,6 +2094,9 @@
     <t xml:space="preserve">44.53</t>
   </si>
   <si>
+    <t xml:space="preserve">7.56</t>
+  </si>
+  <si>
     <t xml:space="preserve">38.95</t>
   </si>
   <si>
@@ -1873,6 +2137,232 @@
   </si>
   <si>
     <t xml:space="preserve">5.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yang 2017a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Info. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular medicine and Psychological Health Promotion for 12 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"只给予药物治疗 和一般的心理健康知识宣传（即指通过各类媒体、各种方 式开展的心理健康知识宣传，如心理健康知识的宣传板 报、宣传册、进社区的心理卫生知识讲座、心理健康义 诊等） "</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicine + Psychological Health Promotion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">干预组</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community-based interventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8800000000000008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean: 11.06 year; SD: 6.30 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicine, Psychosocial and non-pharmacy in-home intervention for 12 months </t>
+  </si>
+  <si>
+    <t xml:space="preserve">"1.2.1 家庭医疗工作模式 精神科医师上门服务同时整 合多学科团队成员（疾控精神卫生分中心工作人员、心理 治疗师、康复治疗师、老年护理师等） ，对照料者、社区 家庭医生、社会工作者等进行痴呆卫生宣教，利用社区的 家庭医生制工作模式，争取各居委会和社区卫生服务中心 的支持，同时对患者和照料者实施心理社会干预。 1.2.2 心理社会干预内容 ①对痴呆照料者培训，内容包 括什么是痴呆及 BPSD，其疾病进程的一般规律，有效的 治疗方法和时机，护理要点、护理技巧和注意事项，患者 生活环境的布置，同患者交流的技巧等，以提高患者的服 药依从性，减少并发症，并接受照料者的倾诉，指导其放 松，加强心理支持和辅导。对患者灵活采用行为干预，如 日常生活能力训练、音乐疗法、怀旧和人生回顾、记忆训 练等 [2-3]，并调整其居住环境的布置。②在患者急性期每周 家访，调整药物，听取照料者及家属的意见，提出合理建 议。③待病情稳定后，采取每周电话随访、每月上门随访 方式，针对存在严重疾病或行动不便者给予更高程度的关 注，适当增加探访频率以降低其风险概率。 1.2.3 干预形式 ①对社区相关人员进行培训，发放相关 宣传材料500 份。②建立老年痴呆家庭的自助互助小组， 互相分享讨论心得体会，举办家庭成员活动。③开展每半 年 1 次的相关人员座谈协调会，讨论干预过程中遇到的问 题及解决方案。"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicine +Psychosocial intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lok 2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nursing home in the city of Konya, Turkey.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.829999999999998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Literate: 20.0%; Primary education: 36.6%; High school and above: 43.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control (no intervention)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control group was not administered any intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reminiscence therapy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.260000000000002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Literate: 16.6%; Primary education: 40.0%; High school and above: 43.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reminiscence therapy in groups of 6 people, 1 session (60 minutes) per week for 8 weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Reminiscence therapy was applied once a week and lasted for 8 weeks.Every session took 60 minutes. Individuals in the intervention group were divided in five groups. Each group consisted of six people. Ses-sions included the titles of the first meeting, childhood experiences,festivals, memorable travelled places, favorite foods, important histor-ical terms, achievements, and music of the term. The patients were encouraged to remember their important experiences, positive experi-ences, and achievements in the past by reminiscence therapy, and they were allowed to interactively share them verbally with group members. Group leader provided a supportive approach to ensure interaction and share between the participants and to make them feel-ing stronger, valuable, and self‐confident. Materials triggering th ememory, such as photographs, household goods, other reminiscent of the past, music of old times, and foods, were used."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline.For.studies.in.carers.only:.Part-time.working.(percent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.(WHOQOL-BREF).Post-test.(1.month.after.24.week.intervention).mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.(WHOQOL-BREF).Post-test.(1.month.after.24.week.intervention).N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.(WHOQOL-BREF).Post-test.(1.month.after.24.week.intervention).SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.(WHOQOL-BREF).Pre-test.mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.(WHOQOL-BREF).Pre-test.N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caregiver.quality.of.life.(WHOQOL-BREF).Pre-test.SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wang 2012e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutual support group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"The caregivers were recruited from a list of people with dementia attending one of two dementia resources and respite care centers in Guangzhou, Guangdong Province of mainland China. The resource center provided daytime physical care, self-care and skills training for clients, respite care, social and recreational activi-ties, and care-giving resources to about 3,000 clients with dementia, and their family members. The cli-ents with dementia were received to this center from mainly three sources, including: a regional psychiat-ric center, two psychiatric outpatient departments, and Social Security and Welfare Department of The Government."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9% (18-30yr);   41% (31-50yr);      23.1% (51-70yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer-led mutual support group sessions, 1.5 hours every two weeks over a 24-week period, in addition to usual care</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"The peer-led mutual support group met bi-weekly, for a total of 12 1.5-hour sessions. All group sessions mainly consisted of information giving, sharing and discussion, psychological support, and problem solving; and a group protocol was spe-cifi cally designed for this study, based on evidence from other mutual support group intervention studies (Almberg et al., 1997; Fung &amp; Chien 2002; Toseland et al., 1989). Seven major themes of fam-ily support groups formed the basis for group members’ interactions and purposive activities in each session, including: (1) information about cli-ent’s condition; (2) development of group as a sup-port system; (3) emotional impact of care-giving; (4) learning about self-care; (5) improvement of interpersonal relationships; (6) establishing sup-port outside the group; and (7) improvement of home care skills. The protocol of the mutual sup-port group is presented in Table 1.To foster the use of problem-solving strategy within the group, at least one group members shared personal care-giving problems with other members in each session and these problems were worked on using a six-step model suggested by Zarit, Orr, and Zarit (1985). These six steps consisted of defi ning the problem, generation of alternatives, examining and evaluating each alternative, cognitive rehearsal of action plan, execution of the plan as homework, and evaluation of agreed outcomes.An advanced practice psychiatric nurse, who had more than 5 years of experience in dementia care and community mental health services and had experienced group facilitation, was chosen as facilitator for the supportive group. This nurse attended a 2-day training workshop organized by the research team on facilitation of a mutual sup-port group before the study was started. During the 24-week group intervention, the audio-taped group sessions were reviewed by the facilitator, together with the research team, to monitor treat-ment integrity, adherence to the protocol and any questions from group members.One to two peer leaders, elected by the group members, agreed to coordinate and plan the group sessions with the facilitator’s consultation, as suggested by Chien et al. (2006) and Toseland et al. (1989). The elected leaders were experienced in family and dementia care and received three 4-hour training sessions on planning and leading a mutual support group, using the protocol."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Routine care group (control)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3% (18-30yr);    43.6% (31-50yr);    23.1% (51.70yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conventional family services provided by dementia centers, including medical consultation, financial and social services advice, educational talks on dementia care, and referals and advice on medical and social services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"The control group received the conventional family services provided by the dementia centers. Similar to the other big cities in Guangdong and other Provinces of mainland China, the services included: (1) medical consultation of client and advice to family on client’s illness condition,  treatment plan and effects of med-ications provided on monthly basis by two visiting doctors; (2) advice and referrals of fi nancial aids and social welfare services provided by a social worker; (3) educational talk or seminars in dementia care conducted by registered general nurses; and (4) refer-rals and advices on medical and social services by the center staff. In other developing cities and sub-urban or remote areas, there is not any dementia care cen-ter and the only health care service that those fami-lies can obtain is the medical consultation by visiting doctors and their referrals to hospital care whenever necessary.Participants in the control group were informed about community supporting ser-vices for dementia care and referral to appropri-ate agencies for respite could be obtained from staff in the dementia center. After post-test, the research assistant asked them whether they would like to participate in a mutual support group spe-cifi cally organized for them."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28</t>
   </si>
 </sst>
 </file>
@@ -7889,255 +8379,507 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
+        <v>478</v>
+      </c>
+      <c r="M1" t="s">
+        <v>479</v>
+      </c>
+      <c r="N1" t="s">
+        <v>480</v>
+      </c>
+      <c r="O1" t="s">
+        <v>481</v>
+      </c>
+      <c r="P1" t="s">
+        <v>482</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>483</v>
+      </c>
+      <c r="R1" t="s">
+        <v>484</v>
+      </c>
+      <c r="S1" t="s">
+        <v>485</v>
+      </c>
+      <c r="T1" t="s">
+        <v>486</v>
+      </c>
+      <c r="U1" t="s">
+        <v>487</v>
+      </c>
+      <c r="V1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="W1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="X1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Y1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Z1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="AA1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="AB1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="AC1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AD1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AE1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AF1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI1" t="s">
         <v>25</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AJ1" t="s">
+        <v>488</v>
+      </c>
+      <c r="AK1" t="s">
         <v>26</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AL1" t="s">
+        <v>489</v>
+      </c>
+      <c r="AM1" t="s">
         <v>28</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AN1" t="s">
+        <v>490</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>491</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>492</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>493</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>494</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>495</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>496</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>497</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>498</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>499</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>500</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>501</v>
+      </c>
+      <c r="AZ1" t="s">
         <v>29</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="BA1" t="s">
         <v>30</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="BB1" t="s">
         <v>31</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="BC1" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="BD1" t="s">
         <v>33</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="BE1" t="s">
         <v>34</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="BF1" t="s">
         <v>35</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="BG1" t="s">
         <v>36</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="BH1" t="s">
         <v>37</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="BI1" t="s">
+        <v>42</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>43</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>44</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>45</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>46</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>47</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>48</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>49</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BX1" t="s">
         <v>75</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="BY1" t="s">
         <v>76</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="BZ1" t="s">
         <v>77</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="CA1" t="s">
         <v>78</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="CB1" t="s">
         <v>79</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="CC1" t="s">
         <v>80</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="CD1" t="s">
         <v>81</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="CE1" t="s">
         <v>82</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="CF1" t="s">
         <v>83</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="CG1" t="s">
         <v>84</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="CH1" t="s">
         <v>85</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="CI1" t="s">
         <v>86</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="CJ1" t="s">
         <v>87</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="CK1" t="s">
         <v>88</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="CL1" t="s">
         <v>89</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="CM1" t="s">
         <v>90</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="CN1" t="s">
         <v>91</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="CO1" t="s">
         <v>92</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="CP1" t="s">
         <v>93</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="CQ1" t="s">
         <v>94</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="CR1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CX1" t="s">
         <v>107</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="CY1" t="s">
         <v>108</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="CZ1" t="s">
         <v>109</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="DA1" t="s">
         <v>110</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="DB1" t="s">
         <v>111</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="DC1" t="s">
         <v>112</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="DD1" t="s">
         <v>113</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="DE1" t="s">
         <v>114</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="DF1" t="s">
         <v>115</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="DG1" t="s">
         <v>116</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="DH1" t="s">
         <v>117</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="DI1" t="s">
         <v>118</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="DJ1" t="s">
         <v>119</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="DK1" t="s">
         <v>120</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="DL1" t="s">
         <v>121</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="DM1" t="s">
         <v>122</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="DN1" t="s">
+        <v>502</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>503</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>504</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>505</v>
+      </c>
+      <c r="DR1" t="s">
+        <v>506</v>
+      </c>
+      <c r="DS1" t="s">
+        <v>507</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>508</v>
+      </c>
+      <c r="DU1" t="s">
+        <v>509</v>
+      </c>
+      <c r="DV1" t="s">
+        <v>510</v>
+      </c>
+      <c r="DW1" t="s">
+        <v>511</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>512</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>513</v>
+      </c>
+      <c r="DZ1" t="s">
         <v>123</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="EA1" t="s">
         <v>124</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="EB1" t="s">
         <v>125</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="EC1" t="s">
         <v>126</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="ED1" t="s">
         <v>127</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="EE1" t="s">
         <v>128</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="EF1" t="s">
         <v>129</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="EG1" t="s">
         <v>130</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="EH1" t="s">
         <v>131</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="EI1" t="s">
+        <v>514</v>
+      </c>
+      <c r="EJ1" t="s">
+        <v>515</v>
+      </c>
+      <c r="EK1" t="s">
+        <v>516</v>
+      </c>
+      <c r="EL1" t="s">
+        <v>517</v>
+      </c>
+      <c r="EM1" t="s">
+        <v>518</v>
+      </c>
+      <c r="EN1" t="s">
+        <v>519</v>
+      </c>
+      <c r="EO1" t="s">
+        <v>520</v>
+      </c>
+      <c r="EP1" t="s">
+        <v>521</v>
+      </c>
+      <c r="EQ1" t="s">
+        <v>522</v>
+      </c>
+      <c r="ER1" t="s">
+        <v>523</v>
+      </c>
+      <c r="ES1" t="s">
+        <v>524</v>
+      </c>
+      <c r="ET1" t="s">
+        <v>525</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>526</v>
+      </c>
+      <c r="EV1" t="s">
+        <v>527</v>
+      </c>
+      <c r="EW1" t="s">
+        <v>528</v>
+      </c>
+      <c r="EX1" t="s">
+        <v>529</v>
+      </c>
+      <c r="EY1" t="s">
+        <v>530</v>
+      </c>
+      <c r="EZ1" t="s">
+        <v>531</v>
+      </c>
+      <c r="FA1" t="s">
+        <v>532</v>
+      </c>
+      <c r="FB1" t="s">
+        <v>533</v>
+      </c>
+      <c r="FC1" t="s">
+        <v>534</v>
+      </c>
+      <c r="FD1" t="s">
+        <v>535</v>
+      </c>
+      <c r="FE1" t="s">
+        <v>536</v>
+      </c>
+      <c r="FF1" t="s">
+        <v>537</v>
+      </c>
+      <c r="FG1" t="s">
         <v>140</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="FH1" t="s">
         <v>141</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="FI1" t="s">
         <v>142</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="FJ1" t="s">
         <v>143</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="FK1" t="s">
         <v>144</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="FL1" t="s">
         <v>145</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="FM1" t="s">
         <v>146</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="FN1" t="s">
         <v>147</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="FO1" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="B2" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C2" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="E2" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="F2" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="G2" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="H2" t="s">
         <v>169</v>
@@ -8146,166 +8888,114 @@
         <v>170</v>
       </c>
       <c r="J2" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="K2" t="s">
         <v>172</v>
       </c>
-      <c r="L2" t="s">
-        <v>173</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2" t="s">
         <v>174</v>
       </c>
-      <c r="N2" t="s">
-        <v>173</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="W2" t="s">
         <v>175</v>
       </c>
-      <c r="P2" t="s">
+      <c r="X2" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z2" t="s">
         <v>174</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="AA2" t="s">
         <v>175</v>
       </c>
-      <c r="R2" t="s">
-        <v>235</v>
-      </c>
-      <c r="S2" t="s">
-        <v>236</v>
-      </c>
-      <c r="T2" t="s">
-        <v>237</v>
-      </c>
-      <c r="U2" t="s">
-        <v>238</v>
-      </c>
-      <c r="V2" t="s">
-        <v>239</v>
-      </c>
-      <c r="W2" t="s">
-        <v>240</v>
-      </c>
-      <c r="X2" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-      <c r="AF2"/>
+      <c r="AB2" t="s">
+        <v>202</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>204</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>205</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>13.44</v>
+      </c>
       <c r="AG2"/>
-      <c r="AH2" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-0.84</v>
+      <c r="AH2"/>
+      <c r="AI2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AJ2"/>
+      <c r="AK2" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL2"/>
+      <c r="AM2" t="s">
+        <v>182</v>
+      </c>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2" t="s">
+        <v>207</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>208</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>209</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>210</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>211</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>212</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>208</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>213</v>
       </c>
       <c r="BR2"/>
       <c r="BS2"/>
@@ -8325,28 +9015,112 @@
       <c r="CG2"/>
       <c r="CH2"/>
       <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="B3" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C3" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>215</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="F3" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="G3" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="H3" t="s">
         <v>169</v>
@@ -8355,113 +9129,115 @@
         <v>170</v>
       </c>
       <c r="J3" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="K3" t="s">
         <v>172</v>
       </c>
-      <c r="L3" t="s">
-        <v>173</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3" t="s">
         <v>174</v>
       </c>
-      <c r="N3" t="s">
-        <v>173</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="W3" t="s">
         <v>175</v>
       </c>
-      <c r="P3" t="s">
+      <c r="X3" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z3" t="s">
         <v>174</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="AA3" t="s">
         <v>175</v>
       </c>
-      <c r="R3" t="s">
-        <v>242</v>
-      </c>
-      <c r="S3" t="s">
-        <v>243</v>
-      </c>
-      <c r="T3" t="s">
-        <v>244</v>
-      </c>
-      <c r="U3" t="s">
-        <v>245</v>
-      </c>
-      <c r="V3" t="s">
-        <v>246</v>
-      </c>
-      <c r="W3" t="s">
-        <v>247</v>
-      </c>
-      <c r="X3" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
-      <c r="AD3"/>
-      <c r="AE3"/>
-      <c r="AF3"/>
+      <c r="AB3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>218</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>220</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>14</v>
+      </c>
       <c r="AG3"/>
       <c r="AH3"/>
-      <c r="AI3" t="n">
-        <v>29</v>
+      <c r="AI3" t="s">
+        <v>221</v>
       </c>
       <c r="AJ3"/>
-      <c r="AK3"/>
+      <c r="AK3" t="s">
+        <v>222</v>
+      </c>
       <c r="AL3"/>
-      <c r="AM3" t="n">
-        <v>29</v>
+      <c r="AM3" t="s">
+        <v>223</v>
       </c>
       <c r="AN3"/>
       <c r="AO3"/>
       <c r="AP3"/>
-      <c r="AQ3" t="n">
-        <v>29</v>
-      </c>
+      <c r="AQ3"/>
       <c r="AR3"/>
       <c r="AS3"/>
       <c r="AT3"/>
-      <c r="AU3" t="n">
-        <v>29</v>
-      </c>
+      <c r="AU3"/>
       <c r="AV3"/>
       <c r="AW3"/>
       <c r="AX3"/>
-      <c r="AY3" t="n">
-        <v>29</v>
-      </c>
+      <c r="AY3"/>
       <c r="AZ3"/>
       <c r="BA3"/>
       <c r="BB3"/>
-      <c r="BC3" t="n">
-        <v>29</v>
-      </c>
+      <c r="BC3"/>
       <c r="BD3"/>
       <c r="BE3"/>
       <c r="BF3"/>
-      <c r="BG3" t="n">
-        <v>29</v>
-      </c>
+      <c r="BG3"/>
       <c r="BH3"/>
-      <c r="BI3"/>
-      <c r="BJ3"/>
-      <c r="BK3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BL3"/>
-      <c r="BM3"/>
-      <c r="BN3"/>
-      <c r="BO3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BP3"/>
-      <c r="BQ3"/>
+      <c r="BI3" t="s">
+        <v>224</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>208</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>225</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>226</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>227</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>228</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>208</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>229</v>
+      </c>
       <c r="BR3"/>
       <c r="BS3"/>
       <c r="BT3"/>
@@ -8480,16 +9256,100 @@
       <c r="CG3"/>
       <c r="CH3"/>
       <c r="CI3"/>
+      <c r="CJ3"/>
+      <c r="CK3"/>
+      <c r="CL3"/>
+      <c r="CM3"/>
+      <c r="CN3"/>
+      <c r="CO3"/>
+      <c r="CP3"/>
+      <c r="CQ3"/>
+      <c r="CR3"/>
+      <c r="CS3"/>
+      <c r="CT3"/>
+      <c r="CU3"/>
+      <c r="CV3"/>
+      <c r="CW3"/>
+      <c r="CX3"/>
+      <c r="CY3"/>
+      <c r="CZ3"/>
+      <c r="DA3"/>
+      <c r="DB3"/>
+      <c r="DC3"/>
+      <c r="DD3"/>
+      <c r="DE3"/>
+      <c r="DF3"/>
+      <c r="DG3"/>
+      <c r="DH3"/>
+      <c r="DI3"/>
+      <c r="DJ3"/>
+      <c r="DK3"/>
+      <c r="DL3"/>
+      <c r="DM3"/>
+      <c r="DN3"/>
+      <c r="DO3"/>
+      <c r="DP3"/>
+      <c r="DQ3"/>
+      <c r="DR3"/>
+      <c r="DS3"/>
+      <c r="DT3"/>
+      <c r="DU3"/>
+      <c r="DV3"/>
+      <c r="DW3"/>
+      <c r="DX3"/>
+      <c r="DY3"/>
+      <c r="DZ3"/>
+      <c r="EA3"/>
+      <c r="EB3"/>
+      <c r="EC3"/>
+      <c r="ED3"/>
+      <c r="EE3"/>
+      <c r="EF3"/>
+      <c r="EG3"/>
+      <c r="EH3"/>
+      <c r="EI3"/>
+      <c r="EJ3"/>
+      <c r="EK3"/>
+      <c r="EL3"/>
+      <c r="EM3"/>
+      <c r="EN3"/>
+      <c r="EO3"/>
+      <c r="EP3"/>
+      <c r="EQ3"/>
+      <c r="ER3"/>
+      <c r="ES3"/>
+      <c r="ET3"/>
+      <c r="EU3"/>
+      <c r="EV3"/>
+      <c r="EW3"/>
+      <c r="EX3"/>
+      <c r="EY3"/>
+      <c r="EZ3"/>
+      <c r="FA3"/>
+      <c r="FB3"/>
+      <c r="FC3"/>
+      <c r="FD3"/>
+      <c r="FE3"/>
+      <c r="FF3"/>
+      <c r="FG3"/>
+      <c r="FH3"/>
+      <c r="FI3"/>
+      <c r="FJ3"/>
+      <c r="FK3"/>
+      <c r="FL3"/>
+      <c r="FM3"/>
+      <c r="FN3"/>
+      <c r="FO3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>276</v>
+        <v>538</v>
       </c>
       <c r="B4" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>539</v>
       </c>
       <c r="D4" t="s">
         <v>166</v>
@@ -8498,10 +9358,10 @@
         <v>166</v>
       </c>
       <c r="F4" t="s">
-        <v>199</v>
+        <v>417</v>
       </c>
       <c r="G4" t="s">
-        <v>278</v>
+        <v>540</v>
       </c>
       <c r="H4" t="s">
         <v>253</v>
@@ -8510,75 +9370,101 @@
         <v>170</v>
       </c>
       <c r="J4" t="s">
-        <v>201</v>
-      </c>
-      <c r="K4"/>
+        <v>171</v>
+      </c>
+      <c r="K4" t="s">
+        <v>541</v>
+      </c>
       <c r="L4" t="s">
-        <v>175</v>
+        <v>542</v>
       </c>
       <c r="M4" t="s">
-        <v>175</v>
+        <v>543</v>
       </c>
       <c r="N4" t="s">
-        <v>175</v>
+        <v>544</v>
       </c>
       <c r="O4" t="s">
-        <v>175</v>
+        <v>545</v>
       </c>
       <c r="P4" t="s">
-        <v>174</v>
+        <v>546</v>
       </c>
       <c r="Q4" t="s">
-        <v>175</v>
-      </c>
-      <c r="R4"/>
-      <c r="S4"/>
+        <v>547</v>
+      </c>
+      <c r="R4" t="s">
+        <v>545</v>
+      </c>
+      <c r="S4" t="s">
+        <v>548</v>
+      </c>
       <c r="T4"/>
       <c r="U4" t="s">
-        <v>279</v>
-      </c>
-      <c r="V4"/>
-      <c r="W4"/>
-      <c r="X4"/>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4"/>
-      <c r="AB4" t="s">
-        <v>280</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>281</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>282</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>283</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>281</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>284</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="V4" t="s">
+        <v>174</v>
+      </c>
+      <c r="W4" t="s">
+        <v>175</v>
+      </c>
+      <c r="X4" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
+      <c r="AF4" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="AG4"/>
       <c r="AH4"/>
-      <c r="AI4"/>
+      <c r="AI4" t="s">
+        <v>550</v>
+      </c>
       <c r="AJ4"/>
-      <c r="AK4"/>
+      <c r="AK4" t="s">
+        <v>551</v>
+      </c>
       <c r="AL4"/>
-      <c r="AM4"/>
+      <c r="AM4" t="s">
+        <v>552</v>
+      </c>
       <c r="AN4"/>
       <c r="AO4"/>
       <c r="AP4"/>
       <c r="AQ4"/>
       <c r="AR4"/>
       <c r="AS4"/>
-      <c r="AT4"/>
-      <c r="AU4"/>
-      <c r="AV4"/>
-      <c r="AW4"/>
-      <c r="AX4"/>
-      <c r="AY4"/>
+      <c r="AT4" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AZ4"/>
       <c r="BA4"/>
       <c r="BB4"/>
@@ -8600,67 +9486,139 @@
       <c r="BR4"/>
       <c r="BS4"/>
       <c r="BT4"/>
-      <c r="BU4" t="s">
-        <v>285</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>281</v>
-      </c>
-      <c r="BW4" t="s">
-        <v>286</v>
-      </c>
-      <c r="BX4" t="s">
-        <v>287</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>281</v>
-      </c>
-      <c r="BZ4" t="s">
-        <v>288</v>
-      </c>
+      <c r="BU4"/>
+      <c r="BV4"/>
+      <c r="BW4"/>
+      <c r="BX4"/>
+      <c r="BY4"/>
+      <c r="BZ4"/>
       <c r="CA4"/>
       <c r="CB4"/>
       <c r="CC4"/>
-      <c r="CD4" t="s">
-        <v>289</v>
-      </c>
-      <c r="CE4" t="s">
-        <v>281</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>290</v>
-      </c>
-      <c r="CG4" t="s">
-        <v>291</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>281</v>
-      </c>
-      <c r="CI4" t="s">
-        <v>292</v>
-      </c>
+      <c r="CD4"/>
+      <c r="CE4"/>
+      <c r="CF4"/>
+      <c r="CG4"/>
+      <c r="CH4"/>
+      <c r="CI4"/>
+      <c r="CJ4"/>
+      <c r="CK4"/>
+      <c r="CL4"/>
+      <c r="CM4"/>
+      <c r="CN4"/>
+      <c r="CO4"/>
+      <c r="CP4"/>
+      <c r="CQ4"/>
+      <c r="CR4"/>
+      <c r="CS4"/>
+      <c r="CT4"/>
+      <c r="CU4"/>
+      <c r="CV4"/>
+      <c r="CW4"/>
+      <c r="CX4"/>
+      <c r="CY4"/>
+      <c r="CZ4"/>
+      <c r="DA4"/>
+      <c r="DB4"/>
+      <c r="DC4"/>
+      <c r="DD4"/>
+      <c r="DE4"/>
+      <c r="DF4"/>
+      <c r="DG4"/>
+      <c r="DH4"/>
+      <c r="DI4"/>
+      <c r="DJ4"/>
+      <c r="DK4"/>
+      <c r="DL4"/>
+      <c r="DM4"/>
+      <c r="DN4"/>
+      <c r="DO4"/>
+      <c r="DP4"/>
+      <c r="DQ4"/>
+      <c r="DR4"/>
+      <c r="DS4"/>
+      <c r="DT4"/>
+      <c r="DU4"/>
+      <c r="DV4"/>
+      <c r="DW4"/>
+      <c r="DX4"/>
+      <c r="DY4"/>
+      <c r="DZ4"/>
+      <c r="EA4"/>
+      <c r="EB4"/>
+      <c r="EC4"/>
+      <c r="ED4"/>
+      <c r="EE4"/>
+      <c r="EF4"/>
+      <c r="EG4"/>
+      <c r="EH4"/>
+      <c r="EI4"/>
+      <c r="EJ4"/>
+      <c r="EK4"/>
+      <c r="EL4"/>
+      <c r="EM4"/>
+      <c r="EN4"/>
+      <c r="EO4"/>
+      <c r="EP4"/>
+      <c r="EQ4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>40</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="ET4"/>
+      <c r="EU4"/>
+      <c r="EV4" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>40</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="EY4"/>
+      <c r="EZ4"/>
+      <c r="FA4"/>
+      <c r="FB4"/>
+      <c r="FC4"/>
+      <c r="FD4"/>
+      <c r="FE4"/>
+      <c r="FF4"/>
+      <c r="FG4"/>
+      <c r="FH4"/>
+      <c r="FI4"/>
+      <c r="FJ4"/>
+      <c r="FK4"/>
+      <c r="FL4"/>
+      <c r="FM4"/>
+      <c r="FN4"/>
+      <c r="FO4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>276</v>
+        <v>538</v>
       </c>
       <c r="B5" t="n">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C5" t="s">
-        <v>293</v>
+        <v>231</v>
       </c>
       <c r="D5" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
       <c r="E5" t="s">
-        <v>250</v>
+        <v>554</v>
       </c>
       <c r="F5" t="s">
-        <v>199</v>
+        <v>417</v>
       </c>
       <c r="G5" t="s">
-        <v>278</v>
+        <v>540</v>
       </c>
       <c r="H5" t="s">
         <v>253</v>
@@ -8669,81 +9627,101 @@
         <v>170</v>
       </c>
       <c r="J5" t="s">
-        <v>201</v>
-      </c>
-      <c r="K5"/>
+        <v>171</v>
+      </c>
+      <c r="K5" t="s">
+        <v>541</v>
+      </c>
       <c r="L5" t="s">
-        <v>175</v>
+        <v>542</v>
       </c>
       <c r="M5" t="s">
-        <v>175</v>
+        <v>543</v>
       </c>
       <c r="N5" t="s">
-        <v>175</v>
+        <v>555</v>
       </c>
       <c r="O5" t="s">
-        <v>175</v>
+        <v>545</v>
       </c>
       <c r="P5" t="s">
-        <v>174</v>
+        <v>556</v>
       </c>
       <c r="Q5" t="s">
-        <v>175</v>
-      </c>
-      <c r="R5"/>
-      <c r="S5"/>
+        <v>557</v>
+      </c>
+      <c r="R5" t="s">
+        <v>545</v>
+      </c>
+      <c r="S5" t="s">
+        <v>558</v>
+      </c>
       <c r="T5"/>
       <c r="U5" t="s">
-        <v>279</v>
-      </c>
-      <c r="V5"/>
-      <c r="W5"/>
-      <c r="X5"/>
+        <v>549</v>
+      </c>
+      <c r="V5" t="s">
+        <v>174</v>
+      </c>
+      <c r="W5" t="s">
+        <v>175</v>
+      </c>
+      <c r="X5" t="s">
+        <v>173</v>
+      </c>
       <c r="Y5" t="s">
-        <v>294</v>
+        <v>175</v>
       </c>
       <c r="Z5" t="s">
-        <v>281</v>
+        <v>174</v>
       </c>
       <c r="AA5" t="s">
-        <v>295</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>296</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>281</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>297</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>298</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>281</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>299</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
+      <c r="AF5" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="AG5"/>
       <c r="AH5"/>
-      <c r="AI5"/>
+      <c r="AI5" t="s">
+        <v>559</v>
+      </c>
       <c r="AJ5"/>
-      <c r="AK5"/>
+      <c r="AK5" t="s">
+        <v>560</v>
+      </c>
       <c r="AL5"/>
-      <c r="AM5"/>
+      <c r="AM5" t="s">
+        <v>561</v>
+      </c>
       <c r="AN5"/>
       <c r="AO5"/>
       <c r="AP5"/>
       <c r="AQ5"/>
       <c r="AR5"/>
       <c r="AS5"/>
-      <c r="AT5"/>
-      <c r="AU5"/>
-      <c r="AV5"/>
-      <c r="AW5"/>
-      <c r="AX5"/>
-      <c r="AY5"/>
+      <c r="AT5" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.9</v>
+      </c>
       <c r="AZ5"/>
       <c r="BA5"/>
       <c r="BB5"/>
@@ -8762,60 +9740,5154 @@
       <c r="BO5"/>
       <c r="BP5"/>
       <c r="BQ5"/>
-      <c r="BR5" t="s">
+      <c r="BR5"/>
+      <c r="BS5"/>
+      <c r="BT5"/>
+      <c r="BU5"/>
+      <c r="BV5"/>
+      <c r="BW5"/>
+      <c r="BX5"/>
+      <c r="BY5"/>
+      <c r="BZ5"/>
+      <c r="CA5"/>
+      <c r="CB5"/>
+      <c r="CC5"/>
+      <c r="CD5"/>
+      <c r="CE5"/>
+      <c r="CF5"/>
+      <c r="CG5"/>
+      <c r="CH5"/>
+      <c r="CI5"/>
+      <c r="CJ5"/>
+      <c r="CK5"/>
+      <c r="CL5"/>
+      <c r="CM5"/>
+      <c r="CN5"/>
+      <c r="CO5"/>
+      <c r="CP5"/>
+      <c r="CQ5"/>
+      <c r="CR5"/>
+      <c r="CS5"/>
+      <c r="CT5"/>
+      <c r="CU5"/>
+      <c r="CV5"/>
+      <c r="CW5"/>
+      <c r="CX5"/>
+      <c r="CY5"/>
+      <c r="CZ5"/>
+      <c r="DA5"/>
+      <c r="DB5"/>
+      <c r="DC5"/>
+      <c r="DD5"/>
+      <c r="DE5"/>
+      <c r="DF5"/>
+      <c r="DG5"/>
+      <c r="DH5"/>
+      <c r="DI5"/>
+      <c r="DJ5"/>
+      <c r="DK5"/>
+      <c r="DL5"/>
+      <c r="DM5"/>
+      <c r="DN5"/>
+      <c r="DO5"/>
+      <c r="DP5"/>
+      <c r="DQ5"/>
+      <c r="DR5"/>
+      <c r="DS5"/>
+      <c r="DT5"/>
+      <c r="DU5"/>
+      <c r="DV5"/>
+      <c r="DW5"/>
+      <c r="DX5"/>
+      <c r="DY5"/>
+      <c r="DZ5"/>
+      <c r="EA5"/>
+      <c r="EB5"/>
+      <c r="EC5"/>
+      <c r="ED5"/>
+      <c r="EE5"/>
+      <c r="EF5"/>
+      <c r="EG5"/>
+      <c r="EH5"/>
+      <c r="EI5"/>
+      <c r="EJ5"/>
+      <c r="EK5"/>
+      <c r="EL5"/>
+      <c r="EM5"/>
+      <c r="EN5"/>
+      <c r="EO5"/>
+      <c r="EP5"/>
+      <c r="EQ5" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>40</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="ET5"/>
+      <c r="EU5"/>
+      <c r="EV5" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>40</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="EY5"/>
+      <c r="EZ5"/>
+      <c r="FA5"/>
+      <c r="FB5"/>
+      <c r="FC5"/>
+      <c r="FD5"/>
+      <c r="FE5"/>
+      <c r="FF5"/>
+      <c r="FG5"/>
+      <c r="FH5"/>
+      <c r="FI5"/>
+      <c r="FJ5"/>
+      <c r="FK5"/>
+      <c r="FL5"/>
+      <c r="FM5"/>
+      <c r="FN5"/>
+      <c r="FO5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>562</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C6" t="s">
+        <v>563</v>
+      </c>
+      <c r="D6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" t="s">
+        <v>417</v>
+      </c>
+      <c r="G6" t="s">
+        <v>564</v>
+      </c>
+      <c r="H6" t="s">
+        <v>253</v>
+      </c>
+      <c r="I6" t="s">
+        <v>170</v>
+      </c>
+      <c r="J6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K6" t="s">
+        <v>565</v>
+      </c>
+      <c r="L6" t="s">
+        <v>566</v>
+      </c>
+      <c r="M6" t="s">
+        <v>543</v>
+      </c>
+      <c r="N6" t="s">
+        <v>567</v>
+      </c>
+      <c r="O6" t="s">
+        <v>568</v>
+      </c>
+      <c r="P6" t="s">
+        <v>569</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>570</v>
+      </c>
+      <c r="R6" t="s">
+        <v>568</v>
+      </c>
+      <c r="S6" t="s">
+        <v>571</v>
+      </c>
+      <c r="T6" t="s">
+        <v>549</v>
+      </c>
+      <c r="U6"/>
+      <c r="V6" t="s">
+        <v>174</v>
+      </c>
+      <c r="W6" t="s">
+        <v>174</v>
+      </c>
+      <c r="X6" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
+      <c r="AF6" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="AG6"/>
+      <c r="AH6"/>
+      <c r="AI6" t="s">
+        <v>572</v>
+      </c>
+      <c r="AJ6"/>
+      <c r="AK6"/>
+      <c r="AL6"/>
+      <c r="AM6"/>
+      <c r="AN6"/>
+      <c r="AO6"/>
+      <c r="AP6"/>
+      <c r="AQ6"/>
+      <c r="AR6"/>
+      <c r="AS6"/>
+      <c r="AT6"/>
+      <c r="AU6"/>
+      <c r="AV6"/>
+      <c r="AW6"/>
+      <c r="AX6"/>
+      <c r="AY6"/>
+      <c r="AZ6"/>
+      <c r="BA6"/>
+      <c r="BB6"/>
+      <c r="BC6"/>
+      <c r="BD6"/>
+      <c r="BE6"/>
+      <c r="BF6"/>
+      <c r="BG6"/>
+      <c r="BH6"/>
+      <c r="BI6"/>
+      <c r="BJ6"/>
+      <c r="BK6"/>
+      <c r="BL6"/>
+      <c r="BM6"/>
+      <c r="BN6"/>
+      <c r="BO6"/>
+      <c r="BP6"/>
+      <c r="BQ6"/>
+      <c r="BR6"/>
+      <c r="BS6"/>
+      <c r="BT6"/>
+      <c r="BU6"/>
+      <c r="BV6"/>
+      <c r="BW6"/>
+      <c r="BX6"/>
+      <c r="BY6"/>
+      <c r="BZ6"/>
+      <c r="CA6"/>
+      <c r="CB6"/>
+      <c r="CC6"/>
+      <c r="CD6"/>
+      <c r="CE6"/>
+      <c r="CF6"/>
+      <c r="CG6"/>
+      <c r="CH6"/>
+      <c r="CI6"/>
+      <c r="CJ6"/>
+      <c r="CK6"/>
+      <c r="CL6"/>
+      <c r="CM6"/>
+      <c r="CN6"/>
+      <c r="CO6"/>
+      <c r="CP6"/>
+      <c r="CQ6"/>
+      <c r="CR6"/>
+      <c r="CS6"/>
+      <c r="CT6"/>
+      <c r="CU6"/>
+      <c r="CV6"/>
+      <c r="CW6"/>
+      <c r="CX6"/>
+      <c r="CY6"/>
+      <c r="CZ6"/>
+      <c r="DA6"/>
+      <c r="DB6"/>
+      <c r="DC6"/>
+      <c r="DD6"/>
+      <c r="DE6"/>
+      <c r="DF6"/>
+      <c r="DG6"/>
+      <c r="DH6"/>
+      <c r="DI6"/>
+      <c r="DJ6"/>
+      <c r="DK6"/>
+      <c r="DL6"/>
+      <c r="DM6"/>
+      <c r="DN6"/>
+      <c r="DO6"/>
+      <c r="DP6"/>
+      <c r="DQ6"/>
+      <c r="DR6"/>
+      <c r="DS6"/>
+      <c r="DT6"/>
+      <c r="DU6"/>
+      <c r="DV6"/>
+      <c r="DW6"/>
+      <c r="DX6"/>
+      <c r="DY6"/>
+      <c r="DZ6"/>
+      <c r="EA6"/>
+      <c r="EB6"/>
+      <c r="EC6"/>
+      <c r="ED6"/>
+      <c r="EE6"/>
+      <c r="EF6"/>
+      <c r="EG6"/>
+      <c r="EH6"/>
+      <c r="EI6"/>
+      <c r="EJ6"/>
+      <c r="EK6"/>
+      <c r="EL6"/>
+      <c r="EM6"/>
+      <c r="EN6"/>
+      <c r="EO6"/>
+      <c r="EP6"/>
+      <c r="EQ6" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>60</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="ET6"/>
+      <c r="EU6"/>
+      <c r="EV6" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>60</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="EY6"/>
+      <c r="EZ6"/>
+      <c r="FA6"/>
+      <c r="FB6"/>
+      <c r="FC6"/>
+      <c r="FD6"/>
+      <c r="FE6"/>
+      <c r="FF6"/>
+      <c r="FG6"/>
+      <c r="FH6"/>
+      <c r="FI6"/>
+      <c r="FJ6"/>
+      <c r="FK6"/>
+      <c r="FL6"/>
+      <c r="FM6"/>
+      <c r="FN6"/>
+      <c r="FO6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>562</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C7" t="s">
+        <v>573</v>
+      </c>
+      <c r="D7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G7" t="s">
+        <v>564</v>
+      </c>
+      <c r="H7" t="s">
+        <v>253</v>
+      </c>
+      <c r="I7" t="s">
+        <v>170</v>
+      </c>
+      <c r="J7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K7" t="s">
+        <v>565</v>
+      </c>
+      <c r="L7" t="s">
+        <v>566</v>
+      </c>
+      <c r="M7" t="s">
+        <v>543</v>
+      </c>
+      <c r="N7" t="s">
+        <v>325</v>
+      </c>
+      <c r="O7" t="s">
+        <v>568</v>
+      </c>
+      <c r="P7" t="s">
+        <v>574</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>575</v>
+      </c>
+      <c r="R7" t="s">
+        <v>568</v>
+      </c>
+      <c r="S7" t="s">
+        <v>546</v>
+      </c>
+      <c r="T7" t="s">
+        <v>549</v>
+      </c>
+      <c r="U7"/>
+      <c r="V7" t="s">
+        <v>174</v>
+      </c>
+      <c r="W7" t="s">
+        <v>174</v>
+      </c>
+      <c r="X7" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>576</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>449</v>
+      </c>
+      <c r="AD7"/>
+      <c r="AE7"/>
+      <c r="AF7" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AG7"/>
+      <c r="AH7"/>
+      <c r="AI7" t="s">
+        <v>577</v>
+      </c>
+      <c r="AJ7"/>
+      <c r="AK7" t="s">
+        <v>578</v>
+      </c>
+      <c r="AL7"/>
+      <c r="AM7" t="s">
+        <v>552</v>
+      </c>
+      <c r="AN7"/>
+      <c r="AO7"/>
+      <c r="AP7"/>
+      <c r="AQ7"/>
+      <c r="AR7"/>
+      <c r="AS7"/>
+      <c r="AT7"/>
+      <c r="AU7"/>
+      <c r="AV7"/>
+      <c r="AW7"/>
+      <c r="AX7"/>
+      <c r="AY7"/>
+      <c r="AZ7"/>
+      <c r="BA7"/>
+      <c r="BB7"/>
+      <c r="BC7"/>
+      <c r="BD7"/>
+      <c r="BE7"/>
+      <c r="BF7"/>
+      <c r="BG7"/>
+      <c r="BH7"/>
+      <c r="BI7"/>
+      <c r="BJ7"/>
+      <c r="BK7"/>
+      <c r="BL7"/>
+      <c r="BM7"/>
+      <c r="BN7"/>
+      <c r="BO7"/>
+      <c r="BP7"/>
+      <c r="BQ7"/>
+      <c r="BR7"/>
+      <c r="BS7"/>
+      <c r="BT7"/>
+      <c r="BU7"/>
+      <c r="BV7"/>
+      <c r="BW7"/>
+      <c r="BX7"/>
+      <c r="BY7"/>
+      <c r="BZ7"/>
+      <c r="CA7"/>
+      <c r="CB7"/>
+      <c r="CC7"/>
+      <c r="CD7"/>
+      <c r="CE7"/>
+      <c r="CF7"/>
+      <c r="CG7"/>
+      <c r="CH7"/>
+      <c r="CI7"/>
+      <c r="CJ7"/>
+      <c r="CK7"/>
+      <c r="CL7"/>
+      <c r="CM7"/>
+      <c r="CN7"/>
+      <c r="CO7"/>
+      <c r="CP7"/>
+      <c r="CQ7"/>
+      <c r="CR7"/>
+      <c r="CS7"/>
+      <c r="CT7"/>
+      <c r="CU7"/>
+      <c r="CV7"/>
+      <c r="CW7"/>
+      <c r="CX7"/>
+      <c r="CY7"/>
+      <c r="CZ7"/>
+      <c r="DA7"/>
+      <c r="DB7"/>
+      <c r="DC7"/>
+      <c r="DD7"/>
+      <c r="DE7"/>
+      <c r="DF7"/>
+      <c r="DG7"/>
+      <c r="DH7"/>
+      <c r="DI7"/>
+      <c r="DJ7"/>
+      <c r="DK7"/>
+      <c r="DL7"/>
+      <c r="DM7"/>
+      <c r="DN7"/>
+      <c r="DO7"/>
+      <c r="DP7"/>
+      <c r="DQ7"/>
+      <c r="DR7"/>
+      <c r="DS7"/>
+      <c r="DT7"/>
+      <c r="DU7"/>
+      <c r="DV7"/>
+      <c r="DW7"/>
+      <c r="DX7"/>
+      <c r="DY7"/>
+      <c r="DZ7"/>
+      <c r="EA7"/>
+      <c r="EB7"/>
+      <c r="EC7"/>
+      <c r="ED7"/>
+      <c r="EE7"/>
+      <c r="EF7"/>
+      <c r="EG7"/>
+      <c r="EH7"/>
+      <c r="EI7"/>
+      <c r="EJ7"/>
+      <c r="EK7"/>
+      <c r="EL7"/>
+      <c r="EM7"/>
+      <c r="EN7"/>
+      <c r="EO7"/>
+      <c r="EP7"/>
+      <c r="EQ7" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>60</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="ET7"/>
+      <c r="EU7"/>
+      <c r="EV7" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>60</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="EY7"/>
+      <c r="EZ7"/>
+      <c r="FA7"/>
+      <c r="FB7"/>
+      <c r="FC7"/>
+      <c r="FD7"/>
+      <c r="FE7"/>
+      <c r="FF7"/>
+      <c r="FG7"/>
+      <c r="FH7"/>
+      <c r="FI7"/>
+      <c r="FJ7"/>
+      <c r="FK7"/>
+      <c r="FL7"/>
+      <c r="FM7"/>
+      <c r="FN7"/>
+      <c r="FO7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" t="s">
+        <v>185</v>
+      </c>
+      <c r="E8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F8" t="s">
+        <v>232</v>
+      </c>
+      <c r="G8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H8" t="s">
+        <v>169</v>
+      </c>
+      <c r="I8" t="s">
+        <v>170</v>
+      </c>
+      <c r="J8" t="s">
+        <v>234</v>
+      </c>
+      <c r="K8" t="s">
+        <v>172</v>
+      </c>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8" t="s">
+        <v>173</v>
+      </c>
+      <c r="W8" t="s">
+        <v>174</v>
+      </c>
+      <c r="X8" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>235</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>236</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>237</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>238</v>
+      </c>
+      <c r="AF8"/>
+      <c r="AG8"/>
+      <c r="AH8"/>
+      <c r="AI8" t="s">
+        <v>239</v>
+      </c>
+      <c r="AJ8"/>
+      <c r="AK8" t="s">
+        <v>240</v>
+      </c>
+      <c r="AL8"/>
+      <c r="AM8" t="s">
+        <v>193</v>
+      </c>
+      <c r="AN8"/>
+      <c r="AO8"/>
+      <c r="AP8"/>
+      <c r="AQ8"/>
+      <c r="AR8"/>
+      <c r="AS8"/>
+      <c r="AT8"/>
+      <c r="AU8"/>
+      <c r="AV8"/>
+      <c r="AW8"/>
+      <c r="AX8"/>
+      <c r="AY8"/>
+      <c r="AZ8"/>
+      <c r="BA8"/>
+      <c r="BB8"/>
+      <c r="BC8"/>
+      <c r="BD8"/>
+      <c r="BE8"/>
+      <c r="BF8"/>
+      <c r="BG8"/>
+      <c r="BH8"/>
+      <c r="BI8"/>
+      <c r="BJ8"/>
+      <c r="BK8"/>
+      <c r="BL8"/>
+      <c r="BM8"/>
+      <c r="BN8"/>
+      <c r="BO8"/>
+      <c r="BP8"/>
+      <c r="BQ8"/>
+      <c r="BR8"/>
+      <c r="BS8"/>
+      <c r="BT8"/>
+      <c r="BU8"/>
+      <c r="BV8"/>
+      <c r="BW8"/>
+      <c r="BX8" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>27</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>27</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>27</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>27</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="CR8"/>
+      <c r="CS8"/>
+      <c r="CT8"/>
+      <c r="CU8"/>
+      <c r="CV8"/>
+      <c r="CW8"/>
+      <c r="CX8" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>27</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>27</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>27</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="DN8"/>
+      <c r="DO8"/>
+      <c r="DP8"/>
+      <c r="DQ8"/>
+      <c r="DR8"/>
+      <c r="DS8"/>
+      <c r="DT8"/>
+      <c r="DU8"/>
+      <c r="DV8"/>
+      <c r="DW8"/>
+      <c r="DX8"/>
+      <c r="DY8"/>
+      <c r="DZ8"/>
+      <c r="EA8"/>
+      <c r="EB8"/>
+      <c r="EC8"/>
+      <c r="ED8"/>
+      <c r="EE8"/>
+      <c r="EF8"/>
+      <c r="EG8"/>
+      <c r="EH8"/>
+      <c r="EI8"/>
+      <c r="EJ8"/>
+      <c r="EK8"/>
+      <c r="EL8"/>
+      <c r="EM8"/>
+      <c r="EN8"/>
+      <c r="EO8"/>
+      <c r="EP8"/>
+      <c r="EQ8"/>
+      <c r="ER8"/>
+      <c r="ES8"/>
+      <c r="ET8"/>
+      <c r="EU8"/>
+      <c r="EV8"/>
+      <c r="EW8"/>
+      <c r="EX8"/>
+      <c r="EY8"/>
+      <c r="EZ8"/>
+      <c r="FA8"/>
+      <c r="FB8"/>
+      <c r="FC8"/>
+      <c r="FD8"/>
+      <c r="FE8"/>
+      <c r="FF8"/>
+      <c r="FG8"/>
+      <c r="FH8"/>
+      <c r="FI8"/>
+      <c r="FJ8"/>
+      <c r="FK8"/>
+      <c r="FL8"/>
+      <c r="FM8"/>
+      <c r="FN8"/>
+      <c r="FO8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F9" t="s">
+        <v>232</v>
+      </c>
+      <c r="G9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H9" t="s">
+        <v>169</v>
+      </c>
+      <c r="I9" t="s">
+        <v>170</v>
+      </c>
+      <c r="J9" t="s">
+        <v>234</v>
+      </c>
+      <c r="K9" t="s">
+        <v>172</v>
+      </c>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9" t="s">
+        <v>173</v>
+      </c>
+      <c r="W9" t="s">
+        <v>174</v>
+      </c>
+      <c r="X9" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>243</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>245</v>
+      </c>
+      <c r="AF9"/>
+      <c r="AG9"/>
+      <c r="AH9"/>
+      <c r="AI9" t="s">
+        <v>246</v>
+      </c>
+      <c r="AJ9"/>
+      <c r="AK9" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL9"/>
+      <c r="AM9" t="s">
+        <v>182</v>
+      </c>
+      <c r="AN9"/>
+      <c r="AO9"/>
+      <c r="AP9"/>
+      <c r="AQ9"/>
+      <c r="AR9"/>
+      <c r="AS9"/>
+      <c r="AT9"/>
+      <c r="AU9"/>
+      <c r="AV9"/>
+      <c r="AW9"/>
+      <c r="AX9"/>
+      <c r="AY9"/>
+      <c r="AZ9"/>
+      <c r="BA9"/>
+      <c r="BB9"/>
+      <c r="BC9"/>
+      <c r="BD9"/>
+      <c r="BE9"/>
+      <c r="BF9"/>
+      <c r="BG9"/>
+      <c r="BH9"/>
+      <c r="BI9"/>
+      <c r="BJ9"/>
+      <c r="BK9"/>
+      <c r="BL9"/>
+      <c r="BM9"/>
+      <c r="BN9"/>
+      <c r="BO9"/>
+      <c r="BP9"/>
+      <c r="BQ9"/>
+      <c r="BR9"/>
+      <c r="BS9"/>
+      <c r="BT9"/>
+      <c r="BU9"/>
+      <c r="BV9"/>
+      <c r="BW9"/>
+      <c r="BX9"/>
+      <c r="BY9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BZ9"/>
+      <c r="CA9"/>
+      <c r="CB9"/>
+      <c r="CC9" t="n">
+        <v>29</v>
+      </c>
+      <c r="CD9"/>
+      <c r="CE9"/>
+      <c r="CF9"/>
+      <c r="CG9" t="n">
+        <v>29</v>
+      </c>
+      <c r="CH9"/>
+      <c r="CI9"/>
+      <c r="CJ9"/>
+      <c r="CK9" t="n">
+        <v>29</v>
+      </c>
+      <c r="CL9"/>
+      <c r="CM9"/>
+      <c r="CN9"/>
+      <c r="CO9" t="n">
+        <v>29</v>
+      </c>
+      <c r="CP9"/>
+      <c r="CQ9"/>
+      <c r="CR9"/>
+      <c r="CS9"/>
+      <c r="CT9"/>
+      <c r="CU9"/>
+      <c r="CV9"/>
+      <c r="CW9"/>
+      <c r="CX9"/>
+      <c r="CY9" t="n">
+        <v>29</v>
+      </c>
+      <c r="CZ9"/>
+      <c r="DA9"/>
+      <c r="DB9"/>
+      <c r="DC9" t="n">
+        <v>29</v>
+      </c>
+      <c r="DD9"/>
+      <c r="DE9"/>
+      <c r="DF9"/>
+      <c r="DG9" t="n">
+        <v>29</v>
+      </c>
+      <c r="DH9"/>
+      <c r="DI9"/>
+      <c r="DJ9"/>
+      <c r="DK9" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL9"/>
+      <c r="DM9"/>
+      <c r="DN9"/>
+      <c r="DO9"/>
+      <c r="DP9"/>
+      <c r="DQ9"/>
+      <c r="DR9"/>
+      <c r="DS9"/>
+      <c r="DT9"/>
+      <c r="DU9"/>
+      <c r="DV9"/>
+      <c r="DW9"/>
+      <c r="DX9"/>
+      <c r="DY9"/>
+      <c r="DZ9"/>
+      <c r="EA9"/>
+      <c r="EB9"/>
+      <c r="EC9"/>
+      <c r="ED9"/>
+      <c r="EE9"/>
+      <c r="EF9"/>
+      <c r="EG9"/>
+      <c r="EH9"/>
+      <c r="EI9"/>
+      <c r="EJ9"/>
+      <c r="EK9"/>
+      <c r="EL9"/>
+      <c r="EM9"/>
+      <c r="EN9"/>
+      <c r="EO9"/>
+      <c r="EP9"/>
+      <c r="EQ9"/>
+      <c r="ER9"/>
+      <c r="ES9"/>
+      <c r="ET9"/>
+      <c r="EU9"/>
+      <c r="EV9"/>
+      <c r="EW9"/>
+      <c r="EX9"/>
+      <c r="EY9"/>
+      <c r="EZ9"/>
+      <c r="FA9"/>
+      <c r="FB9"/>
+      <c r="FC9"/>
+      <c r="FD9"/>
+      <c r="FE9"/>
+      <c r="FF9"/>
+      <c r="FG9"/>
+      <c r="FH9"/>
+      <c r="FI9"/>
+      <c r="FJ9"/>
+      <c r="FK9"/>
+      <c r="FL9"/>
+      <c r="FM9"/>
+      <c r="FN9"/>
+      <c r="FO9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>579</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C10" t="s">
+        <v>580</v>
+      </c>
+      <c r="D10" t="s">
+        <v>461</v>
+      </c>
+      <c r="E10" t="s">
+        <v>581</v>
+      </c>
+      <c r="F10" t="s">
+        <v>417</v>
+      </c>
+      <c r="G10" t="s">
+        <v>582</v>
+      </c>
+      <c r="H10" t="s">
+        <v>253</v>
+      </c>
+      <c r="I10" t="s">
+        <v>170</v>
+      </c>
+      <c r="J10" t="s">
+        <v>171</v>
+      </c>
+      <c r="K10" t="s">
+        <v>541</v>
+      </c>
+      <c r="L10" t="s">
+        <v>566</v>
+      </c>
+      <c r="M10" t="s">
+        <v>543</v>
+      </c>
+      <c r="N10" t="s">
+        <v>583</v>
+      </c>
+      <c r="O10" t="s">
+        <v>322</v>
+      </c>
+      <c r="P10" t="s">
+        <v>584</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>585</v>
+      </c>
+      <c r="R10" t="s">
+        <v>322</v>
+      </c>
+      <c r="S10" t="s">
+        <v>586</v>
+      </c>
+      <c r="T10"/>
+      <c r="U10" t="s">
+        <v>587</v>
+      </c>
+      <c r="V10" t="s">
+        <v>174</v>
+      </c>
+      <c r="W10" t="s">
+        <v>174</v>
+      </c>
+      <c r="X10" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>588</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>589</v>
+      </c>
+      <c r="AD10"/>
+      <c r="AE10"/>
+      <c r="AF10" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AG10"/>
+      <c r="AH10"/>
+      <c r="AI10" t="s">
+        <v>590</v>
+      </c>
+      <c r="AJ10"/>
+      <c r="AK10" t="s">
+        <v>591</v>
+      </c>
+      <c r="AL10"/>
+      <c r="AM10" t="s">
+        <v>592</v>
+      </c>
+      <c r="AN10"/>
+      <c r="AO10"/>
+      <c r="AP10"/>
+      <c r="AQ10"/>
+      <c r="AR10"/>
+      <c r="AS10"/>
+      <c r="AT10"/>
+      <c r="AU10"/>
+      <c r="AV10"/>
+      <c r="AW10"/>
+      <c r="AX10"/>
+      <c r="AY10"/>
+      <c r="AZ10"/>
+      <c r="BA10"/>
+      <c r="BB10"/>
+      <c r="BC10"/>
+      <c r="BD10"/>
+      <c r="BE10"/>
+      <c r="BF10"/>
+      <c r="BG10"/>
+      <c r="BH10"/>
+      <c r="BI10"/>
+      <c r="BJ10"/>
+      <c r="BK10"/>
+      <c r="BL10"/>
+      <c r="BM10"/>
+      <c r="BN10"/>
+      <c r="BO10"/>
+      <c r="BP10"/>
+      <c r="BQ10"/>
+      <c r="BR10"/>
+      <c r="BS10"/>
+      <c r="BT10"/>
+      <c r="BU10"/>
+      <c r="BV10"/>
+      <c r="BW10"/>
+      <c r="BX10"/>
+      <c r="BY10"/>
+      <c r="BZ10"/>
+      <c r="CA10"/>
+      <c r="CB10"/>
+      <c r="CC10"/>
+      <c r="CD10"/>
+      <c r="CE10"/>
+      <c r="CF10"/>
+      <c r="CG10"/>
+      <c r="CH10"/>
+      <c r="CI10"/>
+      <c r="CJ10"/>
+      <c r="CK10"/>
+      <c r="CL10"/>
+      <c r="CM10"/>
+      <c r="CN10"/>
+      <c r="CO10"/>
+      <c r="CP10"/>
+      <c r="CQ10"/>
+      <c r="CR10"/>
+      <c r="CS10"/>
+      <c r="CT10"/>
+      <c r="CU10"/>
+      <c r="CV10"/>
+      <c r="CW10"/>
+      <c r="CX10"/>
+      <c r="CY10"/>
+      <c r="CZ10"/>
+      <c r="DA10"/>
+      <c r="DB10"/>
+      <c r="DC10"/>
+      <c r="DD10"/>
+      <c r="DE10"/>
+      <c r="DF10"/>
+      <c r="DG10"/>
+      <c r="DH10"/>
+      <c r="DI10"/>
+      <c r="DJ10"/>
+      <c r="DK10"/>
+      <c r="DL10"/>
+      <c r="DM10"/>
+      <c r="DN10" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>17</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DT10"/>
+      <c r="DU10"/>
+      <c r="DV10"/>
+      <c r="DW10"/>
+      <c r="DX10"/>
+      <c r="DY10"/>
+      <c r="DZ10"/>
+      <c r="EA10"/>
+      <c r="EB10"/>
+      <c r="EC10"/>
+      <c r="ED10"/>
+      <c r="EE10"/>
+      <c r="EF10"/>
+      <c r="EG10"/>
+      <c r="EH10"/>
+      <c r="EI10"/>
+      <c r="EJ10"/>
+      <c r="EK10"/>
+      <c r="EL10"/>
+      <c r="EM10"/>
+      <c r="EN10"/>
+      <c r="EO10"/>
+      <c r="EP10"/>
+      <c r="EQ10"/>
+      <c r="ER10"/>
+      <c r="ES10"/>
+      <c r="ET10"/>
+      <c r="EU10"/>
+      <c r="EV10"/>
+      <c r="EW10"/>
+      <c r="EX10"/>
+      <c r="EY10"/>
+      <c r="EZ10"/>
+      <c r="FA10"/>
+      <c r="FB10"/>
+      <c r="FC10"/>
+      <c r="FD10"/>
+      <c r="FE10"/>
+      <c r="FF10"/>
+      <c r="FG10"/>
+      <c r="FH10"/>
+      <c r="FI10"/>
+      <c r="FJ10"/>
+      <c r="FK10"/>
+      <c r="FL10"/>
+      <c r="FM10"/>
+      <c r="FN10"/>
+      <c r="FO10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>579</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C11" t="s">
+        <v>593</v>
+      </c>
+      <c r="D11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E11" t="s">
+        <v>166</v>
+      </c>
+      <c r="F11" t="s">
+        <v>417</v>
+      </c>
+      <c r="G11" t="s">
+        <v>582</v>
+      </c>
+      <c r="H11" t="s">
+        <v>253</v>
+      </c>
+      <c r="I11" t="s">
+        <v>170</v>
+      </c>
+      <c r="J11" t="s">
+        <v>171</v>
+      </c>
+      <c r="K11" t="s">
+        <v>541</v>
+      </c>
+      <c r="L11" t="s">
+        <v>566</v>
+      </c>
+      <c r="M11" t="s">
+        <v>543</v>
+      </c>
+      <c r="N11" t="s">
+        <v>594</v>
+      </c>
+      <c r="O11" t="s">
+        <v>322</v>
+      </c>
+      <c r="P11" t="s">
+        <v>595</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>596</v>
+      </c>
+      <c r="R11" t="s">
+        <v>322</v>
+      </c>
+      <c r="S11" t="s">
+        <v>597</v>
+      </c>
+      <c r="T11"/>
+      <c r="U11" t="s">
+        <v>587</v>
+      </c>
+      <c r="V11" t="s">
+        <v>174</v>
+      </c>
+      <c r="W11" t="s">
+        <v>174</v>
+      </c>
+      <c r="X11" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>598</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>599</v>
+      </c>
+      <c r="AD11"/>
+      <c r="AE11"/>
+      <c r="AF11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG11"/>
+      <c r="AH11"/>
+      <c r="AI11" t="s">
+        <v>593</v>
+      </c>
+      <c r="AJ11"/>
+      <c r="AK11" t="s">
+        <v>600</v>
+      </c>
+      <c r="AL11"/>
+      <c r="AM11" t="s">
+        <v>601</v>
+      </c>
+      <c r="AN11"/>
+      <c r="AO11"/>
+      <c r="AP11"/>
+      <c r="AQ11"/>
+      <c r="AR11"/>
+      <c r="AS11"/>
+      <c r="AT11"/>
+      <c r="AU11"/>
+      <c r="AV11"/>
+      <c r="AW11"/>
+      <c r="AX11"/>
+      <c r="AY11"/>
+      <c r="AZ11"/>
+      <c r="BA11"/>
+      <c r="BB11"/>
+      <c r="BC11"/>
+      <c r="BD11"/>
+      <c r="BE11"/>
+      <c r="BF11"/>
+      <c r="BG11"/>
+      <c r="BH11"/>
+      <c r="BI11"/>
+      <c r="BJ11"/>
+      <c r="BK11"/>
+      <c r="BL11"/>
+      <c r="BM11"/>
+      <c r="BN11"/>
+      <c r="BO11"/>
+      <c r="BP11"/>
+      <c r="BQ11"/>
+      <c r="BR11"/>
+      <c r="BS11"/>
+      <c r="BT11"/>
+      <c r="BU11"/>
+      <c r="BV11"/>
+      <c r="BW11"/>
+      <c r="BX11"/>
+      <c r="BY11"/>
+      <c r="BZ11"/>
+      <c r="CA11"/>
+      <c r="CB11"/>
+      <c r="CC11"/>
+      <c r="CD11"/>
+      <c r="CE11"/>
+      <c r="CF11"/>
+      <c r="CG11"/>
+      <c r="CH11"/>
+      <c r="CI11"/>
+      <c r="CJ11"/>
+      <c r="CK11"/>
+      <c r="CL11"/>
+      <c r="CM11"/>
+      <c r="CN11"/>
+      <c r="CO11"/>
+      <c r="CP11"/>
+      <c r="CQ11"/>
+      <c r="CR11"/>
+      <c r="CS11"/>
+      <c r="CT11"/>
+      <c r="CU11"/>
+      <c r="CV11"/>
+      <c r="CW11"/>
+      <c r="CX11"/>
+      <c r="CY11"/>
+      <c r="CZ11"/>
+      <c r="DA11"/>
+      <c r="DB11"/>
+      <c r="DC11"/>
+      <c r="DD11"/>
+      <c r="DE11"/>
+      <c r="DF11"/>
+      <c r="DG11"/>
+      <c r="DH11"/>
+      <c r="DI11"/>
+      <c r="DJ11"/>
+      <c r="DK11"/>
+      <c r="DL11"/>
+      <c r="DM11"/>
+      <c r="DN11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>19</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>17</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="DT11"/>
+      <c r="DU11"/>
+      <c r="DV11"/>
+      <c r="DW11"/>
+      <c r="DX11"/>
+      <c r="DY11"/>
+      <c r="DZ11"/>
+      <c r="EA11"/>
+      <c r="EB11"/>
+      <c r="EC11"/>
+      <c r="ED11"/>
+      <c r="EE11"/>
+      <c r="EF11"/>
+      <c r="EG11"/>
+      <c r="EH11"/>
+      <c r="EI11"/>
+      <c r="EJ11"/>
+      <c r="EK11"/>
+      <c r="EL11"/>
+      <c r="EM11"/>
+      <c r="EN11"/>
+      <c r="EO11"/>
+      <c r="EP11"/>
+      <c r="EQ11"/>
+      <c r="ER11"/>
+      <c r="ES11"/>
+      <c r="ET11"/>
+      <c r="EU11"/>
+      <c r="EV11"/>
+      <c r="EW11"/>
+      <c r="EX11"/>
+      <c r="EY11"/>
+      <c r="EZ11"/>
+      <c r="FA11"/>
+      <c r="FB11"/>
+      <c r="FC11"/>
+      <c r="FD11"/>
+      <c r="FE11"/>
+      <c r="FF11"/>
+      <c r="FG11"/>
+      <c r="FH11"/>
+      <c r="FI11"/>
+      <c r="FJ11"/>
+      <c r="FK11"/>
+      <c r="FL11"/>
+      <c r="FM11"/>
+      <c r="FN11"/>
+      <c r="FO11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>602</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C12" t="s">
+        <v>603</v>
+      </c>
+      <c r="D12" t="s">
+        <v>553</v>
+      </c>
+      <c r="E12" t="s">
+        <v>554</v>
+      </c>
+      <c r="F12" t="s">
+        <v>417</v>
+      </c>
+      <c r="G12" t="s">
+        <v>582</v>
+      </c>
+      <c r="H12" t="s">
+        <v>253</v>
+      </c>
+      <c r="I12" t="s">
+        <v>170</v>
+      </c>
+      <c r="J12" t="s">
+        <v>201</v>
+      </c>
+      <c r="K12" t="s">
+        <v>604</v>
+      </c>
+      <c r="L12" t="s">
+        <v>566</v>
+      </c>
+      <c r="M12" t="s">
+        <v>543</v>
+      </c>
+      <c r="N12" t="s">
+        <v>605</v>
+      </c>
+      <c r="O12" t="s">
+        <v>304</v>
+      </c>
+      <c r="P12" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>607</v>
+      </c>
+      <c r="R12" t="s">
+        <v>304</v>
+      </c>
+      <c r="S12" t="s">
         <v>300</v>
       </c>
-      <c r="BS5" t="s">
+      <c r="T12"/>
+      <c r="U12" t="s">
+        <v>587</v>
+      </c>
+      <c r="V12" t="s">
+        <v>174</v>
+      </c>
+      <c r="W12" t="s">
+        <v>174</v>
+      </c>
+      <c r="X12" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>608</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>609</v>
+      </c>
+      <c r="AD12"/>
+      <c r="AE12"/>
+      <c r="AF12" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="AG12"/>
+      <c r="AH12"/>
+      <c r="AI12"/>
+      <c r="AJ12" t="s">
+        <v>610</v>
+      </c>
+      <c r="AK12"/>
+      <c r="AL12" t="s">
+        <v>611</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>612</v>
+      </c>
+      <c r="AN12"/>
+      <c r="AO12"/>
+      <c r="AP12"/>
+      <c r="AQ12"/>
+      <c r="AR12"/>
+      <c r="AS12"/>
+      <c r="AT12"/>
+      <c r="AU12"/>
+      <c r="AV12"/>
+      <c r="AW12"/>
+      <c r="AX12"/>
+      <c r="AY12"/>
+      <c r="AZ12"/>
+      <c r="BA12"/>
+      <c r="BB12"/>
+      <c r="BC12"/>
+      <c r="BD12"/>
+      <c r="BE12"/>
+      <c r="BF12"/>
+      <c r="BG12"/>
+      <c r="BH12"/>
+      <c r="BI12"/>
+      <c r="BJ12"/>
+      <c r="BK12"/>
+      <c r="BL12"/>
+      <c r="BM12"/>
+      <c r="BN12"/>
+      <c r="BO12"/>
+      <c r="BP12"/>
+      <c r="BQ12"/>
+      <c r="BR12"/>
+      <c r="BS12"/>
+      <c r="BT12"/>
+      <c r="BU12"/>
+      <c r="BV12"/>
+      <c r="BW12"/>
+      <c r="BX12"/>
+      <c r="BY12"/>
+      <c r="BZ12"/>
+      <c r="CA12"/>
+      <c r="CB12"/>
+      <c r="CC12"/>
+      <c r="CD12"/>
+      <c r="CE12"/>
+      <c r="CF12"/>
+      <c r="CG12"/>
+      <c r="CH12"/>
+      <c r="CI12"/>
+      <c r="CJ12"/>
+      <c r="CK12"/>
+      <c r="CL12"/>
+      <c r="CM12"/>
+      <c r="CN12"/>
+      <c r="CO12"/>
+      <c r="CP12"/>
+      <c r="CQ12"/>
+      <c r="CR12"/>
+      <c r="CS12"/>
+      <c r="CT12"/>
+      <c r="CU12"/>
+      <c r="CV12"/>
+      <c r="CW12"/>
+      <c r="CX12"/>
+      <c r="CY12"/>
+      <c r="CZ12"/>
+      <c r="DA12"/>
+      <c r="DB12"/>
+      <c r="DC12"/>
+      <c r="DD12"/>
+      <c r="DE12"/>
+      <c r="DF12"/>
+      <c r="DG12"/>
+      <c r="DH12"/>
+      <c r="DI12"/>
+      <c r="DJ12"/>
+      <c r="DK12"/>
+      <c r="DL12"/>
+      <c r="DM12"/>
+      <c r="DN12"/>
+      <c r="DO12"/>
+      <c r="DP12"/>
+      <c r="DQ12"/>
+      <c r="DR12"/>
+      <c r="DS12"/>
+      <c r="DT12"/>
+      <c r="DU12"/>
+      <c r="DV12"/>
+      <c r="DW12"/>
+      <c r="DX12"/>
+      <c r="DY12"/>
+      <c r="DZ12"/>
+      <c r="EA12"/>
+      <c r="EB12"/>
+      <c r="EC12"/>
+      <c r="ED12"/>
+      <c r="EE12"/>
+      <c r="EF12"/>
+      <c r="EG12"/>
+      <c r="EH12"/>
+      <c r="EI12"/>
+      <c r="EJ12"/>
+      <c r="EK12"/>
+      <c r="EL12"/>
+      <c r="EM12"/>
+      <c r="EN12"/>
+      <c r="EO12"/>
+      <c r="EP12"/>
+      <c r="EQ12"/>
+      <c r="ER12"/>
+      <c r="ES12"/>
+      <c r="ET12"/>
+      <c r="EU12"/>
+      <c r="EV12"/>
+      <c r="EW12"/>
+      <c r="EX12"/>
+      <c r="EY12"/>
+      <c r="EZ12"/>
+      <c r="FA12" t="s">
+        <v>607</v>
+      </c>
+      <c r="FB12" t="s">
+        <v>304</v>
+      </c>
+      <c r="FC12" t="s">
+        <v>300</v>
+      </c>
+      <c r="FD12" t="s">
+        <v>605</v>
+      </c>
+      <c r="FE12" t="s">
+        <v>304</v>
+      </c>
+      <c r="FF12" t="s">
+        <v>606</v>
+      </c>
+      <c r="FG12"/>
+      <c r="FH12"/>
+      <c r="FI12"/>
+      <c r="FJ12"/>
+      <c r="FK12"/>
+      <c r="FL12"/>
+      <c r="FM12"/>
+      <c r="FN12"/>
+      <c r="FO12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>602</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" t="s">
+        <v>166</v>
+      </c>
+      <c r="E13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" t="s">
+        <v>417</v>
+      </c>
+      <c r="G13" t="s">
+        <v>582</v>
+      </c>
+      <c r="H13" t="s">
+        <v>253</v>
+      </c>
+      <c r="I13" t="s">
+        <v>170</v>
+      </c>
+      <c r="J13" t="s">
+        <v>201</v>
+      </c>
+      <c r="K13" t="s">
+        <v>604</v>
+      </c>
+      <c r="L13" t="s">
+        <v>566</v>
+      </c>
+      <c r="M13" t="s">
+        <v>543</v>
+      </c>
+      <c r="N13" t="s">
+        <v>613</v>
+      </c>
+      <c r="O13" t="s">
+        <v>304</v>
+      </c>
+      <c r="P13" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>615</v>
+      </c>
+      <c r="R13" t="s">
+        <v>304</v>
+      </c>
+      <c r="S13" t="s">
+        <v>616</v>
+      </c>
+      <c r="T13"/>
+      <c r="U13" t="s">
+        <v>587</v>
+      </c>
+      <c r="V13" t="s">
+        <v>174</v>
+      </c>
+      <c r="W13" t="s">
+        <v>174</v>
+      </c>
+      <c r="X13" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>617</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>391</v>
+      </c>
+      <c r="AD13"/>
+      <c r="AE13"/>
+      <c r="AF13" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="AG13"/>
+      <c r="AH13"/>
+      <c r="AI13"/>
+      <c r="AJ13" t="s">
+        <v>618</v>
+      </c>
+      <c r="AK13"/>
+      <c r="AL13" t="s">
+        <v>619</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>620</v>
+      </c>
+      <c r="AN13"/>
+      <c r="AO13"/>
+      <c r="AP13"/>
+      <c r="AQ13"/>
+      <c r="AR13"/>
+      <c r="AS13"/>
+      <c r="AT13"/>
+      <c r="AU13"/>
+      <c r="AV13"/>
+      <c r="AW13"/>
+      <c r="AX13"/>
+      <c r="AY13"/>
+      <c r="AZ13"/>
+      <c r="BA13"/>
+      <c r="BB13"/>
+      <c r="BC13"/>
+      <c r="BD13"/>
+      <c r="BE13"/>
+      <c r="BF13"/>
+      <c r="BG13"/>
+      <c r="BH13"/>
+      <c r="BI13"/>
+      <c r="BJ13"/>
+      <c r="BK13"/>
+      <c r="BL13"/>
+      <c r="BM13"/>
+      <c r="BN13"/>
+      <c r="BO13"/>
+      <c r="BP13"/>
+      <c r="BQ13"/>
+      <c r="BR13"/>
+      <c r="BS13"/>
+      <c r="BT13"/>
+      <c r="BU13"/>
+      <c r="BV13"/>
+      <c r="BW13"/>
+      <c r="BX13"/>
+      <c r="BY13"/>
+      <c r="BZ13"/>
+      <c r="CA13"/>
+      <c r="CB13"/>
+      <c r="CC13"/>
+      <c r="CD13"/>
+      <c r="CE13"/>
+      <c r="CF13"/>
+      <c r="CG13"/>
+      <c r="CH13"/>
+      <c r="CI13"/>
+      <c r="CJ13"/>
+      <c r="CK13"/>
+      <c r="CL13"/>
+      <c r="CM13"/>
+      <c r="CN13"/>
+      <c r="CO13"/>
+      <c r="CP13"/>
+      <c r="CQ13"/>
+      <c r="CR13"/>
+      <c r="CS13"/>
+      <c r="CT13"/>
+      <c r="CU13"/>
+      <c r="CV13"/>
+      <c r="CW13"/>
+      <c r="CX13"/>
+      <c r="CY13"/>
+      <c r="CZ13"/>
+      <c r="DA13"/>
+      <c r="DB13"/>
+      <c r="DC13"/>
+      <c r="DD13"/>
+      <c r="DE13"/>
+      <c r="DF13"/>
+      <c r="DG13"/>
+      <c r="DH13"/>
+      <c r="DI13"/>
+      <c r="DJ13"/>
+      <c r="DK13"/>
+      <c r="DL13"/>
+      <c r="DM13"/>
+      <c r="DN13"/>
+      <c r="DO13"/>
+      <c r="DP13"/>
+      <c r="DQ13"/>
+      <c r="DR13"/>
+      <c r="DS13"/>
+      <c r="DT13"/>
+      <c r="DU13"/>
+      <c r="DV13"/>
+      <c r="DW13"/>
+      <c r="DX13"/>
+      <c r="DY13"/>
+      <c r="DZ13"/>
+      <c r="EA13"/>
+      <c r="EB13"/>
+      <c r="EC13"/>
+      <c r="ED13"/>
+      <c r="EE13"/>
+      <c r="EF13"/>
+      <c r="EG13"/>
+      <c r="EH13"/>
+      <c r="EI13"/>
+      <c r="EJ13"/>
+      <c r="EK13"/>
+      <c r="EL13"/>
+      <c r="EM13"/>
+      <c r="EN13"/>
+      <c r="EO13"/>
+      <c r="EP13"/>
+      <c r="EQ13"/>
+      <c r="ER13"/>
+      <c r="ES13"/>
+      <c r="ET13"/>
+      <c r="EU13"/>
+      <c r="EV13"/>
+      <c r="EW13"/>
+      <c r="EX13"/>
+      <c r="EY13"/>
+      <c r="EZ13"/>
+      <c r="FA13" t="s">
+        <v>615</v>
+      </c>
+      <c r="FB13" t="s">
+        <v>304</v>
+      </c>
+      <c r="FC13" t="s">
+        <v>616</v>
+      </c>
+      <c r="FD13" t="s">
+        <v>613</v>
+      </c>
+      <c r="FE13" t="s">
+        <v>304</v>
+      </c>
+      <c r="FF13" t="s">
+        <v>614</v>
+      </c>
+      <c r="FG13"/>
+      <c r="FH13"/>
+      <c r="FI13"/>
+      <c r="FJ13"/>
+      <c r="FK13"/>
+      <c r="FL13"/>
+      <c r="FM13"/>
+      <c r="FN13"/>
+      <c r="FO13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>621</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C14" t="s">
+        <v>622</v>
+      </c>
+      <c r="D14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" t="s">
+        <v>417</v>
+      </c>
+      <c r="G14" t="s">
+        <v>582</v>
+      </c>
+      <c r="H14" t="s">
+        <v>253</v>
+      </c>
+      <c r="I14" t="s">
+        <v>170</v>
+      </c>
+      <c r="J14" t="s">
+        <v>171</v>
+      </c>
+      <c r="K14" t="s">
+        <v>541</v>
+      </c>
+      <c r="L14" t="s">
+        <v>566</v>
+      </c>
+      <c r="M14" t="s">
+        <v>543</v>
+      </c>
+      <c r="N14" t="s">
+        <v>623</v>
+      </c>
+      <c r="O14" t="s">
+        <v>624</v>
+      </c>
+      <c r="P14" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>626</v>
+      </c>
+      <c r="R14" t="s">
+        <v>624</v>
+      </c>
+      <c r="S14" t="s">
+        <v>627</v>
+      </c>
+      <c r="T14"/>
+      <c r="U14" t="s">
+        <v>549</v>
+      </c>
+      <c r="V14" t="s">
+        <v>174</v>
+      </c>
+      <c r="W14" t="s">
+        <v>174</v>
+      </c>
+      <c r="X14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB14"/>
+      <c r="AC14" t="s">
+        <v>628</v>
+      </c>
+      <c r="AD14"/>
+      <c r="AE14"/>
+      <c r="AF14" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="AG14"/>
+      <c r="AH14"/>
+      <c r="AI14" t="s">
+        <v>629</v>
+      </c>
+      <c r="AJ14"/>
+      <c r="AK14" t="s">
+        <v>630</v>
+      </c>
+      <c r="AL14"/>
+      <c r="AM14" t="s">
+        <v>631</v>
+      </c>
+      <c r="AN14"/>
+      <c r="AO14"/>
+      <c r="AP14"/>
+      <c r="AQ14"/>
+      <c r="AR14"/>
+      <c r="AS14"/>
+      <c r="AT14"/>
+      <c r="AU14"/>
+      <c r="AV14"/>
+      <c r="AW14"/>
+      <c r="AX14"/>
+      <c r="AY14"/>
+      <c r="AZ14"/>
+      <c r="BA14"/>
+      <c r="BB14"/>
+      <c r="BC14"/>
+      <c r="BD14"/>
+      <c r="BE14"/>
+      <c r="BF14"/>
+      <c r="BG14"/>
+      <c r="BH14"/>
+      <c r="BI14"/>
+      <c r="BJ14"/>
+      <c r="BK14"/>
+      <c r="BL14"/>
+      <c r="BM14"/>
+      <c r="BN14"/>
+      <c r="BO14"/>
+      <c r="BP14"/>
+      <c r="BQ14"/>
+      <c r="BR14"/>
+      <c r="BS14"/>
+      <c r="BT14"/>
+      <c r="BU14"/>
+      <c r="BV14"/>
+      <c r="BW14"/>
+      <c r="BX14"/>
+      <c r="BY14"/>
+      <c r="BZ14"/>
+      <c r="CA14"/>
+      <c r="CB14"/>
+      <c r="CC14"/>
+      <c r="CD14"/>
+      <c r="CE14"/>
+      <c r="CF14"/>
+      <c r="CG14"/>
+      <c r="CH14"/>
+      <c r="CI14"/>
+      <c r="CJ14"/>
+      <c r="CK14"/>
+      <c r="CL14"/>
+      <c r="CM14"/>
+      <c r="CN14"/>
+      <c r="CO14"/>
+      <c r="CP14"/>
+      <c r="CQ14"/>
+      <c r="CR14"/>
+      <c r="CS14"/>
+      <c r="CT14"/>
+      <c r="CU14"/>
+      <c r="CV14"/>
+      <c r="CW14"/>
+      <c r="CX14"/>
+      <c r="CY14"/>
+      <c r="CZ14"/>
+      <c r="DA14"/>
+      <c r="DB14"/>
+      <c r="DC14"/>
+      <c r="DD14"/>
+      <c r="DE14"/>
+      <c r="DF14"/>
+      <c r="DG14"/>
+      <c r="DH14"/>
+      <c r="DI14"/>
+      <c r="DJ14"/>
+      <c r="DK14"/>
+      <c r="DL14"/>
+      <c r="DM14"/>
+      <c r="DN14"/>
+      <c r="DO14"/>
+      <c r="DP14"/>
+      <c r="DQ14"/>
+      <c r="DR14"/>
+      <c r="DS14"/>
+      <c r="DT14"/>
+      <c r="DU14"/>
+      <c r="DV14"/>
+      <c r="DW14"/>
+      <c r="DX14"/>
+      <c r="DY14"/>
+      <c r="DZ14"/>
+      <c r="EA14"/>
+      <c r="EB14"/>
+      <c r="EC14"/>
+      <c r="ED14"/>
+      <c r="EE14"/>
+      <c r="EF14"/>
+      <c r="EG14"/>
+      <c r="EH14"/>
+      <c r="EI14"/>
+      <c r="EJ14"/>
+      <c r="EK14"/>
+      <c r="EL14"/>
+      <c r="EM14"/>
+      <c r="EN14"/>
+      <c r="EO14"/>
+      <c r="EP14"/>
+      <c r="EQ14"/>
+      <c r="ER14"/>
+      <c r="ES14"/>
+      <c r="ET14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="EV14"/>
+      <c r="EW14"/>
+      <c r="EX14"/>
+      <c r="EY14" t="s">
+        <v>627</v>
+      </c>
+      <c r="EZ14" t="s">
+        <v>626</v>
+      </c>
+      <c r="FA14"/>
+      <c r="FB14"/>
+      <c r="FC14"/>
+      <c r="FD14"/>
+      <c r="FE14"/>
+      <c r="FF14"/>
+      <c r="FG14"/>
+      <c r="FH14"/>
+      <c r="FI14"/>
+      <c r="FJ14"/>
+      <c r="FK14"/>
+      <c r="FL14"/>
+      <c r="FM14"/>
+      <c r="FN14"/>
+      <c r="FO14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>621</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C15" t="s">
+        <v>632</v>
+      </c>
+      <c r="D15" t="s">
+        <v>553</v>
+      </c>
+      <c r="E15" t="s">
+        <v>554</v>
+      </c>
+      <c r="F15" t="s">
+        <v>417</v>
+      </c>
+      <c r="G15" t="s">
+        <v>582</v>
+      </c>
+      <c r="H15" t="s">
+        <v>253</v>
+      </c>
+      <c r="I15" t="s">
+        <v>170</v>
+      </c>
+      <c r="J15" t="s">
+        <v>171</v>
+      </c>
+      <c r="K15" t="s">
+        <v>541</v>
+      </c>
+      <c r="L15" t="s">
+        <v>566</v>
+      </c>
+      <c r="M15" t="s">
+        <v>543</v>
+      </c>
+      <c r="N15" t="s">
+        <v>633</v>
+      </c>
+      <c r="O15" t="s">
+        <v>624</v>
+      </c>
+      <c r="P15" t="s">
+        <v>634</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>635</v>
+      </c>
+      <c r="R15" t="s">
+        <v>624</v>
+      </c>
+      <c r="S15" t="s">
+        <v>636</v>
+      </c>
+      <c r="T15"/>
+      <c r="U15" t="s">
+        <v>549</v>
+      </c>
+      <c r="V15" t="s">
+        <v>174</v>
+      </c>
+      <c r="W15" t="s">
+        <v>174</v>
+      </c>
+      <c r="X15" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB15"/>
+      <c r="AC15" t="s">
+        <v>637</v>
+      </c>
+      <c r="AD15"/>
+      <c r="AE15"/>
+      <c r="AF15" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="AG15"/>
+      <c r="AH15"/>
+      <c r="AI15" t="s">
+        <v>638</v>
+      </c>
+      <c r="AJ15"/>
+      <c r="AK15" t="s">
+        <v>639</v>
+      </c>
+      <c r="AL15"/>
+      <c r="AM15" t="s">
+        <v>640</v>
+      </c>
+      <c r="AN15"/>
+      <c r="AO15"/>
+      <c r="AP15"/>
+      <c r="AQ15"/>
+      <c r="AR15"/>
+      <c r="AS15"/>
+      <c r="AT15"/>
+      <c r="AU15"/>
+      <c r="AV15"/>
+      <c r="AW15"/>
+      <c r="AX15"/>
+      <c r="AY15"/>
+      <c r="AZ15"/>
+      <c r="BA15"/>
+      <c r="BB15"/>
+      <c r="BC15"/>
+      <c r="BD15"/>
+      <c r="BE15"/>
+      <c r="BF15"/>
+      <c r="BG15"/>
+      <c r="BH15"/>
+      <c r="BI15"/>
+      <c r="BJ15"/>
+      <c r="BK15"/>
+      <c r="BL15"/>
+      <c r="BM15"/>
+      <c r="BN15"/>
+      <c r="BO15"/>
+      <c r="BP15"/>
+      <c r="BQ15"/>
+      <c r="BR15"/>
+      <c r="BS15"/>
+      <c r="BT15"/>
+      <c r="BU15"/>
+      <c r="BV15"/>
+      <c r="BW15"/>
+      <c r="BX15"/>
+      <c r="BY15"/>
+      <c r="BZ15"/>
+      <c r="CA15"/>
+      <c r="CB15"/>
+      <c r="CC15"/>
+      <c r="CD15"/>
+      <c r="CE15"/>
+      <c r="CF15"/>
+      <c r="CG15"/>
+      <c r="CH15"/>
+      <c r="CI15"/>
+      <c r="CJ15"/>
+      <c r="CK15"/>
+      <c r="CL15"/>
+      <c r="CM15"/>
+      <c r="CN15"/>
+      <c r="CO15"/>
+      <c r="CP15"/>
+      <c r="CQ15"/>
+      <c r="CR15"/>
+      <c r="CS15"/>
+      <c r="CT15"/>
+      <c r="CU15"/>
+      <c r="CV15"/>
+      <c r="CW15"/>
+      <c r="CX15"/>
+      <c r="CY15"/>
+      <c r="CZ15"/>
+      <c r="DA15"/>
+      <c r="DB15"/>
+      <c r="DC15"/>
+      <c r="DD15"/>
+      <c r="DE15"/>
+      <c r="DF15"/>
+      <c r="DG15"/>
+      <c r="DH15"/>
+      <c r="DI15"/>
+      <c r="DJ15"/>
+      <c r="DK15"/>
+      <c r="DL15"/>
+      <c r="DM15"/>
+      <c r="DN15"/>
+      <c r="DO15"/>
+      <c r="DP15"/>
+      <c r="DQ15"/>
+      <c r="DR15"/>
+      <c r="DS15"/>
+      <c r="DT15"/>
+      <c r="DU15"/>
+      <c r="DV15"/>
+      <c r="DW15"/>
+      <c r="DX15"/>
+      <c r="DY15"/>
+      <c r="DZ15"/>
+      <c r="EA15"/>
+      <c r="EB15"/>
+      <c r="EC15"/>
+      <c r="ED15"/>
+      <c r="EE15"/>
+      <c r="EF15"/>
+      <c r="EG15"/>
+      <c r="EH15"/>
+      <c r="EI15"/>
+      <c r="EJ15"/>
+      <c r="EK15"/>
+      <c r="EL15"/>
+      <c r="EM15"/>
+      <c r="EN15"/>
+      <c r="EO15"/>
+      <c r="EP15"/>
+      <c r="EQ15"/>
+      <c r="ER15"/>
+      <c r="ES15"/>
+      <c r="ET15" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="EV15"/>
+      <c r="EW15"/>
+      <c r="EX15"/>
+      <c r="EY15" t="s">
+        <v>636</v>
+      </c>
+      <c r="EZ15" t="s">
+        <v>635</v>
+      </c>
+      <c r="FA15"/>
+      <c r="FB15"/>
+      <c r="FC15"/>
+      <c r="FD15"/>
+      <c r="FE15"/>
+      <c r="FF15"/>
+      <c r="FG15"/>
+      <c r="FH15"/>
+      <c r="FI15"/>
+      <c r="FJ15"/>
+      <c r="FK15"/>
+      <c r="FL15"/>
+      <c r="FM15"/>
+      <c r="FN15"/>
+      <c r="FO15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>641</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C16" t="s">
+        <v>563</v>
+      </c>
+      <c r="D16" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" t="s">
+        <v>166</v>
+      </c>
+      <c r="F16" t="s">
+        <v>417</v>
+      </c>
+      <c r="G16" t="s">
+        <v>642</v>
+      </c>
+      <c r="H16" t="s">
+        <v>253</v>
+      </c>
+      <c r="I16" t="s">
+        <v>170</v>
+      </c>
+      <c r="J16" t="s">
+        <v>201</v>
+      </c>
+      <c r="K16" t="s">
+        <v>172</v>
+      </c>
+      <c r="L16" t="s">
+        <v>566</v>
+      </c>
+      <c r="M16" t="s">
+        <v>543</v>
+      </c>
+      <c r="N16" t="s">
+        <v>643</v>
+      </c>
+      <c r="O16" t="s">
+        <v>644</v>
+      </c>
+      <c r="P16" t="s">
+        <v>645</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>646</v>
+      </c>
+      <c r="R16" t="s">
+        <v>644</v>
+      </c>
+      <c r="S16" t="s">
+        <v>647</v>
+      </c>
+      <c r="T16"/>
+      <c r="U16" t="s">
+        <v>549</v>
+      </c>
+      <c r="V16" t="s">
+        <v>174</v>
+      </c>
+      <c r="W16" t="s">
+        <v>175</v>
+      </c>
+      <c r="X16" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
+      <c r="AE16"/>
+      <c r="AF16" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="AG16"/>
+      <c r="AH16"/>
+      <c r="AI16" t="s">
+        <v>648</v>
+      </c>
+      <c r="AJ16"/>
+      <c r="AK16" t="s">
+        <v>649</v>
+      </c>
+      <c r="AL16"/>
+      <c r="AM16" t="s">
+        <v>650</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>651</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>644</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>652</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>653</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>644</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>654</v>
+      </c>
+      <c r="AT16"/>
+      <c r="AU16"/>
+      <c r="AV16"/>
+      <c r="AW16" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="AZ16"/>
+      <c r="BA16"/>
+      <c r="BB16"/>
+      <c r="BC16"/>
+      <c r="BD16"/>
+      <c r="BE16"/>
+      <c r="BF16"/>
+      <c r="BG16"/>
+      <c r="BH16"/>
+      <c r="BI16"/>
+      <c r="BJ16"/>
+      <c r="BK16"/>
+      <c r="BL16"/>
+      <c r="BM16"/>
+      <c r="BN16"/>
+      <c r="BO16"/>
+      <c r="BP16"/>
+      <c r="BQ16"/>
+      <c r="BR16"/>
+      <c r="BS16"/>
+      <c r="BT16"/>
+      <c r="BU16"/>
+      <c r="BV16"/>
+      <c r="BW16"/>
+      <c r="BX16"/>
+      <c r="BY16"/>
+      <c r="BZ16"/>
+      <c r="CA16"/>
+      <c r="CB16"/>
+      <c r="CC16"/>
+      <c r="CD16"/>
+      <c r="CE16"/>
+      <c r="CF16"/>
+      <c r="CG16"/>
+      <c r="CH16"/>
+      <c r="CI16"/>
+      <c r="CJ16"/>
+      <c r="CK16"/>
+      <c r="CL16"/>
+      <c r="CM16"/>
+      <c r="CN16"/>
+      <c r="CO16"/>
+      <c r="CP16"/>
+      <c r="CQ16"/>
+      <c r="CR16"/>
+      <c r="CS16"/>
+      <c r="CT16"/>
+      <c r="CU16"/>
+      <c r="CV16"/>
+      <c r="CW16"/>
+      <c r="CX16"/>
+      <c r="CY16"/>
+      <c r="CZ16"/>
+      <c r="DA16"/>
+      <c r="DB16"/>
+      <c r="DC16"/>
+      <c r="DD16"/>
+      <c r="DE16"/>
+      <c r="DF16"/>
+      <c r="DG16"/>
+      <c r="DH16"/>
+      <c r="DI16"/>
+      <c r="DJ16"/>
+      <c r="DK16"/>
+      <c r="DL16"/>
+      <c r="DM16"/>
+      <c r="DN16"/>
+      <c r="DO16"/>
+      <c r="DP16"/>
+      <c r="DQ16"/>
+      <c r="DR16"/>
+      <c r="DS16"/>
+      <c r="DT16"/>
+      <c r="DU16"/>
+      <c r="DV16"/>
+      <c r="DW16"/>
+      <c r="DX16"/>
+      <c r="DY16"/>
+      <c r="DZ16"/>
+      <c r="EA16"/>
+      <c r="EB16"/>
+      <c r="EC16"/>
+      <c r="ED16"/>
+      <c r="EE16"/>
+      <c r="EF16"/>
+      <c r="EG16"/>
+      <c r="EH16"/>
+      <c r="EI16" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>61</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>61</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="EO16"/>
+      <c r="EP16"/>
+      <c r="EQ16"/>
+      <c r="ER16"/>
+      <c r="ES16"/>
+      <c r="ET16"/>
+      <c r="EU16"/>
+      <c r="EV16" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>61</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="EY16"/>
+      <c r="EZ16"/>
+      <c r="FA16"/>
+      <c r="FB16"/>
+      <c r="FC16"/>
+      <c r="FD16"/>
+      <c r="FE16"/>
+      <c r="FF16"/>
+      <c r="FG16"/>
+      <c r="FH16"/>
+      <c r="FI16"/>
+      <c r="FJ16"/>
+      <c r="FK16"/>
+      <c r="FL16"/>
+      <c r="FM16"/>
+      <c r="FN16"/>
+      <c r="FO16"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>641</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C17" t="s">
+        <v>655</v>
+      </c>
+      <c r="D17" t="s">
+        <v>553</v>
+      </c>
+      <c r="E17" t="s">
+        <v>554</v>
+      </c>
+      <c r="F17" t="s">
+        <v>417</v>
+      </c>
+      <c r="G17" t="s">
+        <v>642</v>
+      </c>
+      <c r="H17" t="s">
+        <v>253</v>
+      </c>
+      <c r="I17" t="s">
+        <v>170</v>
+      </c>
+      <c r="J17" t="s">
+        <v>201</v>
+      </c>
+      <c r="K17" t="s">
+        <v>172</v>
+      </c>
+      <c r="L17" t="s">
+        <v>566</v>
+      </c>
+      <c r="M17" t="s">
+        <v>543</v>
+      </c>
+      <c r="N17" t="s">
+        <v>656</v>
+      </c>
+      <c r="O17" t="s">
+        <v>657</v>
+      </c>
+      <c r="P17" t="s">
+        <v>645</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>658</v>
+      </c>
+      <c r="R17" t="s">
+        <v>657</v>
+      </c>
+      <c r="S17" t="s">
+        <v>659</v>
+      </c>
+      <c r="T17"/>
+      <c r="U17" t="s">
+        <v>549</v>
+      </c>
+      <c r="V17" t="s">
+        <v>174</v>
+      </c>
+      <c r="W17" t="s">
+        <v>175</v>
+      </c>
+      <c r="X17" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB17"/>
+      <c r="AC17"/>
+      <c r="AD17"/>
+      <c r="AE17"/>
+      <c r="AF17" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="AG17"/>
+      <c r="AH17"/>
+      <c r="AI17" t="s">
+        <v>660</v>
+      </c>
+      <c r="AJ17"/>
+      <c r="AK17" t="s">
+        <v>661</v>
+      </c>
+      <c r="AL17"/>
+      <c r="AM17" t="s">
+        <v>662</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>663</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>657</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>664</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>665</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>657</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>666</v>
+      </c>
+      <c r="AT17"/>
+      <c r="AU17"/>
+      <c r="AV17"/>
+      <c r="AW17" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>62</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AZ17"/>
+      <c r="BA17"/>
+      <c r="BB17"/>
+      <c r="BC17"/>
+      <c r="BD17"/>
+      <c r="BE17"/>
+      <c r="BF17"/>
+      <c r="BG17"/>
+      <c r="BH17"/>
+      <c r="BI17"/>
+      <c r="BJ17"/>
+      <c r="BK17"/>
+      <c r="BL17"/>
+      <c r="BM17"/>
+      <c r="BN17"/>
+      <c r="BO17"/>
+      <c r="BP17"/>
+      <c r="BQ17"/>
+      <c r="BR17"/>
+      <c r="BS17"/>
+      <c r="BT17"/>
+      <c r="BU17"/>
+      <c r="BV17"/>
+      <c r="BW17"/>
+      <c r="BX17"/>
+      <c r="BY17"/>
+      <c r="BZ17"/>
+      <c r="CA17"/>
+      <c r="CB17"/>
+      <c r="CC17"/>
+      <c r="CD17"/>
+      <c r="CE17"/>
+      <c r="CF17"/>
+      <c r="CG17"/>
+      <c r="CH17"/>
+      <c r="CI17"/>
+      <c r="CJ17"/>
+      <c r="CK17"/>
+      <c r="CL17"/>
+      <c r="CM17"/>
+      <c r="CN17"/>
+      <c r="CO17"/>
+      <c r="CP17"/>
+      <c r="CQ17"/>
+      <c r="CR17"/>
+      <c r="CS17"/>
+      <c r="CT17"/>
+      <c r="CU17"/>
+      <c r="CV17"/>
+      <c r="CW17"/>
+      <c r="CX17"/>
+      <c r="CY17"/>
+      <c r="CZ17"/>
+      <c r="DA17"/>
+      <c r="DB17"/>
+      <c r="DC17"/>
+      <c r="DD17"/>
+      <c r="DE17"/>
+      <c r="DF17"/>
+      <c r="DG17"/>
+      <c r="DH17"/>
+      <c r="DI17"/>
+      <c r="DJ17"/>
+      <c r="DK17"/>
+      <c r="DL17"/>
+      <c r="DM17"/>
+      <c r="DN17"/>
+      <c r="DO17"/>
+      <c r="DP17"/>
+      <c r="DQ17"/>
+      <c r="DR17"/>
+      <c r="DS17"/>
+      <c r="DT17"/>
+      <c r="DU17"/>
+      <c r="DV17"/>
+      <c r="DW17"/>
+      <c r="DX17"/>
+      <c r="DY17"/>
+      <c r="DZ17"/>
+      <c r="EA17"/>
+      <c r="EB17"/>
+      <c r="EC17"/>
+      <c r="ED17"/>
+      <c r="EE17"/>
+      <c r="EF17"/>
+      <c r="EG17"/>
+      <c r="EH17"/>
+      <c r="EI17" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>62</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>62</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="EO17"/>
+      <c r="EP17"/>
+      <c r="EQ17"/>
+      <c r="ER17"/>
+      <c r="ES17"/>
+      <c r="ET17"/>
+      <c r="EU17"/>
+      <c r="EV17" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>62</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="EY17"/>
+      <c r="EZ17"/>
+      <c r="FA17"/>
+      <c r="FB17"/>
+      <c r="FC17"/>
+      <c r="FD17"/>
+      <c r="FE17"/>
+      <c r="FF17"/>
+      <c r="FG17"/>
+      <c r="FH17"/>
+      <c r="FI17"/>
+      <c r="FJ17"/>
+      <c r="FK17"/>
+      <c r="FL17"/>
+      <c r="FM17"/>
+      <c r="FN17"/>
+      <c r="FO17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>276</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C18" t="s">
+        <v>277</v>
+      </c>
+      <c r="D18" t="s">
+        <v>166</v>
+      </c>
+      <c r="E18" t="s">
+        <v>166</v>
+      </c>
+      <c r="F18" t="s">
+        <v>199</v>
+      </c>
+      <c r="G18" t="s">
+        <v>278</v>
+      </c>
+      <c r="H18" t="s">
+        <v>253</v>
+      </c>
+      <c r="I18" t="s">
+        <v>170</v>
+      </c>
+      <c r="J18" t="s">
+        <v>201</v>
+      </c>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+      <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18" t="s">
+        <v>175</v>
+      </c>
+      <c r="W18" t="s">
+        <v>175</v>
+      </c>
+      <c r="X18" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB18"/>
+      <c r="AC18"/>
+      <c r="AD18"/>
+      <c r="AE18" t="s">
+        <v>279</v>
+      </c>
+      <c r="AF18"/>
+      <c r="AG18"/>
+      <c r="AH18"/>
+      <c r="AI18"/>
+      <c r="AJ18"/>
+      <c r="AK18"/>
+      <c r="AL18"/>
+      <c r="AM18"/>
+      <c r="AN18"/>
+      <c r="AO18"/>
+      <c r="AP18"/>
+      <c r="AQ18"/>
+      <c r="AR18"/>
+      <c r="AS18"/>
+      <c r="AT18"/>
+      <c r="AU18"/>
+      <c r="AV18"/>
+      <c r="AW18"/>
+      <c r="AX18"/>
+      <c r="AY18"/>
+      <c r="AZ18"/>
+      <c r="BA18"/>
+      <c r="BB18"/>
+      <c r="BC18" t="s">
+        <v>280</v>
+      </c>
+      <c r="BD18" t="s">
         <v>281</v>
       </c>
-      <c r="BT5" t="s">
+      <c r="BE18" t="s">
+        <v>282</v>
+      </c>
+      <c r="BF18" t="s">
+        <v>283</v>
+      </c>
+      <c r="BG18" t="s">
+        <v>281</v>
+      </c>
+      <c r="BH18" t="s">
+        <v>284</v>
+      </c>
+      <c r="BI18"/>
+      <c r="BJ18"/>
+      <c r="BK18"/>
+      <c r="BL18"/>
+      <c r="BM18"/>
+      <c r="BN18"/>
+      <c r="BO18"/>
+      <c r="BP18"/>
+      <c r="BQ18"/>
+      <c r="BR18"/>
+      <c r="BS18"/>
+      <c r="BT18"/>
+      <c r="BU18"/>
+      <c r="BV18"/>
+      <c r="BW18"/>
+      <c r="BX18"/>
+      <c r="BY18"/>
+      <c r="BZ18"/>
+      <c r="CA18"/>
+      <c r="CB18"/>
+      <c r="CC18"/>
+      <c r="CD18"/>
+      <c r="CE18"/>
+      <c r="CF18"/>
+      <c r="CG18"/>
+      <c r="CH18"/>
+      <c r="CI18"/>
+      <c r="CJ18"/>
+      <c r="CK18"/>
+      <c r="CL18"/>
+      <c r="CM18"/>
+      <c r="CN18"/>
+      <c r="CO18"/>
+      <c r="CP18"/>
+      <c r="CQ18"/>
+      <c r="CR18"/>
+      <c r="CS18"/>
+      <c r="CT18"/>
+      <c r="CU18"/>
+      <c r="CV18"/>
+      <c r="CW18"/>
+      <c r="CX18"/>
+      <c r="CY18"/>
+      <c r="CZ18"/>
+      <c r="DA18"/>
+      <c r="DB18"/>
+      <c r="DC18"/>
+      <c r="DD18"/>
+      <c r="DE18"/>
+      <c r="DF18"/>
+      <c r="DG18"/>
+      <c r="DH18"/>
+      <c r="DI18"/>
+      <c r="DJ18"/>
+      <c r="DK18"/>
+      <c r="DL18"/>
+      <c r="DM18"/>
+      <c r="DN18"/>
+      <c r="DO18"/>
+      <c r="DP18"/>
+      <c r="DQ18"/>
+      <c r="DR18"/>
+      <c r="DS18"/>
+      <c r="DT18"/>
+      <c r="DU18"/>
+      <c r="DV18"/>
+      <c r="DW18"/>
+      <c r="DX18"/>
+      <c r="DY18"/>
+      <c r="DZ18"/>
+      <c r="EA18"/>
+      <c r="EB18"/>
+      <c r="EC18" t="s">
+        <v>285</v>
+      </c>
+      <c r="ED18" t="s">
+        <v>281</v>
+      </c>
+      <c r="EE18" t="s">
+        <v>286</v>
+      </c>
+      <c r="EF18" t="s">
+        <v>287</v>
+      </c>
+      <c r="EG18" t="s">
+        <v>281</v>
+      </c>
+      <c r="EH18" t="s">
+        <v>288</v>
+      </c>
+      <c r="EI18"/>
+      <c r="EJ18"/>
+      <c r="EK18"/>
+      <c r="EL18"/>
+      <c r="EM18"/>
+      <c r="EN18"/>
+      <c r="EO18"/>
+      <c r="EP18"/>
+      <c r="EQ18"/>
+      <c r="ER18"/>
+      <c r="ES18"/>
+      <c r="ET18"/>
+      <c r="EU18"/>
+      <c r="EV18"/>
+      <c r="EW18"/>
+      <c r="EX18"/>
+      <c r="EY18"/>
+      <c r="EZ18"/>
+      <c r="FA18"/>
+      <c r="FB18"/>
+      <c r="FC18"/>
+      <c r="FD18"/>
+      <c r="FE18"/>
+      <c r="FF18"/>
+      <c r="FG18"/>
+      <c r="FH18"/>
+      <c r="FI18"/>
+      <c r="FJ18" t="s">
+        <v>289</v>
+      </c>
+      <c r="FK18" t="s">
+        <v>281</v>
+      </c>
+      <c r="FL18" t="s">
+        <v>290</v>
+      </c>
+      <c r="FM18" t="s">
+        <v>291</v>
+      </c>
+      <c r="FN18" t="s">
+        <v>281</v>
+      </c>
+      <c r="FO18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>276</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C19" t="s">
+        <v>293</v>
+      </c>
+      <c r="D19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E19" t="s">
+        <v>250</v>
+      </c>
+      <c r="F19" t="s">
+        <v>199</v>
+      </c>
+      <c r="G19" t="s">
+        <v>278</v>
+      </c>
+      <c r="H19" t="s">
+        <v>253</v>
+      </c>
+      <c r="I19" t="s">
+        <v>170</v>
+      </c>
+      <c r="J19" t="s">
+        <v>201</v>
+      </c>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19" t="s">
+        <v>175</v>
+      </c>
+      <c r="W19" t="s">
+        <v>175</v>
+      </c>
+      <c r="X19" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB19"/>
+      <c r="AC19"/>
+      <c r="AD19"/>
+      <c r="AE19" t="s">
+        <v>279</v>
+      </c>
+      <c r="AF19"/>
+      <c r="AG19"/>
+      <c r="AH19"/>
+      <c r="AI19"/>
+      <c r="AJ19"/>
+      <c r="AK19"/>
+      <c r="AL19"/>
+      <c r="AM19"/>
+      <c r="AN19"/>
+      <c r="AO19"/>
+      <c r="AP19"/>
+      <c r="AQ19"/>
+      <c r="AR19"/>
+      <c r="AS19"/>
+      <c r="AT19"/>
+      <c r="AU19"/>
+      <c r="AV19"/>
+      <c r="AW19"/>
+      <c r="AX19"/>
+      <c r="AY19"/>
+      <c r="AZ19" t="s">
+        <v>294</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>281</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>295</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>296</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>281</v>
+      </c>
+      <c r="BE19" t="s">
+        <v>297</v>
+      </c>
+      <c r="BF19" t="s">
+        <v>298</v>
+      </c>
+      <c r="BG19" t="s">
+        <v>281</v>
+      </c>
+      <c r="BH19" t="s">
+        <v>299</v>
+      </c>
+      <c r="BI19"/>
+      <c r="BJ19"/>
+      <c r="BK19"/>
+      <c r="BL19"/>
+      <c r="BM19"/>
+      <c r="BN19"/>
+      <c r="BO19"/>
+      <c r="BP19"/>
+      <c r="BQ19"/>
+      <c r="BR19"/>
+      <c r="BS19"/>
+      <c r="BT19"/>
+      <c r="BU19"/>
+      <c r="BV19"/>
+      <c r="BW19"/>
+      <c r="BX19"/>
+      <c r="BY19"/>
+      <c r="BZ19"/>
+      <c r="CA19"/>
+      <c r="CB19"/>
+      <c r="CC19"/>
+      <c r="CD19"/>
+      <c r="CE19"/>
+      <c r="CF19"/>
+      <c r="CG19"/>
+      <c r="CH19"/>
+      <c r="CI19"/>
+      <c r="CJ19"/>
+      <c r="CK19"/>
+      <c r="CL19"/>
+      <c r="CM19"/>
+      <c r="CN19"/>
+      <c r="CO19"/>
+      <c r="CP19"/>
+      <c r="CQ19"/>
+      <c r="CR19"/>
+      <c r="CS19"/>
+      <c r="CT19"/>
+      <c r="CU19"/>
+      <c r="CV19"/>
+      <c r="CW19"/>
+      <c r="CX19"/>
+      <c r="CY19"/>
+      <c r="CZ19"/>
+      <c r="DA19"/>
+      <c r="DB19"/>
+      <c r="DC19"/>
+      <c r="DD19"/>
+      <c r="DE19"/>
+      <c r="DF19"/>
+      <c r="DG19"/>
+      <c r="DH19"/>
+      <c r="DI19"/>
+      <c r="DJ19"/>
+      <c r="DK19"/>
+      <c r="DL19"/>
+      <c r="DM19"/>
+      <c r="DN19"/>
+      <c r="DO19"/>
+      <c r="DP19"/>
+      <c r="DQ19"/>
+      <c r="DR19"/>
+      <c r="DS19"/>
+      <c r="DT19"/>
+      <c r="DU19"/>
+      <c r="DV19"/>
+      <c r="DW19"/>
+      <c r="DX19"/>
+      <c r="DY19"/>
+      <c r="DZ19" t="s">
+        <v>300</v>
+      </c>
+      <c r="EA19" t="s">
+        <v>281</v>
+      </c>
+      <c r="EB19" t="s">
         <v>301</v>
       </c>
-      <c r="BU5" t="s">
+      <c r="EC19" t="s">
         <v>302</v>
       </c>
-      <c r="BV5" t="s">
+      <c r="ED19" t="s">
         <v>281</v>
       </c>
-      <c r="BW5" t="s">
+      <c r="EE19" t="s">
         <v>303</v>
       </c>
-      <c r="BX5" t="s">
+      <c r="EF19" t="s">
         <v>304</v>
       </c>
-      <c r="BY5" t="s">
+      <c r="EG19" t="s">
         <v>281</v>
       </c>
-      <c r="BZ5" t="s">
+      <c r="EH19" t="s">
         <v>305</v>
       </c>
-      <c r="CA5" t="s">
+      <c r="EI19"/>
+      <c r="EJ19"/>
+      <c r="EK19"/>
+      <c r="EL19"/>
+      <c r="EM19"/>
+      <c r="EN19"/>
+      <c r="EO19"/>
+      <c r="EP19"/>
+      <c r="EQ19"/>
+      <c r="ER19"/>
+      <c r="ES19"/>
+      <c r="ET19"/>
+      <c r="EU19"/>
+      <c r="EV19"/>
+      <c r="EW19"/>
+      <c r="EX19"/>
+      <c r="EY19"/>
+      <c r="EZ19"/>
+      <c r="FA19"/>
+      <c r="FB19"/>
+      <c r="FC19"/>
+      <c r="FD19"/>
+      <c r="FE19"/>
+      <c r="FF19"/>
+      <c r="FG19" t="s">
         <v>306</v>
       </c>
-      <c r="CB5" t="s">
+      <c r="FH19" t="s">
         <v>281</v>
       </c>
-      <c r="CC5" t="s">
+      <c r="FI19" t="s">
         <v>307</v>
       </c>
-      <c r="CD5" t="s">
+      <c r="FJ19" t="s">
         <v>308</v>
       </c>
-      <c r="CE5" t="s">
+      <c r="FK19" t="s">
         <v>281</v>
       </c>
-      <c r="CF5" t="s">
+      <c r="FL19" t="s">
         <v>309</v>
       </c>
-      <c r="CG5" t="s">
+      <c r="FM19" t="s">
         <v>310</v>
       </c>
-      <c r="CH5" t="s">
+      <c r="FN19" t="s">
         <v>281</v>
       </c>
-      <c r="CI5" t="s">
+      <c r="FO19" t="s">
         <v>311</v>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>667</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C20" t="s">
+        <v>622</v>
+      </c>
+      <c r="D20" t="s">
+        <v>166</v>
+      </c>
+      <c r="E20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" t="s">
+        <v>417</v>
+      </c>
+      <c r="G20" t="s">
+        <v>668</v>
+      </c>
+      <c r="H20" t="s">
+        <v>169</v>
+      </c>
+      <c r="I20" t="s">
+        <v>170</v>
+      </c>
+      <c r="J20" t="s">
+        <v>254</v>
+      </c>
+      <c r="K20" t="s">
+        <v>669</v>
+      </c>
+      <c r="L20" t="s">
+        <v>566</v>
+      </c>
+      <c r="M20" t="s">
+        <v>543</v>
+      </c>
+      <c r="N20" t="s">
+        <v>670</v>
+      </c>
+      <c r="O20" t="s">
+        <v>317</v>
+      </c>
+      <c r="P20" t="s">
+        <v>671</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>672</v>
+      </c>
+      <c r="R20" t="s">
+        <v>317</v>
+      </c>
+      <c r="S20" t="s">
+        <v>673</v>
+      </c>
+      <c r="T20"/>
+      <c r="U20" t="s">
+        <v>549</v>
+      </c>
+      <c r="V20" t="s">
+        <v>174</v>
+      </c>
+      <c r="W20" t="s">
+        <v>175</v>
+      </c>
+      <c r="X20" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>674</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>675</v>
+      </c>
+      <c r="AD20"/>
+      <c r="AE20"/>
+      <c r="AF20" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="AG20"/>
+      <c r="AH20"/>
+      <c r="AI20" t="s">
+        <v>676</v>
+      </c>
+      <c r="AJ20"/>
+      <c r="AK20" t="s">
+        <v>677</v>
+      </c>
+      <c r="AL20"/>
+      <c r="AM20" t="s">
+        <v>678</v>
+      </c>
+      <c r="AN20"/>
+      <c r="AO20"/>
+      <c r="AP20"/>
+      <c r="AQ20"/>
+      <c r="AR20"/>
+      <c r="AS20"/>
+      <c r="AT20"/>
+      <c r="AU20"/>
+      <c r="AV20"/>
+      <c r="AW20"/>
+      <c r="AX20"/>
+      <c r="AY20"/>
+      <c r="AZ20"/>
+      <c r="BA20"/>
+      <c r="BB20"/>
+      <c r="BC20"/>
+      <c r="BD20"/>
+      <c r="BE20"/>
+      <c r="BF20"/>
+      <c r="BG20"/>
+      <c r="BH20"/>
+      <c r="BI20"/>
+      <c r="BJ20"/>
+      <c r="BK20"/>
+      <c r="BL20"/>
+      <c r="BM20"/>
+      <c r="BN20"/>
+      <c r="BO20"/>
+      <c r="BP20"/>
+      <c r="BQ20"/>
+      <c r="BR20"/>
+      <c r="BS20"/>
+      <c r="BT20"/>
+      <c r="BU20"/>
+      <c r="BV20"/>
+      <c r="BW20"/>
+      <c r="BX20"/>
+      <c r="BY20"/>
+      <c r="BZ20"/>
+      <c r="CA20"/>
+      <c r="CB20"/>
+      <c r="CC20"/>
+      <c r="CD20"/>
+      <c r="CE20"/>
+      <c r="CF20"/>
+      <c r="CG20"/>
+      <c r="CH20"/>
+      <c r="CI20"/>
+      <c r="CJ20"/>
+      <c r="CK20"/>
+      <c r="CL20"/>
+      <c r="CM20"/>
+      <c r="CN20"/>
+      <c r="CO20"/>
+      <c r="CP20"/>
+      <c r="CQ20"/>
+      <c r="CR20"/>
+      <c r="CS20"/>
+      <c r="CT20"/>
+      <c r="CU20"/>
+      <c r="CV20"/>
+      <c r="CW20"/>
+      <c r="CX20"/>
+      <c r="CY20"/>
+      <c r="CZ20"/>
+      <c r="DA20"/>
+      <c r="DB20"/>
+      <c r="DC20"/>
+      <c r="DD20"/>
+      <c r="DE20"/>
+      <c r="DF20"/>
+      <c r="DG20"/>
+      <c r="DH20"/>
+      <c r="DI20"/>
+      <c r="DJ20"/>
+      <c r="DK20"/>
+      <c r="DL20"/>
+      <c r="DM20"/>
+      <c r="DN20"/>
+      <c r="DO20"/>
+      <c r="DP20"/>
+      <c r="DQ20"/>
+      <c r="DR20"/>
+      <c r="DS20"/>
+      <c r="DT20"/>
+      <c r="DU20"/>
+      <c r="DV20"/>
+      <c r="DW20"/>
+      <c r="DX20"/>
+      <c r="DY20"/>
+      <c r="DZ20"/>
+      <c r="EA20"/>
+      <c r="EB20"/>
+      <c r="EC20"/>
+      <c r="ED20"/>
+      <c r="EE20"/>
+      <c r="EF20"/>
+      <c r="EG20"/>
+      <c r="EH20"/>
+      <c r="EI20"/>
+      <c r="EJ20"/>
+      <c r="EK20"/>
+      <c r="EL20"/>
+      <c r="EM20"/>
+      <c r="EN20"/>
+      <c r="EO20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="EP20" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="EQ20"/>
+      <c r="ER20"/>
+      <c r="ES20"/>
+      <c r="ET20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="EU20" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="EV20"/>
+      <c r="EW20"/>
+      <c r="EX20"/>
+      <c r="EY20"/>
+      <c r="EZ20"/>
+      <c r="FA20"/>
+      <c r="FB20"/>
+      <c r="FC20"/>
+      <c r="FD20"/>
+      <c r="FE20"/>
+      <c r="FF20"/>
+      <c r="FG20"/>
+      <c r="FH20"/>
+      <c r="FI20"/>
+      <c r="FJ20"/>
+      <c r="FK20"/>
+      <c r="FL20"/>
+      <c r="FM20"/>
+      <c r="FN20"/>
+      <c r="FO20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>667</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C21" t="s">
+        <v>679</v>
+      </c>
+      <c r="D21" t="s">
+        <v>553</v>
+      </c>
+      <c r="E21" t="s">
+        <v>680</v>
+      </c>
+      <c r="F21" t="s">
+        <v>417</v>
+      </c>
+      <c r="G21" t="s">
+        <v>668</v>
+      </c>
+      <c r="H21" t="s">
+        <v>169</v>
+      </c>
+      <c r="I21" t="s">
+        <v>170</v>
+      </c>
+      <c r="J21" t="s">
+        <v>254</v>
+      </c>
+      <c r="K21" t="s">
+        <v>669</v>
+      </c>
+      <c r="L21" t="s">
+        <v>566</v>
+      </c>
+      <c r="M21" t="s">
+        <v>543</v>
+      </c>
+      <c r="N21" t="s">
+        <v>681</v>
+      </c>
+      <c r="O21" t="s">
+        <v>361</v>
+      </c>
+      <c r="P21" t="s">
+        <v>682</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>683</v>
+      </c>
+      <c r="R21" t="s">
+        <v>361</v>
+      </c>
+      <c r="S21" t="s">
+        <v>684</v>
+      </c>
+      <c r="T21"/>
+      <c r="U21" t="s">
+        <v>549</v>
+      </c>
+      <c r="V21" t="s">
+        <v>174</v>
+      </c>
+      <c r="W21" t="s">
+        <v>175</v>
+      </c>
+      <c r="X21" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>685</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>686</v>
+      </c>
+      <c r="AD21"/>
+      <c r="AE21"/>
+      <c r="AF21" t="n">
+        <v>9.88</v>
+      </c>
+      <c r="AG21"/>
+      <c r="AH21"/>
+      <c r="AI21" t="s">
+        <v>687</v>
+      </c>
+      <c r="AJ21"/>
+      <c r="AK21" t="s">
+        <v>688</v>
+      </c>
+      <c r="AL21"/>
+      <c r="AM21" t="s">
+        <v>689</v>
+      </c>
+      <c r="AN21"/>
+      <c r="AO21"/>
+      <c r="AP21"/>
+      <c r="AQ21"/>
+      <c r="AR21"/>
+      <c r="AS21"/>
+      <c r="AT21"/>
+      <c r="AU21"/>
+      <c r="AV21"/>
+      <c r="AW21"/>
+      <c r="AX21"/>
+      <c r="AY21"/>
+      <c r="AZ21"/>
+      <c r="BA21"/>
+      <c r="BB21"/>
+      <c r="BC21"/>
+      <c r="BD21"/>
+      <c r="BE21"/>
+      <c r="BF21"/>
+      <c r="BG21"/>
+      <c r="BH21"/>
+      <c r="BI21"/>
+      <c r="BJ21"/>
+      <c r="BK21"/>
+      <c r="BL21"/>
+      <c r="BM21"/>
+      <c r="BN21"/>
+      <c r="BO21"/>
+      <c r="BP21"/>
+      <c r="BQ21"/>
+      <c r="BR21"/>
+      <c r="BS21"/>
+      <c r="BT21"/>
+      <c r="BU21"/>
+      <c r="BV21"/>
+      <c r="BW21"/>
+      <c r="BX21"/>
+      <c r="BY21"/>
+      <c r="BZ21"/>
+      <c r="CA21"/>
+      <c r="CB21"/>
+      <c r="CC21"/>
+      <c r="CD21"/>
+      <c r="CE21"/>
+      <c r="CF21"/>
+      <c r="CG21"/>
+      <c r="CH21"/>
+      <c r="CI21"/>
+      <c r="CJ21"/>
+      <c r="CK21"/>
+      <c r="CL21"/>
+      <c r="CM21"/>
+      <c r="CN21"/>
+      <c r="CO21"/>
+      <c r="CP21"/>
+      <c r="CQ21"/>
+      <c r="CR21"/>
+      <c r="CS21"/>
+      <c r="CT21"/>
+      <c r="CU21"/>
+      <c r="CV21"/>
+      <c r="CW21"/>
+      <c r="CX21"/>
+      <c r="CY21"/>
+      <c r="CZ21"/>
+      <c r="DA21"/>
+      <c r="DB21"/>
+      <c r="DC21"/>
+      <c r="DD21"/>
+      <c r="DE21"/>
+      <c r="DF21"/>
+      <c r="DG21"/>
+      <c r="DH21"/>
+      <c r="DI21"/>
+      <c r="DJ21"/>
+      <c r="DK21"/>
+      <c r="DL21"/>
+      <c r="DM21"/>
+      <c r="DN21"/>
+      <c r="DO21"/>
+      <c r="DP21"/>
+      <c r="DQ21"/>
+      <c r="DR21"/>
+      <c r="DS21"/>
+      <c r="DT21"/>
+      <c r="DU21"/>
+      <c r="DV21"/>
+      <c r="DW21"/>
+      <c r="DX21"/>
+      <c r="DY21"/>
+      <c r="DZ21"/>
+      <c r="EA21"/>
+      <c r="EB21"/>
+      <c r="EC21"/>
+      <c r="ED21"/>
+      <c r="EE21"/>
+      <c r="EF21"/>
+      <c r="EG21"/>
+      <c r="EH21"/>
+      <c r="EI21"/>
+      <c r="EJ21"/>
+      <c r="EK21"/>
+      <c r="EL21"/>
+      <c r="EM21"/>
+      <c r="EN21"/>
+      <c r="EO21" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="EP21" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="EQ21"/>
+      <c r="ER21"/>
+      <c r="ES21"/>
+      <c r="ET21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="EU21" t="n">
+        <v>9.88</v>
+      </c>
+      <c r="EV21"/>
+      <c r="EW21"/>
+      <c r="EX21"/>
+      <c r="EY21"/>
+      <c r="EZ21"/>
+      <c r="FA21"/>
+      <c r="FB21"/>
+      <c r="FC21"/>
+      <c r="FD21"/>
+      <c r="FE21"/>
+      <c r="FF21"/>
+      <c r="FG21"/>
+      <c r="FH21"/>
+      <c r="FI21"/>
+      <c r="FJ21"/>
+      <c r="FK21"/>
+      <c r="FL21"/>
+      <c r="FM21"/>
+      <c r="FN21"/>
+      <c r="FO21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>446</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C22" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" t="s">
+        <v>166</v>
+      </c>
+      <c r="F22" t="s">
+        <v>251</v>
+      </c>
+      <c r="G22" t="s">
+        <v>447</v>
+      </c>
+      <c r="H22" t="s">
+        <v>169</v>
+      </c>
+      <c r="I22" t="s">
+        <v>170</v>
+      </c>
+      <c r="J22" t="s">
+        <v>201</v>
+      </c>
+      <c r="K22" t="s">
+        <v>172</v>
+      </c>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22" t="s">
+        <v>174</v>
+      </c>
+      <c r="W22" t="s">
+        <v>174</v>
+      </c>
+      <c r="X22" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>448</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>449</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>450</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>451</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>345</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>256</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>452</v>
+      </c>
+      <c r="AJ22"/>
+      <c r="AK22"/>
+      <c r="AL22"/>
+      <c r="AM22" t="s">
+        <v>182</v>
+      </c>
+      <c r="AN22"/>
+      <c r="AO22"/>
+      <c r="AP22"/>
+      <c r="AQ22"/>
+      <c r="AR22"/>
+      <c r="AS22"/>
+      <c r="AT22"/>
+      <c r="AU22"/>
+      <c r="AV22"/>
+      <c r="AW22"/>
+      <c r="AX22"/>
+      <c r="AY22"/>
+      <c r="AZ22"/>
+      <c r="BA22"/>
+      <c r="BB22"/>
+      <c r="BC22"/>
+      <c r="BD22"/>
+      <c r="BE22"/>
+      <c r="BF22"/>
+      <c r="BG22"/>
+      <c r="BH22"/>
+      <c r="BI22"/>
+      <c r="BJ22"/>
+      <c r="BK22"/>
+      <c r="BL22"/>
+      <c r="BM22"/>
+      <c r="BN22"/>
+      <c r="BO22"/>
+      <c r="BP22"/>
+      <c r="BQ22"/>
+      <c r="BR22" t="s">
+        <v>453</v>
+      </c>
+      <c r="BS22" t="s">
+        <v>272</v>
+      </c>
+      <c r="BT22" t="s">
+        <v>454</v>
+      </c>
+      <c r="BU22" t="s">
+        <v>455</v>
+      </c>
+      <c r="BV22" t="s">
+        <v>272</v>
+      </c>
+      <c r="BW22" t="s">
+        <v>456</v>
+      </c>
+      <c r="BX22"/>
+      <c r="BY22"/>
+      <c r="BZ22"/>
+      <c r="CA22"/>
+      <c r="CB22"/>
+      <c r="CC22"/>
+      <c r="CD22"/>
+      <c r="CE22"/>
+      <c r="CF22"/>
+      <c r="CG22"/>
+      <c r="CH22"/>
+      <c r="CI22"/>
+      <c r="CJ22"/>
+      <c r="CK22"/>
+      <c r="CL22"/>
+      <c r="CM22"/>
+      <c r="CN22"/>
+      <c r="CO22"/>
+      <c r="CP22"/>
+      <c r="CQ22"/>
+      <c r="CR22" t="s">
+        <v>457</v>
+      </c>
+      <c r="CS22" t="s">
+        <v>272</v>
+      </c>
+      <c r="CT22" t="s">
+        <v>301</v>
+      </c>
+      <c r="CU22" t="s">
+        <v>458</v>
+      </c>
+      <c r="CV22" t="s">
+        <v>272</v>
+      </c>
+      <c r="CW22" t="s">
+        <v>459</v>
+      </c>
+      <c r="CX22"/>
+      <c r="CY22"/>
+      <c r="CZ22"/>
+      <c r="DA22"/>
+      <c r="DB22"/>
+      <c r="DC22"/>
+      <c r="DD22"/>
+      <c r="DE22"/>
+      <c r="DF22"/>
+      <c r="DG22"/>
+      <c r="DH22"/>
+      <c r="DI22"/>
+      <c r="DJ22"/>
+      <c r="DK22"/>
+      <c r="DL22"/>
+      <c r="DM22"/>
+      <c r="DN22"/>
+      <c r="DO22"/>
+      <c r="DP22"/>
+      <c r="DQ22"/>
+      <c r="DR22"/>
+      <c r="DS22"/>
+      <c r="DT22"/>
+      <c r="DU22"/>
+      <c r="DV22"/>
+      <c r="DW22"/>
+      <c r="DX22"/>
+      <c r="DY22"/>
+      <c r="DZ22"/>
+      <c r="EA22"/>
+      <c r="EB22"/>
+      <c r="EC22"/>
+      <c r="ED22"/>
+      <c r="EE22"/>
+      <c r="EF22"/>
+      <c r="EG22"/>
+      <c r="EH22"/>
+      <c r="EI22"/>
+      <c r="EJ22"/>
+      <c r="EK22"/>
+      <c r="EL22"/>
+      <c r="EM22"/>
+      <c r="EN22"/>
+      <c r="EO22"/>
+      <c r="EP22"/>
+      <c r="EQ22"/>
+      <c r="ER22"/>
+      <c r="ES22"/>
+      <c r="ET22"/>
+      <c r="EU22"/>
+      <c r="EV22"/>
+      <c r="EW22"/>
+      <c r="EX22"/>
+      <c r="EY22"/>
+      <c r="EZ22"/>
+      <c r="FA22"/>
+      <c r="FB22"/>
+      <c r="FC22"/>
+      <c r="FD22"/>
+      <c r="FE22"/>
+      <c r="FF22"/>
+      <c r="FG22"/>
+      <c r="FH22"/>
+      <c r="FI22"/>
+      <c r="FJ22"/>
+      <c r="FK22"/>
+      <c r="FL22"/>
+      <c r="FM22"/>
+      <c r="FN22"/>
+      <c r="FO22"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>446</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C23" t="s">
+        <v>460</v>
+      </c>
+      <c r="D23" t="s">
+        <v>461</v>
+      </c>
+      <c r="E23" t="s">
+        <v>462</v>
+      </c>
+      <c r="F23" t="s">
+        <v>251</v>
+      </c>
+      <c r="G23" t="s">
+        <v>447</v>
+      </c>
+      <c r="H23" t="s">
+        <v>169</v>
+      </c>
+      <c r="I23" t="s">
+        <v>170</v>
+      </c>
+      <c r="J23" t="s">
+        <v>201</v>
+      </c>
+      <c r="K23" t="s">
+        <v>172</v>
+      </c>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23" t="s">
+        <v>174</v>
+      </c>
+      <c r="W23" t="s">
+        <v>174</v>
+      </c>
+      <c r="X23" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>463</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>464</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>465</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>466</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>345</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>256</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>467</v>
+      </c>
+      <c r="AJ23"/>
+      <c r="AK23" t="s">
+        <v>468</v>
+      </c>
+      <c r="AL23"/>
+      <c r="AM23" t="s">
+        <v>469</v>
+      </c>
+      <c r="AN23"/>
+      <c r="AO23"/>
+      <c r="AP23"/>
+      <c r="AQ23"/>
+      <c r="AR23"/>
+      <c r="AS23"/>
+      <c r="AT23"/>
+      <c r="AU23"/>
+      <c r="AV23"/>
+      <c r="AW23"/>
+      <c r="AX23"/>
+      <c r="AY23"/>
+      <c r="AZ23"/>
+      <c r="BA23"/>
+      <c r="BB23"/>
+      <c r="BC23"/>
+      <c r="BD23"/>
+      <c r="BE23"/>
+      <c r="BF23"/>
+      <c r="BG23"/>
+      <c r="BH23"/>
+      <c r="BI23"/>
+      <c r="BJ23"/>
+      <c r="BK23"/>
+      <c r="BL23"/>
+      <c r="BM23"/>
+      <c r="BN23"/>
+      <c r="BO23"/>
+      <c r="BP23"/>
+      <c r="BQ23"/>
+      <c r="BR23" t="s">
+        <v>470</v>
+      </c>
+      <c r="BS23" t="s">
+        <v>272</v>
+      </c>
+      <c r="BT23" t="s">
+        <v>471</v>
+      </c>
+      <c r="BU23" t="s">
+        <v>472</v>
+      </c>
+      <c r="BV23" t="s">
+        <v>272</v>
+      </c>
+      <c r="BW23" t="s">
+        <v>473</v>
+      </c>
+      <c r="BX23"/>
+      <c r="BY23"/>
+      <c r="BZ23"/>
+      <c r="CA23"/>
+      <c r="CB23"/>
+      <c r="CC23"/>
+      <c r="CD23"/>
+      <c r="CE23"/>
+      <c r="CF23"/>
+      <c r="CG23"/>
+      <c r="CH23"/>
+      <c r="CI23"/>
+      <c r="CJ23"/>
+      <c r="CK23"/>
+      <c r="CL23"/>
+      <c r="CM23"/>
+      <c r="CN23"/>
+      <c r="CO23"/>
+      <c r="CP23"/>
+      <c r="CQ23"/>
+      <c r="CR23" t="s">
+        <v>474</v>
+      </c>
+      <c r="CS23" t="s">
+        <v>272</v>
+      </c>
+      <c r="CT23" t="s">
+        <v>475</v>
+      </c>
+      <c r="CU23" t="s">
+        <v>476</v>
+      </c>
+      <c r="CV23" t="s">
+        <v>272</v>
+      </c>
+      <c r="CW23" t="s">
+        <v>477</v>
+      </c>
+      <c r="CX23"/>
+      <c r="CY23"/>
+      <c r="CZ23"/>
+      <c r="DA23"/>
+      <c r="DB23"/>
+      <c r="DC23"/>
+      <c r="DD23"/>
+      <c r="DE23"/>
+      <c r="DF23"/>
+      <c r="DG23"/>
+      <c r="DH23"/>
+      <c r="DI23"/>
+      <c r="DJ23"/>
+      <c r="DK23"/>
+      <c r="DL23"/>
+      <c r="DM23"/>
+      <c r="DN23"/>
+      <c r="DO23"/>
+      <c r="DP23"/>
+      <c r="DQ23"/>
+      <c r="DR23"/>
+      <c r="DS23"/>
+      <c r="DT23"/>
+      <c r="DU23"/>
+      <c r="DV23"/>
+      <c r="DW23"/>
+      <c r="DX23"/>
+      <c r="DY23"/>
+      <c r="DZ23"/>
+      <c r="EA23"/>
+      <c r="EB23"/>
+      <c r="EC23"/>
+      <c r="ED23"/>
+      <c r="EE23"/>
+      <c r="EF23"/>
+      <c r="EG23"/>
+      <c r="EH23"/>
+      <c r="EI23"/>
+      <c r="EJ23"/>
+      <c r="EK23"/>
+      <c r="EL23"/>
+      <c r="EM23"/>
+      <c r="EN23"/>
+      <c r="EO23"/>
+      <c r="EP23"/>
+      <c r="EQ23"/>
+      <c r="ER23"/>
+      <c r="ES23"/>
+      <c r="ET23"/>
+      <c r="EU23"/>
+      <c r="EV23"/>
+      <c r="EW23"/>
+      <c r="EX23"/>
+      <c r="EY23"/>
+      <c r="EZ23"/>
+      <c r="FA23"/>
+      <c r="FB23"/>
+      <c r="FC23"/>
+      <c r="FD23"/>
+      <c r="FE23"/>
+      <c r="FF23"/>
+      <c r="FG23"/>
+      <c r="FH23"/>
+      <c r="FI23"/>
+      <c r="FJ23"/>
+      <c r="FK23"/>
+      <c r="FL23"/>
+      <c r="FM23"/>
+      <c r="FN23"/>
+      <c r="FO23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>690</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C24" t="s">
+        <v>165</v>
+      </c>
+      <c r="D24" t="s">
+        <v>166</v>
+      </c>
+      <c r="E24" t="s">
+        <v>166</v>
+      </c>
+      <c r="F24" t="s">
+        <v>338</v>
+      </c>
+      <c r="G24" t="s">
+        <v>691</v>
+      </c>
+      <c r="H24" t="s">
+        <v>253</v>
+      </c>
+      <c r="I24" t="s">
+        <v>170</v>
+      </c>
+      <c r="J24" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" t="s">
+        <v>541</v>
+      </c>
+      <c r="L24" t="s">
+        <v>566</v>
+      </c>
+      <c r="M24" t="s">
+        <v>543</v>
+      </c>
+      <c r="N24" t="s">
+        <v>692</v>
+      </c>
+      <c r="O24" t="s">
+        <v>693</v>
+      </c>
+      <c r="P24" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>694</v>
+      </c>
+      <c r="R24" t="s">
+        <v>693</v>
+      </c>
+      <c r="S24" t="s">
+        <v>695</v>
+      </c>
+      <c r="T24" t="s">
+        <v>696</v>
+      </c>
+      <c r="U24"/>
+      <c r="V24" t="s">
+        <v>173</v>
+      </c>
+      <c r="W24" t="s">
+        <v>175</v>
+      </c>
+      <c r="X24" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>697</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>698</v>
+      </c>
+      <c r="AD24"/>
+      <c r="AE24"/>
+      <c r="AF24" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="AG24"/>
+      <c r="AH24"/>
+      <c r="AI24" t="s">
+        <v>699</v>
+      </c>
+      <c r="AJ24"/>
+      <c r="AK24" t="s">
+        <v>700</v>
+      </c>
+      <c r="AL24"/>
+      <c r="AM24" t="s">
+        <v>182</v>
+      </c>
+      <c r="AN24"/>
+      <c r="AO24"/>
+      <c r="AP24"/>
+      <c r="AQ24"/>
+      <c r="AR24"/>
+      <c r="AS24"/>
+      <c r="AT24"/>
+      <c r="AU24"/>
+      <c r="AV24"/>
+      <c r="AW24"/>
+      <c r="AX24"/>
+      <c r="AY24"/>
+      <c r="AZ24"/>
+      <c r="BA24"/>
+      <c r="BB24"/>
+      <c r="BC24"/>
+      <c r="BD24"/>
+      <c r="BE24"/>
+      <c r="BF24"/>
+      <c r="BG24"/>
+      <c r="BH24"/>
+      <c r="BI24"/>
+      <c r="BJ24"/>
+      <c r="BK24"/>
+      <c r="BL24"/>
+      <c r="BM24"/>
+      <c r="BN24"/>
+      <c r="BO24"/>
+      <c r="BP24"/>
+      <c r="BQ24"/>
+      <c r="BR24"/>
+      <c r="BS24"/>
+      <c r="BT24"/>
+      <c r="BU24"/>
+      <c r="BV24"/>
+      <c r="BW24"/>
+      <c r="BX24"/>
+      <c r="BY24"/>
+      <c r="BZ24"/>
+      <c r="CA24"/>
+      <c r="CB24"/>
+      <c r="CC24"/>
+      <c r="CD24"/>
+      <c r="CE24"/>
+      <c r="CF24"/>
+      <c r="CG24"/>
+      <c r="CH24"/>
+      <c r="CI24"/>
+      <c r="CJ24"/>
+      <c r="CK24"/>
+      <c r="CL24"/>
+      <c r="CM24"/>
+      <c r="CN24"/>
+      <c r="CO24"/>
+      <c r="CP24"/>
+      <c r="CQ24"/>
+      <c r="CR24"/>
+      <c r="CS24"/>
+      <c r="CT24"/>
+      <c r="CU24"/>
+      <c r="CV24"/>
+      <c r="CW24"/>
+      <c r="CX24"/>
+      <c r="CY24"/>
+      <c r="CZ24"/>
+      <c r="DA24"/>
+      <c r="DB24"/>
+      <c r="DC24"/>
+      <c r="DD24"/>
+      <c r="DE24"/>
+      <c r="DF24"/>
+      <c r="DG24"/>
+      <c r="DH24"/>
+      <c r="DI24"/>
+      <c r="DJ24"/>
+      <c r="DK24"/>
+      <c r="DL24"/>
+      <c r="DM24"/>
+      <c r="DN24"/>
+      <c r="DO24"/>
+      <c r="DP24"/>
+      <c r="DQ24"/>
+      <c r="DR24"/>
+      <c r="DS24"/>
+      <c r="DT24" t="s">
+        <v>694</v>
+      </c>
+      <c r="DU24" t="s">
+        <v>693</v>
+      </c>
+      <c r="DV24" t="s">
+        <v>695</v>
+      </c>
+      <c r="DW24" t="s">
+        <v>701</v>
+      </c>
+      <c r="DX24" t="s">
+        <v>693</v>
+      </c>
+      <c r="DY24" t="s">
+        <v>702</v>
+      </c>
+      <c r="DZ24"/>
+      <c r="EA24"/>
+      <c r="EB24"/>
+      <c r="EC24"/>
+      <c r="ED24"/>
+      <c r="EE24"/>
+      <c r="EF24"/>
+      <c r="EG24"/>
+      <c r="EH24"/>
+      <c r="EI24"/>
+      <c r="EJ24"/>
+      <c r="EK24"/>
+      <c r="EL24"/>
+      <c r="EM24"/>
+      <c r="EN24"/>
+      <c r="EO24"/>
+      <c r="EP24"/>
+      <c r="EQ24"/>
+      <c r="ER24"/>
+      <c r="ES24"/>
+      <c r="ET24"/>
+      <c r="EU24"/>
+      <c r="EV24"/>
+      <c r="EW24"/>
+      <c r="EX24"/>
+      <c r="EY24"/>
+      <c r="EZ24"/>
+      <c r="FA24"/>
+      <c r="FB24"/>
+      <c r="FC24"/>
+      <c r="FD24"/>
+      <c r="FE24"/>
+      <c r="FF24"/>
+      <c r="FG24"/>
+      <c r="FH24"/>
+      <c r="FI24"/>
+      <c r="FJ24"/>
+      <c r="FK24"/>
+      <c r="FL24"/>
+      <c r="FM24"/>
+      <c r="FN24"/>
+      <c r="FO24"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>690</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C25" t="s">
+        <v>703</v>
+      </c>
+      <c r="D25" t="s">
+        <v>461</v>
+      </c>
+      <c r="E25" t="s">
+        <v>703</v>
+      </c>
+      <c r="F25" t="s">
+        <v>338</v>
+      </c>
+      <c r="G25" t="s">
+        <v>691</v>
+      </c>
+      <c r="H25" t="s">
+        <v>253</v>
+      </c>
+      <c r="I25" t="s">
+        <v>170</v>
+      </c>
+      <c r="J25" t="s">
+        <v>171</v>
+      </c>
+      <c r="K25" t="s">
+        <v>541</v>
+      </c>
+      <c r="L25" t="s">
+        <v>566</v>
+      </c>
+      <c r="M25" t="s">
+        <v>543</v>
+      </c>
+      <c r="N25" t="s">
+        <v>704</v>
+      </c>
+      <c r="O25" t="s">
+        <v>693</v>
+      </c>
+      <c r="P25" t="s">
+        <v>705</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>706</v>
+      </c>
+      <c r="R25" t="s">
+        <v>693</v>
+      </c>
+      <c r="S25" t="s">
+        <v>707</v>
+      </c>
+      <c r="T25" t="s">
+        <v>696</v>
+      </c>
+      <c r="U25"/>
+      <c r="V25" t="s">
+        <v>173</v>
+      </c>
+      <c r="W25" t="s">
+        <v>175</v>
+      </c>
+      <c r="X25" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>708</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>568</v>
+      </c>
+      <c r="AD25"/>
+      <c r="AE25"/>
+      <c r="AF25" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="AG25"/>
+      <c r="AH25"/>
+      <c r="AI25" t="s">
+        <v>709</v>
+      </c>
+      <c r="AJ25"/>
+      <c r="AK25" t="s">
+        <v>710</v>
+      </c>
+      <c r="AL25"/>
+      <c r="AM25" t="s">
+        <v>320</v>
+      </c>
+      <c r="AN25"/>
+      <c r="AO25"/>
+      <c r="AP25"/>
+      <c r="AQ25"/>
+      <c r="AR25"/>
+      <c r="AS25"/>
+      <c r="AT25"/>
+      <c r="AU25"/>
+      <c r="AV25"/>
+      <c r="AW25"/>
+      <c r="AX25"/>
+      <c r="AY25"/>
+      <c r="AZ25"/>
+      <c r="BA25"/>
+      <c r="BB25"/>
+      <c r="BC25"/>
+      <c r="BD25"/>
+      <c r="BE25"/>
+      <c r="BF25"/>
+      <c r="BG25"/>
+      <c r="BH25"/>
+      <c r="BI25"/>
+      <c r="BJ25"/>
+      <c r="BK25"/>
+      <c r="BL25"/>
+      <c r="BM25"/>
+      <c r="BN25"/>
+      <c r="BO25"/>
+      <c r="BP25"/>
+      <c r="BQ25"/>
+      <c r="BR25"/>
+      <c r="BS25"/>
+      <c r="BT25"/>
+      <c r="BU25"/>
+      <c r="BV25"/>
+      <c r="BW25"/>
+      <c r="BX25"/>
+      <c r="BY25"/>
+      <c r="BZ25"/>
+      <c r="CA25"/>
+      <c r="CB25"/>
+      <c r="CC25"/>
+      <c r="CD25"/>
+      <c r="CE25"/>
+      <c r="CF25"/>
+      <c r="CG25"/>
+      <c r="CH25"/>
+      <c r="CI25"/>
+      <c r="CJ25"/>
+      <c r="CK25"/>
+      <c r="CL25"/>
+      <c r="CM25"/>
+      <c r="CN25"/>
+      <c r="CO25"/>
+      <c r="CP25"/>
+      <c r="CQ25"/>
+      <c r="CR25"/>
+      <c r="CS25"/>
+      <c r="CT25"/>
+      <c r="CU25"/>
+      <c r="CV25"/>
+      <c r="CW25"/>
+      <c r="CX25"/>
+      <c r="CY25"/>
+      <c r="CZ25"/>
+      <c r="DA25"/>
+      <c r="DB25"/>
+      <c r="DC25"/>
+      <c r="DD25"/>
+      <c r="DE25"/>
+      <c r="DF25"/>
+      <c r="DG25"/>
+      <c r="DH25"/>
+      <c r="DI25"/>
+      <c r="DJ25"/>
+      <c r="DK25"/>
+      <c r="DL25"/>
+      <c r="DM25"/>
+      <c r="DN25"/>
+      <c r="DO25"/>
+      <c r="DP25"/>
+      <c r="DQ25"/>
+      <c r="DR25"/>
+      <c r="DS25"/>
+      <c r="DT25" t="s">
+        <v>706</v>
+      </c>
+      <c r="DU25" t="s">
+        <v>693</v>
+      </c>
+      <c r="DV25" t="s">
+        <v>707</v>
+      </c>
+      <c r="DW25" t="s">
+        <v>694</v>
+      </c>
+      <c r="DX25" t="s">
+        <v>693</v>
+      </c>
+      <c r="DY25" t="s">
+        <v>705</v>
+      </c>
+      <c r="DZ25"/>
+      <c r="EA25"/>
+      <c r="EB25"/>
+      <c r="EC25"/>
+      <c r="ED25"/>
+      <c r="EE25"/>
+      <c r="EF25"/>
+      <c r="EG25"/>
+      <c r="EH25"/>
+      <c r="EI25"/>
+      <c r="EJ25"/>
+      <c r="EK25"/>
+      <c r="EL25"/>
+      <c r="EM25"/>
+      <c r="EN25"/>
+      <c r="EO25"/>
+      <c r="EP25"/>
+      <c r="EQ25"/>
+      <c r="ER25"/>
+      <c r="ES25"/>
+      <c r="ET25"/>
+      <c r="EU25"/>
+      <c r="EV25"/>
+      <c r="EW25"/>
+      <c r="EX25"/>
+      <c r="EY25"/>
+      <c r="EZ25"/>
+      <c r="FA25"/>
+      <c r="FB25"/>
+      <c r="FC25"/>
+      <c r="FD25"/>
+      <c r="FE25"/>
+      <c r="FF25"/>
+      <c r="FG25"/>
+      <c r="FH25"/>
+      <c r="FI25"/>
+      <c r="FJ25"/>
+      <c r="FK25"/>
+      <c r="FL25"/>
+      <c r="FM25"/>
+      <c r="FN25"/>
+      <c r="FO25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8887,7 +14959,7 @@
         <v>485</v>
       </c>
       <c r="T1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="U1" t="s">
         <v>11</v>
@@ -8923,7 +14995,7 @@
         <v>21</v>
       </c>
       <c r="AF1" t="s">
-        <v>487</v>
+        <v>711</v>
       </c>
       <c r="AG1" t="s">
         <v>22</v>
@@ -8944,40 +15016,40 @@
         <v>28</v>
       </c>
       <c r="AM1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AN1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AO1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AP1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AQ1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AR1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AS1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AT1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AU1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AV1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AW1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AX1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AY1" t="s">
         <v>29</v>
@@ -9151,22 +15223,22 @@
         <v>106</v>
       </c>
       <c r="DD1" t="s">
-        <v>500</v>
+        <v>712</v>
       </c>
       <c r="DE1" t="s">
-        <v>501</v>
+        <v>713</v>
       </c>
       <c r="DF1" t="s">
-        <v>502</v>
+        <v>714</v>
       </c>
       <c r="DG1" t="s">
-        <v>503</v>
+        <v>715</v>
       </c>
       <c r="DH1" t="s">
-        <v>504</v>
+        <v>716</v>
       </c>
       <c r="DI1" t="s">
-        <v>505</v>
+        <v>717</v>
       </c>
       <c r="DJ1" t="s">
         <v>107</v>
@@ -9244,40 +15316,40 @@
         <v>131</v>
       </c>
       <c r="EI1" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="EJ1" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="EK1" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="EL1" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="EM1" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="EN1" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="EO1" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="EP1" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="EQ1" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="ER1" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="ES1" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="ET1" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="EU1" t="s">
         <v>136</v>
@@ -9321,13 +15393,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="B2" t="n">
         <v>2010</v>
       </c>
       <c r="C2" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="D2" t="s">
         <v>166</v>
@@ -9339,7 +15411,7 @@
         <v>417</v>
       </c>
       <c r="G2" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="H2" t="s">
         <v>253</v>
@@ -9351,34 +15423,34 @@
         <v>171</v>
       </c>
       <c r="K2" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="L2" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="M2" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="N2" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="O2" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="P2" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="Q2" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="R2" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="S2" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="T2" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="U2" t="s">
         <v>174</v>
@@ -9410,13 +15482,13 @@
       <c r="AH2"/>
       <c r="AI2"/>
       <c r="AJ2" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="AK2" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="AL2" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="AM2"/>
       <c r="AN2"/>
@@ -9570,7 +15642,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="B3" t="n">
         <v>2010</v>
@@ -9579,16 +15651,16 @@
         <v>231</v>
       </c>
       <c r="D3" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="E3" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="F3" t="s">
         <v>417</v>
       </c>
       <c r="G3" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="H3" t="s">
         <v>253</v>
@@ -9600,34 +15672,34 @@
         <v>171</v>
       </c>
       <c r="K3" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="L3" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="M3" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="N3" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="O3" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="P3" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="Q3" t="s">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="R3" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="S3" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="T3" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="U3" t="s">
         <v>174</v>
@@ -9659,13 +15731,13 @@
       <c r="AH3"/>
       <c r="AI3"/>
       <c r="AJ3" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="AK3" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="AL3" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="AM3"/>
       <c r="AN3"/>
@@ -10335,13 +16407,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>542</v>
+        <v>718</v>
       </c>
       <c r="B6" t="n">
         <v>2012</v>
       </c>
       <c r="C6" t="s">
-        <v>543</v>
+        <v>719</v>
       </c>
       <c r="D6" t="s">
         <v>215</v>
@@ -10353,7 +16425,7 @@
         <v>417</v>
       </c>
       <c r="G6" t="s">
-        <v>544</v>
+        <v>720</v>
       </c>
       <c r="H6" t="s">
         <v>169</v>
@@ -10396,28 +16468,28 @@
       </c>
       <c r="AA6"/>
       <c r="AB6" t="s">
-        <v>545</v>
+        <v>721</v>
       </c>
       <c r="AC6" t="s">
-        <v>546</v>
+        <v>722</v>
       </c>
       <c r="AD6" t="s">
-        <v>547</v>
+        <v>723</v>
       </c>
       <c r="AE6" t="s">
-        <v>548</v>
+        <v>724</v>
       </c>
       <c r="AF6" t="s">
-        <v>549</v>
+        <v>725</v>
       </c>
       <c r="AG6"/>
       <c r="AH6"/>
       <c r="AI6"/>
       <c r="AJ6" t="s">
-        <v>550</v>
+        <v>726</v>
       </c>
       <c r="AK6" t="s">
-        <v>551</v>
+        <v>727</v>
       </c>
       <c r="AL6" t="s">
         <v>193</v>
@@ -10492,22 +16564,22 @@
       <c r="DB6"/>
       <c r="DC6"/>
       <c r="DD6" t="s">
-        <v>552</v>
+        <v>728</v>
       </c>
       <c r="DE6" t="s">
-        <v>553</v>
+        <v>729</v>
       </c>
       <c r="DF6" t="s">
-        <v>554</v>
+        <v>730</v>
       </c>
       <c r="DG6" t="s">
-        <v>555</v>
+        <v>731</v>
       </c>
       <c r="DH6" t="s">
-        <v>553</v>
+        <v>729</v>
       </c>
       <c r="DI6" t="s">
-        <v>556</v>
+        <v>732</v>
       </c>
       <c r="DJ6"/>
       <c r="DK6"/>
@@ -10562,13 +16634,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>542</v>
+        <v>718</v>
       </c>
       <c r="B7" t="n">
         <v>2012</v>
       </c>
       <c r="C7" t="s">
-        <v>557</v>
+        <v>733</v>
       </c>
       <c r="D7" t="s">
         <v>166</v>
@@ -10580,7 +16652,7 @@
         <v>417</v>
       </c>
       <c r="G7" t="s">
-        <v>544</v>
+        <v>720</v>
       </c>
       <c r="H7" t="s">
         <v>169</v>
@@ -10626,25 +16698,25 @@
         <v>178</v>
       </c>
       <c r="AC7" t="s">
-        <v>558</v>
+        <v>734</v>
       </c>
       <c r="AD7" t="s">
-        <v>559</v>
+        <v>735</v>
       </c>
       <c r="AE7" t="s">
-        <v>560</v>
+        <v>736</v>
       </c>
       <c r="AF7" t="s">
-        <v>549</v>
+        <v>725</v>
       </c>
       <c r="AG7"/>
       <c r="AH7"/>
       <c r="AI7"/>
       <c r="AJ7" t="s">
-        <v>561</v>
+        <v>737</v>
       </c>
       <c r="AK7" t="s">
-        <v>562</v>
+        <v>738</v>
       </c>
       <c r="AL7" t="s">
         <v>182</v>
@@ -10719,22 +16791,22 @@
       <c r="DB7"/>
       <c r="DC7"/>
       <c r="DD7" t="s">
-        <v>563</v>
+        <v>739</v>
       </c>
       <c r="DE7" t="s">
-        <v>553</v>
+        <v>729</v>
       </c>
       <c r="DF7" t="s">
-        <v>564</v>
+        <v>652</v>
       </c>
       <c r="DG7" t="s">
-        <v>565</v>
+        <v>740</v>
       </c>
       <c r="DH7" t="s">
-        <v>553</v>
+        <v>729</v>
       </c>
       <c r="DI7" t="s">
-        <v>566</v>
+        <v>741</v>
       </c>
       <c r="DJ7"/>
       <c r="DK7"/>
@@ -10789,13 +16861,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>567</v>
+        <v>641</v>
       </c>
       <c r="B8" t="n">
         <v>2014</v>
       </c>
       <c r="C8" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="D8" t="s">
         <v>166</v>
@@ -10807,7 +16879,7 @@
         <v>417</v>
       </c>
       <c r="G8" t="s">
-        <v>569</v>
+        <v>642</v>
       </c>
       <c r="H8" t="s">
         <v>253</v>
@@ -10822,31 +16894,31 @@
         <v>172</v>
       </c>
       <c r="L8" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="M8" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="N8" t="s">
-        <v>571</v>
+        <v>643</v>
       </c>
       <c r="O8" t="s">
-        <v>572</v>
+        <v>644</v>
       </c>
       <c r="P8" t="s">
-        <v>573</v>
+        <v>645</v>
       </c>
       <c r="Q8" t="s">
-        <v>574</v>
+        <v>646</v>
       </c>
       <c r="R8" t="s">
-        <v>572</v>
+        <v>644</v>
       </c>
       <c r="S8" t="s">
-        <v>575</v>
+        <v>647</v>
       </c>
       <c r="T8" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="U8" t="s">
         <v>174</v>
@@ -10878,31 +16950,31 @@
       <c r="AH8"/>
       <c r="AI8"/>
       <c r="AJ8" t="s">
-        <v>576</v>
+        <v>648</v>
       </c>
       <c r="AK8" t="s">
-        <v>577</v>
+        <v>649</v>
       </c>
       <c r="AL8" t="s">
-        <v>578</v>
+        <v>650</v>
       </c>
       <c r="AM8" t="s">
-        <v>579</v>
+        <v>651</v>
       </c>
       <c r="AN8" t="s">
-        <v>572</v>
+        <v>644</v>
       </c>
       <c r="AO8" t="s">
-        <v>564</v>
+        <v>652</v>
       </c>
       <c r="AP8" t="s">
-        <v>580</v>
+        <v>653</v>
       </c>
       <c r="AQ8" t="s">
-        <v>572</v>
+        <v>644</v>
       </c>
       <c r="AR8" t="s">
-        <v>581</v>
+        <v>654</v>
       </c>
       <c r="AS8"/>
       <c r="AT8"/>
@@ -11050,25 +17122,25 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>567</v>
+        <v>641</v>
       </c>
       <c r="B9" t="n">
         <v>2014</v>
       </c>
       <c r="C9" t="s">
-        <v>582</v>
+        <v>655</v>
       </c>
       <c r="D9" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="E9" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="F9" t="s">
         <v>417</v>
       </c>
       <c r="G9" t="s">
-        <v>569</v>
+        <v>642</v>
       </c>
       <c r="H9" t="s">
         <v>253</v>
@@ -11083,31 +17155,31 @@
         <v>172</v>
       </c>
       <c r="L9" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="M9" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="N9" t="s">
-        <v>583</v>
+        <v>656</v>
       </c>
       <c r="O9" t="s">
-        <v>584</v>
+        <v>657</v>
       </c>
       <c r="P9" t="s">
-        <v>573</v>
+        <v>645</v>
       </c>
       <c r="Q9" t="s">
-        <v>585</v>
+        <v>658</v>
       </c>
       <c r="R9" t="s">
-        <v>584</v>
+        <v>657</v>
       </c>
       <c r="S9" t="s">
-        <v>586</v>
+        <v>659</v>
       </c>
       <c r="T9" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="U9" t="s">
         <v>174</v>
@@ -11139,31 +17211,31 @@
       <c r="AH9"/>
       <c r="AI9"/>
       <c r="AJ9" t="s">
-        <v>587</v>
+        <v>660</v>
       </c>
       <c r="AK9" t="s">
-        <v>588</v>
+        <v>661</v>
       </c>
       <c r="AL9" t="s">
-        <v>589</v>
+        <v>662</v>
       </c>
       <c r="AM9" t="s">
-        <v>590</v>
+        <v>663</v>
       </c>
       <c r="AN9" t="s">
-        <v>584</v>
+        <v>657</v>
       </c>
       <c r="AO9" t="s">
-        <v>591</v>
+        <v>664</v>
       </c>
       <c r="AP9" t="s">
-        <v>592</v>
+        <v>665</v>
       </c>
       <c r="AQ9" t="s">
-        <v>584</v>
+        <v>657</v>
       </c>
       <c r="AR9" t="s">
-        <v>593</v>
+        <v>666</v>
       </c>
       <c r="AS9"/>
       <c r="AT9"/>
